--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-ballot</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:44:45+00:00</t>
+    <t>2024-03-25T10:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1880,28 +1880,28 @@
     <t>NK1-7, NK1-3</t>
   </si>
   <si>
-    <t>Patient.contact.relationship:RolePerson</t>
-  </si>
-  <si>
-    <t>RolePerson</t>
+    <t>Patient.contact.relationship:Role</t>
+  </si>
+  <si>
+    <t>Role</t>
   </si>
   <si>
     <t>The nature of the relationship. Rôle de la personne. Ex : personne de confiance, aidant ...</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-related-person-role</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship:RelatedPerson</t>
-  </si>
-  <si>
-    <t>RelatedPerson</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-role</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:RelationType</t>
+  </si>
+  <si>
+    <t>RelationType</t>
   </si>
   <si>
     <t>The nature of the relationship. Relation de la personne. Ex : Mère, époux, enfant ...</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-related-person</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-relation-type</t>
   </si>
   <si>
     <t>Patient.contact.name</t>
@@ -16556,10 +16556,10 @@
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>81</v>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:59:40+00:00</t>
+    <t>2024-03-25T11:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T08:02:06+00:00</t>
+    <t>2024-05-23T12:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:05:52+00:00</t>
+    <t>2024-05-23T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:32:02+00:00</t>
+    <t>2024-05-23T14:35:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T14:35:00+00:00</t>
+    <t>2024-06-11T15:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:12+00:00</t>
+    <t>2024-06-11T15:33:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:34+00:00</t>
+    <t>2024-07-02T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(WORK))</t>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T11:39:28+00:00</t>
+    <t>2024-07-17T12:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:13:27+00:00</t>
+    <t>2024-07-17T14:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T14:21:13+00:00</t>
+    <t>2024-07-17T15:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:15:49+00:00</t>
+    <t>2024-07-17T15:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T07:11:02+00:00</t>
+    <t>2024-07-25T15:28:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:28:42+00:00</t>
+    <t>2024-07-25T15:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:29:18+00:00</t>
+    <t>2024-07-25T15:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -10085,7 +10085,7 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:44:10+00:00</t>
+    <t>2024-08-01T13:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0-ballot</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-03T15:38:30+00:00</t>
+    <t>2024-09-04T07:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T07:28:39+00:00</t>
+    <t>2024-09-04T07:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5315" uniqueCount="684">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5315" uniqueCount="683">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T12:53:53+00:00</t>
+    <t>2024-10-28T08:07:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -431,7 +431,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -451,7 +451,7 @@
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -1664,9 +1664,6 @@
   </si>
   <si>
     <t>Patient.address</t>
-  </si>
-  <si>
-    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](location.html#) resource).</t>
   </si>
   <si>
     <t>May need to keep track of patient addresses for contacting, billing or reporting requirements and also to help with identification.</t>
@@ -7211,7 +7208,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>90</v>
@@ -7449,7 +7446,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>90</v>
@@ -8268,7 +8265,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>90</v>
@@ -8408,7 +8405,7 @@
         <v>273</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>330</v>
+        <v>274</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>275</v>
@@ -8506,7 +8503,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>90</v>
@@ -9325,7 +9322,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>90</v>
@@ -10382,7 +10379,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>90</v>
@@ -11439,7 +11436,7 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>90</v>
@@ -12266,7 +12263,7 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>81</v>
@@ -13557,7 +13554,7 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>81</v>
@@ -15344,10 +15341,10 @@
         <v>238</v>
       </c>
       <c r="N110" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O110" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15428,10 +15425,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15457,14 +15454,14 @@
         <v>272</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15493,7 +15490,7 @@
       </c>
       <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>82</v>
@@ -15511,7 +15508,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15526,16 +15523,16 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AL111" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="AL111" t="s" s="2">
+      <c r="AM111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN111" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN111" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -15543,10 +15540,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15569,19 +15566,19 @@
         <v>82</v>
       </c>
       <c r="K112" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="L112" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="L112" t="s" s="2">
+      <c r="M112" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="M112" t="s" s="2">
+      <c r="N112" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="N112" t="s" s="2">
+      <c r="O112" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -15630,7 +15627,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -15645,7 +15642,7 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>108</v>
@@ -15654,7 +15651,7 @@
         <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -15662,10 +15659,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15688,19 +15685,19 @@
         <v>82</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="L113" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="L113" t="s" s="2">
+      <c r="M113" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="N113" t="s" s="2">
+      <c r="O113" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>82</v>
@@ -15749,7 +15746,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -15764,7 +15761,7 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>108</v>
@@ -15773,7 +15770,7 @@
         <v>82</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -15781,10 +15778,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15807,19 +15804,19 @@
         <v>82</v>
       </c>
       <c r="K114" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="L114" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="L114" t="s" s="2">
+      <c r="M114" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="M114" t="s" s="2">
+      <c r="N114" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="N114" t="s" s="2">
+      <c r="O114" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>82</v>
@@ -15868,7 +15865,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -15880,10 +15877,10 @@
         <v>82</v>
       </c>
       <c r="AJ114" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AK114" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="AK114" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>108</v>
@@ -15900,10 +15897,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16015,10 +16012,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16128,13 +16125,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="C117" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="C117" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="D117" t="s" s="2">
         <v>82</v>
@@ -16156,13 +16153,13 @@
         <v>82</v>
       </c>
       <c r="K117" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="L117" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="L117" t="s" s="2">
+      <c r="M117" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -16245,13 +16242,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="C118" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="C118" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>82</v>
@@ -16273,13 +16270,13 @@
         <v>82</v>
       </c>
       <c r="K118" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="L118" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="L118" t="s" s="2">
+      <c r="M118" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16362,14 +16359,14 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -16391,10 +16388,10 @@
         <v>111</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>114</v>
@@ -16449,7 +16446,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -16481,10 +16478,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16510,14 +16507,14 @@
         <v>272</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>576</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>577</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
@@ -16545,16 +16542,16 @@
         <v>152</v>
       </c>
       <c r="Y120" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="Z120" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="Z120" t="s" s="2">
+      <c r="AA120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB120" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="AC120" s="2"/>
       <c r="AD120" t="s" s="2">
@@ -16564,7 +16561,7 @@
         <v>117</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -16579,7 +16576,7 @@
         <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AL120" t="s" s="2">
         <v>108</v>
@@ -16588,7 +16585,7 @@
         <v>82</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>82</v>
@@ -16596,13 +16593,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="C121" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="C121" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>82</v>
@@ -16627,14 +16624,14 @@
         <v>272</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>82</v>
@@ -16663,7 +16660,7 @@
       </c>
       <c r="Y121" s="2"/>
       <c r="Z121" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>82</v>
@@ -16681,7 +16678,7 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -16696,7 +16693,7 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>108</v>
@@ -16705,7 +16702,7 @@
         <v>82</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>82</v>
@@ -16713,13 +16710,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="C122" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="C122" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>82</v>
@@ -16744,14 +16741,14 @@
         <v>272</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>82</v>
@@ -16780,7 +16777,7 @@
       </c>
       <c r="Y122" s="2"/>
       <c r="Z122" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>82</v>
@@ -16798,7 +16795,7 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -16813,7 +16810,7 @@
         <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>108</v>
@@ -16822,7 +16819,7 @@
         <v>82</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>82</v>
@@ -16830,10 +16827,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16859,16 +16856,16 @@
         <v>390</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="N123" t="s" s="2">
+      <c r="O123" t="s" s="2">
         <v>595</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>596</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>82</v>
@@ -16917,7 +16914,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -16932,16 +16929,16 @@
         <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN123" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>82</v>
@@ -16949,10 +16946,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16984,7 +16981,7 @@
         <v>489</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="O124" t="s" s="2">
         <v>491</v>
@@ -17036,7 +17033,7 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17068,10 +17065,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17094,17 +17091,17 @@
         <v>82</v>
       </c>
       <c r="K125" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="L125" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="L125" t="s" s="2">
+      <c r="M125" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>82</v>
@@ -17153,7 +17150,7 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17168,7 +17165,7 @@
         <v>102</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AL125" t="s" s="2">
         <v>108</v>
@@ -17177,7 +17174,7 @@
         <v>82</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>82</v>
@@ -17185,10 +17182,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17217,11 +17214,11 @@
         <v>496</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>82</v>
@@ -17270,7 +17267,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17294,7 +17291,7 @@
         <v>82</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>82</v>
@@ -17302,10 +17299,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17331,14 +17328,14 @@
         <v>305</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>82</v>
@@ -17387,7 +17384,7 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17396,13 +17393,13 @@
         <v>90</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>108</v>
@@ -17411,7 +17408,7 @@
         <v>82</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>82</v>
@@ -17419,10 +17416,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17448,10 +17445,10 @@
         <v>298</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -17502,7 +17499,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -17517,7 +17514,7 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>108</v>
@@ -17534,10 +17531,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17560,19 +17557,19 @@
         <v>82</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="M129" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="M129" t="s" s="2">
+      <c r="N129" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="N129" t="s" s="2">
+      <c r="O129" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>627</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>82</v>
@@ -17621,7 +17618,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -17636,10 +17633,10 @@
         <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AL129" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="AL129" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>82</v>
@@ -17653,10 +17650,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17768,10 +17765,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17885,14 +17882,14 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -17914,10 +17911,10 @@
         <v>111</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="N132" t="s" s="2">
         <v>114</v>
@@ -17972,7 +17969,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18004,10 +18001,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18033,16 +18030,16 @@
         <v>272</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="M133" t="s" s="2">
+      <c r="N133" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="N133" t="s" s="2">
+      <c r="O133" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>82</v>
@@ -18091,7 +18088,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>90</v>
@@ -18106,16 +18103,16 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AL133" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="AL133" t="s" s="2">
+      <c r="AM133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN133" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="AM133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN133" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>82</v>
@@ -18123,10 +18120,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18152,16 +18149,16 @@
         <v>381</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="N134" t="s" s="2">
+      <c r="O134" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>645</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>82</v>
@@ -18210,7 +18207,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18225,16 +18222,16 @@
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AL134" t="s" s="2">
         <v>646</v>
       </c>
-      <c r="AL134" t="s" s="2">
+      <c r="AM134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN134" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="AM134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN134" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>82</v>
@@ -18242,14 +18239,14 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
@@ -18268,16 +18265,16 @@
         <v>82</v>
       </c>
       <c r="K135" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="L135" t="s" s="2">
         <v>651</v>
       </c>
-      <c r="L135" t="s" s="2">
+      <c r="M135" t="s" s="2">
         <v>652</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="N135" t="s" s="2">
         <v>653</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>654</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -18327,7 +18324,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18342,7 +18339,7 @@
         <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>108</v>
@@ -18351,7 +18348,7 @@
         <v>82</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>82</v>
@@ -18359,10 +18356,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18385,19 +18382,19 @@
         <v>91</v>
       </c>
       <c r="K136" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="L136" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="L136" t="s" s="2">
+      <c r="M136" t="s" s="2">
         <v>659</v>
       </c>
-      <c r="M136" t="s" s="2">
+      <c r="N136" t="s" s="2">
         <v>660</v>
       </c>
-      <c r="N136" t="s" s="2">
+      <c r="O136" t="s" s="2">
         <v>661</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>662</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>82</v>
@@ -18446,7 +18443,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -18461,10 +18458,10 @@
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>82</v>
@@ -18478,10 +18475,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18504,19 +18501,19 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="L137" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="M137" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="M137" t="s" s="2">
+      <c r="N137" t="s" s="2">
         <v>666</v>
       </c>
-      <c r="N137" t="s" s="2">
+      <c r="O137" t="s" s="2">
         <v>667</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>668</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>82</v>
@@ -18565,7 +18562,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -18580,7 +18577,7 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>108</v>
@@ -18597,10 +18594,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18712,10 +18709,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18829,14 +18826,14 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -18858,10 +18855,10 @@
         <v>111</v>
       </c>
       <c r="L140" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="M140" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="N140" t="s" s="2">
         <v>114</v>
@@ -18916,7 +18913,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -18948,10 +18945,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18974,16 +18971,16 @@
         <v>91</v>
       </c>
       <c r="K141" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="L141" t="s" s="2">
         <v>674</v>
       </c>
-      <c r="L141" t="s" s="2">
+      <c r="M141" t="s" s="2">
         <v>675</v>
       </c>
-      <c r="M141" t="s" s="2">
+      <c r="N141" t="s" s="2">
         <v>676</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>677</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -19033,7 +19030,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>90</v>
@@ -19057,7 +19054,7 @@
         <v>82</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>82</v>
@@ -19065,10 +19062,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19094,10 +19091,10 @@
         <v>170</v>
       </c>
       <c r="L142" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="M142" t="s" s="2">
         <v>680</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>681</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -19127,11 +19124,11 @@
         <v>266</v>
       </c>
       <c r="Y142" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="Z142" t="s" s="2">
         <v>681</v>
       </c>
-      <c r="Z142" t="s" s="2">
-        <v>682</v>
-      </c>
       <c r="AA142" t="s" s="2">
         <v>82</v>
       </c>
@@ -19148,7 +19145,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>90</v>
@@ -19163,7 +19160,7 @@
         <v>102</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>108</v>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:07:18+00:00</t>
+    <t>2024-10-28T08:08:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:08:30+00:00</t>
+    <t>2024-10-29T10:42:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:05:50+00:00</t>
+    <t>2025-01-28T09:07:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:07:36+00:00</t>
+    <t>2025-02-04T08:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T08:51:44+00:00</t>
+    <t>2025-02-04T09:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5313" uniqueCount="687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5308" uniqueCount="685">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T09:30:35+00:00</t>
+    <t>2025-02-19T13:47:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1012,12 +1012,6 @@
     &lt;code value="NH"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
     <t>Patient.identifier:NSS.system</t>
@@ -7391,11 +7385,9 @@
       <c r="X42" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="Y42" t="s" s="2">
-        <v>319</v>
-      </c>
+      <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>320</v>
+        <v>275</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7445,7 +7437,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>278</v>
@@ -7493,7 +7485,7 @@
         <v>82</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>283</v>
@@ -7564,7 +7556,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>287</v>
@@ -7681,7 +7673,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>295</v>
@@ -7796,7 +7788,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>302</v>
@@ -7913,13 +7905,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>246</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>82</v>
@@ -7944,7 +7936,7 @@
         <v>247</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="M47" t="s" s="2">
         <v>249</v>
@@ -8032,7 +8024,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>257</v>
@@ -8147,7 +8139,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>258</v>
@@ -8264,7 +8256,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>259</v>
@@ -8312,7 +8304,7 @@
         <v>82</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>82</v>
@@ -8383,7 +8375,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>269</v>
@@ -8431,7 +8423,7 @@
         <v>82</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>82</v>
@@ -8448,11 +8440,9 @@
       <c r="X51" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="Y51" t="s" s="2">
-        <v>319</v>
-      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>320</v>
+        <v>275</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8502,7 +8492,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>278</v>
@@ -8550,7 +8540,7 @@
         <v>82</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>283</v>
@@ -8621,7 +8611,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>287</v>
@@ -8738,7 +8728,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>295</v>
@@ -8853,7 +8843,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>302</v>
@@ -8970,13 +8960,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>246</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>82</v>
@@ -9001,7 +8991,7 @@
         <v>247</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="M56" t="s" s="2">
         <v>249</v>
@@ -9089,7 +9079,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>257</v>
@@ -9204,7 +9194,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>258</v>
@@ -9321,7 +9311,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>259</v>
@@ -9369,7 +9359,7 @@
         <v>82</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>82</v>
@@ -9440,7 +9430,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>269</v>
@@ -9488,7 +9478,7 @@
         <v>82</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>82</v>
@@ -9505,11 +9495,9 @@
       <c r="X60" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="Y60" t="s" s="2">
-        <v>319</v>
-      </c>
+      <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>320</v>
+        <v>275</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9559,7 +9547,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>278</v>
@@ -9607,7 +9595,7 @@
         <v>82</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>283</v>
@@ -9678,7 +9666,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>287</v>
@@ -9795,7 +9783,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>295</v>
@@ -9910,7 +9898,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>302</v>
@@ -10027,13 +10015,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>246</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>82</v>
@@ -10058,7 +10046,7 @@
         <v>247</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="M65" t="s" s="2">
         <v>249</v>
@@ -10146,7 +10134,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>257</v>
@@ -10261,7 +10249,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>258</v>
@@ -10378,7 +10366,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>259</v>
@@ -10426,7 +10414,7 @@
         <v>82</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>82</v>
@@ -10497,7 +10485,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>269</v>
@@ -10545,7 +10533,7 @@
         <v>82</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>82</v>
@@ -10562,11 +10550,9 @@
       <c r="X69" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="Y69" t="s" s="2">
-        <v>319</v>
-      </c>
+      <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>320</v>
+        <v>275</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10616,7 +10602,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>278</v>
@@ -10735,7 +10721,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>287</v>
@@ -10852,7 +10838,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>295</v>
@@ -10967,7 +10953,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>302</v>
@@ -11084,13 +11070,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>246</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D74" t="s" s="2">
         <v>82</v>
@@ -11115,7 +11101,7 @@
         <v>247</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="M74" t="s" s="2">
         <v>249</v>
@@ -11203,7 +11189,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>257</v>
@@ -11318,7 +11304,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>258</v>
@@ -11435,7 +11421,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>259</v>
@@ -11483,7 +11469,7 @@
         <v>82</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>82</v>
@@ -11554,7 +11540,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>269</v>
@@ -11602,7 +11588,7 @@
         <v>82</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>82</v>
@@ -11619,11 +11605,9 @@
       <c r="X78" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="Y78" t="s" s="2">
-        <v>319</v>
-      </c>
+      <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>320</v>
+        <v>275</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>82</v>
@@ -11673,7 +11657,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>278</v>
@@ -11792,7 +11776,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>287</v>
@@ -11909,7 +11893,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>295</v>
@@ -12024,7 +12008,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>302</v>
@@ -12141,10 +12125,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12167,26 +12151,26 @@
         <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="N83" t="s" s="2">
+      <c r="P83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q83" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="O83" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="P83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q83" t="s" s="2">
-        <v>384</v>
-      </c>
       <c r="R83" t="s" s="2">
         <v>82</v>
       </c>
@@ -12230,7 +12214,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12245,13 +12229,13 @@
         <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>82</v>
@@ -12262,10 +12246,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12273,7 +12257,7 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>81</v>
@@ -12288,19 +12272,19 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12337,7 +12321,7 @@
         <v>82</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AC84" s="2"/>
       <c r="AD84" t="s" s="2">
@@ -12347,7 +12331,7 @@
         <v>117</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12362,16 +12346,16 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12379,13 +12363,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D85" t="s" s="2">
         <v>82</v>
@@ -12407,19 +12391,19 @@
         <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="L85" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>401</v>
-      </c>
       <c r="N85" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12468,7 +12452,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12483,16 +12467,16 @@
         <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12500,10 +12484,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12615,10 +12599,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12732,10 +12716,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12761,16 +12745,16 @@
         <v>170</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="N88" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -12780,7 +12764,7 @@
         <v>82</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>82</v>
@@ -12798,28 +12782,28 @@
         <v>264</v>
       </c>
       <c r="Y88" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF88" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12834,7 +12818,7 @@
         <v>102</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>82</v>
@@ -12843,7 +12827,7 @@
         <v>82</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -12851,10 +12835,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12880,16 +12864,16 @@
         <v>104</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="N89" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="O89" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -12938,7 +12922,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12953,7 +12937,7 @@
         <v>102</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>82</v>
@@ -12962,7 +12946,7 @@
         <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -12970,14 +12954,14 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -12999,13 +12983,13 @@
         <v>104</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N90" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13055,7 +13039,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13070,7 +13054,7 @@
         <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>82</v>
@@ -13079,7 +13063,7 @@
         <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13087,14 +13071,14 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13116,13 +13100,13 @@
         <v>104</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13172,7 +13156,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13187,7 +13171,7 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>82</v>
@@ -13196,7 +13180,7 @@
         <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13204,10 +13188,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13233,10 +13217,10 @@
         <v>104</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13287,7 +13271,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13302,7 +13286,7 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>82</v>
@@ -13311,7 +13295,7 @@
         <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13319,10 +13303,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13348,10 +13332,10 @@
         <v>104</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13402,7 +13386,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13417,7 +13401,7 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>82</v>
@@ -13426,7 +13410,7 @@
         <v>82</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13434,10 +13418,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13463,14 +13447,14 @@
         <v>296</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13519,7 +13503,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13534,7 +13518,7 @@
         <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>82</v>
@@ -13543,7 +13527,7 @@
         <v>82</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13551,20 +13535,20 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>81</v>
@@ -13579,19 +13563,19 @@
         <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13640,7 +13624,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13655,16 +13639,16 @@
         <v>102</v>
       </c>
       <c r="AK95" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13672,10 +13656,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13787,10 +13771,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13904,13 +13888,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>82</v>
@@ -13932,13 +13916,13 @@
         <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -14021,10 +14005,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14050,16 +14034,16 @@
         <v>170</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="N99" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="O99" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
@@ -14087,28 +14071,28 @@
         <v>264</v>
       </c>
       <c r="Y99" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF99" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14123,7 +14107,7 @@
         <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>82</v>
@@ -14132,7 +14116,7 @@
         <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14140,10 +14124,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14169,16 +14153,16 @@
         <v>104</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="N100" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14227,7 +14211,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14242,7 +14226,7 @@
         <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>82</v>
@@ -14251,7 +14235,7 @@
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14259,14 +14243,14 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14288,13 +14272,13 @@
         <v>104</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N101" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14344,7 +14328,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14359,7 +14343,7 @@
         <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>82</v>
@@ -14368,7 +14352,7 @@
         <v>82</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14376,14 +14360,14 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -14405,13 +14389,13 @@
         <v>104</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N102" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14461,7 +14445,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14476,7 +14460,7 @@
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>82</v>
@@ -14485,7 +14469,7 @@
         <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14493,10 +14477,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14522,10 +14506,10 @@
         <v>104</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14576,7 +14560,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14591,7 +14575,7 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>82</v>
@@ -14600,7 +14584,7 @@
         <v>82</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14608,10 +14592,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14637,10 +14621,10 @@
         <v>104</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14691,7 +14675,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14706,7 +14690,7 @@
         <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>82</v>
@@ -14715,7 +14699,7 @@
         <v>82</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -14723,10 +14707,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14752,14 +14736,14 @@
         <v>296</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
@@ -14808,7 +14792,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14823,7 +14807,7 @@
         <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>82</v>
@@ -14832,7 +14816,7 @@
         <v>82</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -14840,10 +14824,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14866,19 +14850,19 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="L106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="O106" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -14927,7 +14911,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14942,16 +14926,16 @@
         <v>102</v>
       </c>
       <c r="AK106" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN106" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -14959,10 +14943,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14988,16 +14972,16 @@
         <v>170</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="N107" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>82</v>
@@ -15025,10 +15009,10 @@
         <v>264</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -15046,7 +15030,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15061,16 +15045,16 @@
         <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN107" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AL107" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15078,10 +15062,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15104,19 +15088,19 @@
         <v>91</v>
       </c>
       <c r="K108" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="L108" t="s" s="2">
+      <c r="N108" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="M108" t="s" s="2">
+      <c r="O108" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -15165,7 +15149,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15180,27 +15164,27 @@
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN108" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="AL108" t="s" s="2">
+      <c r="AO108" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>512</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15223,19 +15207,19 @@
         <v>91</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="N109" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="M109" t="s" s="2">
+      <c r="O109" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15284,7 +15268,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15299,7 +15283,7 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>108</v>
@@ -15308,7 +15292,7 @@
         <v>82</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>
@@ -15316,10 +15300,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15345,16 +15329,16 @@
         <v>236</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="N110" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="O110" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15403,7 +15387,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15418,16 +15402,16 @@
         <v>102</v>
       </c>
       <c r="AK110" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN110" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="AL110" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN110" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -15435,10 +15419,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15464,14 +15448,14 @@
         <v>270</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15500,7 +15484,7 @@
       </c>
       <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>82</v>
@@ -15518,7 +15502,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15533,16 +15517,16 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN111" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="AL111" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN111" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -15550,10 +15534,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15576,19 +15560,19 @@
         <v>82</v>
       </c>
       <c r="K112" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="L112" t="s" s="2">
+      <c r="N112" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="M112" t="s" s="2">
+      <c r="O112" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -15637,7 +15621,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -15652,7 +15636,7 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>108</v>
@@ -15661,7 +15645,7 @@
         <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -15669,10 +15653,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15695,19 +15679,19 @@
         <v>82</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="L113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="O113" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>82</v>
@@ -15756,7 +15740,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -15771,7 +15755,7 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>108</v>
@@ -15780,7 +15764,7 @@
         <v>82</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -15788,10 +15772,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15814,19 +15798,19 @@
         <v>82</v>
       </c>
       <c r="K114" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="L114" t="s" s="2">
+      <c r="N114" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="M114" t="s" s="2">
+      <c r="O114" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>82</v>
@@ -15875,7 +15859,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -15887,10 +15871,10 @@
         <v>82</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>108</v>
@@ -15907,10 +15891,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16022,10 +16006,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16135,13 +16119,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B117" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="C117" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="C117" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="D117" t="s" s="2">
         <v>82</v>
@@ -16163,13 +16147,13 @@
         <v>82</v>
       </c>
       <c r="K117" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="L117" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -16252,13 +16236,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>82</v>
@@ -16280,13 +16264,13 @@
         <v>82</v>
       </c>
       <c r="K118" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="L118" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16369,14 +16353,14 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -16398,10 +16382,10 @@
         <v>111</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>114</v>
@@ -16456,7 +16440,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -16488,10 +16472,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16517,14 +16501,14 @@
         <v>270</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
@@ -16552,16 +16536,16 @@
         <v>152</v>
       </c>
       <c r="Y120" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB120" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="Z120" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="AC120" s="2"/>
       <c r="AD120" t="s" s="2">
@@ -16571,7 +16555,7 @@
         <v>117</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -16586,7 +16570,7 @@
         <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="AL120" t="s" s="2">
         <v>108</v>
@@ -16595,7 +16579,7 @@
         <v>82</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>82</v>
@@ -16603,13 +16587,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>82</v>
@@ -16634,14 +16618,14 @@
         <v>270</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>82</v>
@@ -16670,7 +16654,7 @@
       </c>
       <c r="Y121" s="2"/>
       <c r="Z121" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>82</v>
@@ -16688,7 +16672,7 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -16703,7 +16687,7 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>108</v>
@@ -16712,7 +16696,7 @@
         <v>82</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>82</v>
@@ -16720,13 +16704,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>82</v>
@@ -16751,14 +16735,14 @@
         <v>270</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>82</v>
@@ -16787,7 +16771,7 @@
       </c>
       <c r="Y122" s="2"/>
       <c r="Z122" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>82</v>
@@ -16805,7 +16789,7 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -16820,7 +16804,7 @@
         <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>108</v>
@@ -16829,7 +16813,7 @@
         <v>82</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>82</v>
@@ -16837,10 +16821,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16863,17 +16847,17 @@
         <v>82</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>82</v>
@@ -16922,7 +16906,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -16937,7 +16921,7 @@
         <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>108</v>
@@ -16946,7 +16930,7 @@
         <v>82</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>82</v>
@@ -16954,10 +16938,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16980,19 +16964,19 @@
         <v>82</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="N124" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="M124" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>603</v>
-      </c>
       <c r="O124" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>82</v>
@@ -17041,7 +17025,7 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17056,7 +17040,7 @@
         <v>102</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="AL124" t="s" s="2">
         <v>108</v>
@@ -17065,7 +17049,7 @@
         <v>82</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>82</v>
@@ -17073,10 +17057,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17099,17 +17083,17 @@
         <v>82</v>
       </c>
       <c r="K125" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="L125" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>82</v>
@@ -17158,7 +17142,7 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17173,7 +17157,7 @@
         <v>102</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="AL125" t="s" s="2">
         <v>108</v>
@@ -17182,7 +17166,7 @@
         <v>82</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>82</v>
@@ -17190,10 +17174,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17219,14 +17203,14 @@
         <v>170</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>82</v>
@@ -17254,10 +17238,10 @@
         <v>264</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>82</v>
@@ -17275,7 +17259,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17290,7 +17274,7 @@
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>108</v>
@@ -17299,7 +17283,7 @@
         <v>82</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>82</v>
@@ -17307,10 +17291,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17336,14 +17320,14 @@
         <v>303</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>82</v>
@@ -17392,7 +17376,7 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17401,13 +17385,13 @@
         <v>90</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>108</v>
@@ -17416,7 +17400,7 @@
         <v>82</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>82</v>
@@ -17424,10 +17408,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17453,10 +17437,10 @@
         <v>296</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -17507,7 +17491,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -17522,7 +17506,7 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>108</v>
@@ -17539,10 +17523,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17565,19 +17549,19 @@
         <v>82</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="N129" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="M129" t="s" s="2">
+      <c r="O129" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>82</v>
@@ -17626,7 +17610,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -17641,10 +17625,10 @@
         <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>82</v>
@@ -17658,10 +17642,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17773,10 +17757,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17890,14 +17874,14 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -17919,10 +17903,10 @@
         <v>111</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="N132" t="s" s="2">
         <v>114</v>
@@ -17977,7 +17961,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18009,10 +17993,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18038,16 +18022,16 @@
         <v>270</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="N133" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="M133" t="s" s="2">
+      <c r="O133" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>82</v>
@@ -18096,7 +18080,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>90</v>
@@ -18111,16 +18095,16 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AL133" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AM133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN133" t="s" s="2">
         <v>641</v>
-      </c>
-      <c r="AL133" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="AM133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN133" t="s" s="2">
-        <v>643</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>82</v>
@@ -18128,10 +18112,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18154,19 +18138,19 @@
         <v>82</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="N134" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="O134" t="s" s="2">
         <v>646</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>82</v>
@@ -18215,7 +18199,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18230,16 +18214,16 @@
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN134" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="AL134" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="AM134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN134" t="s" s="2">
-        <v>651</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>82</v>
@@ -18247,14 +18231,14 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
@@ -18273,16 +18257,16 @@
         <v>82</v>
       </c>
       <c r="K135" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="L135" t="s" s="2">
+      <c r="N135" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -18332,7 +18316,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18347,7 +18331,7 @@
         <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>108</v>
@@ -18356,7 +18340,7 @@
         <v>82</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>82</v>
@@ -18364,10 +18348,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18390,19 +18374,19 @@
         <v>91</v>
       </c>
       <c r="K136" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>661</v>
       </c>
-      <c r="L136" t="s" s="2">
+      <c r="N136" t="s" s="2">
         <v>662</v>
       </c>
-      <c r="M136" t="s" s="2">
+      <c r="O136" t="s" s="2">
         <v>663</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>665</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>82</v>
@@ -18451,7 +18435,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -18466,10 +18450,10 @@
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>82</v>
@@ -18483,10 +18467,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18509,19 +18493,19 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="L137" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="M137" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="N137" t="s" s="2">
         <v>668</v>
       </c>
-      <c r="M137" t="s" s="2">
+      <c r="O137" t="s" s="2">
         <v>669</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>671</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>82</v>
@@ -18570,7 +18554,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -18585,7 +18569,7 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>108</v>
@@ -18602,10 +18586,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18717,10 +18701,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18834,14 +18818,14 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -18863,10 +18847,10 @@
         <v>111</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="N140" t="s" s="2">
         <v>114</v>
@@ -18921,7 +18905,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -18953,10 +18937,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18979,16 +18963,16 @@
         <v>91</v>
       </c>
       <c r="K141" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="L141" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>677</v>
       </c>
-      <c r="L141" t="s" s="2">
+      <c r="N141" t="s" s="2">
         <v>678</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>680</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -19038,7 +19022,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>90</v>
@@ -19062,7 +19046,7 @@
         <v>82</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>82</v>
@@ -19070,10 +19054,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19099,10 +19083,10 @@
         <v>170</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -19132,10 +19116,10 @@
         <v>264</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>82</v>
@@ -19153,7 +19137,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>90</v>
@@ -19168,7 +19152,7 @@
         <v>102</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>108</v>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:47:59+00:00</t>
+    <t>2025-02-19T13:52:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:52:01+00:00</t>
+    <t>2025-02-19T13:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5308" uniqueCount="685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5308" uniqueCount="684">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:53:58+00:00</t>
+    <t>2025-02-19T13:58:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -665,7 +665,9 @@
     <t>Reliabilility of the identity | Fiabilité de l'identité</t>
   </si>
   <si>
-    <t>Reliabilility of the patient's identity | Précision sur le degré de fiabilité de l'identité du patient (si provisoire, validé... avec la justification : quelle type de pièce d'identité ?) avec la méthode de collection</t>
+    <t>Précision sur le degré de fiabilité de l'identité du patient (si provisoire, validé... avec la justification : quelle type de pièce d'identité ?) accompagné de la méthode de collection.
++Reliabilility of the patient's identity</t>
   </si>
   <si>
     <t>Patient.extension:deathPlace</t>
@@ -681,7 +683,9 @@
     <t>FR Core Patient Death Place Extension</t>
   </si>
   <si>
-    <t>Carries the death place of the patient |Précise le lieu de décès du patient (hôpital, sur la voie publique, au domicile, etc.).</t>
+    <t>Précise le lieu de décès du patient (hôpital, sur la voie publique, au domicile, etc.).
++Carries the death place of the patient</t>
   </si>
   <si>
     <t>Patient.extension:birthdateUpdateIndicator</t>
@@ -1794,10 +1798,12 @@
 </t>
   </si>
   <si>
-    <t>Contact identifier in the patient resource | Identifiant de contact dans la ressource Patient</t>
-  </si>
-  <si>
-    <t>This extension carries the contact identifier in the patient resource | Ajout d'un identifiant de contact dans la ressource Patient</t>
+    <t>FR Core Patient Contact Identifier Extension</t>
+  </si>
+  <si>
+    <t>Identifiant de contact dans la ressource Patient
++This extension carries the contact identifier in the patient resource</t>
   </si>
   <si>
     <t>Patient.contact.extension:comment</t>
@@ -1813,7 +1819,8 @@
     <t>Comment on a dataElement | Commentaire sur un dataElement</t>
   </si>
   <si>
-    <t>add a comment on a dataElement  of a resource | Ajout d'un commentaire sur un dataElement d'une ressource</t>
+    <t>Ajout d'un commentaire sur un dataElement d'une ressource.
+Add a comment on a dataElement  of a resource</t>
   </si>
   <si>
     <t>Patient.contact.modifierExtension</t>
@@ -1849,10 +1856,6 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:coding.system}
-</t>
   </si>
   <si>
     <t>code</t>
@@ -16545,7 +16548,7 @@
         <v>82</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>582</v>
+        <v>142</v>
       </c>
       <c r="AC120" s="2"/>
       <c r="AD120" t="s" s="2">
@@ -16570,7 +16573,7 @@
         <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AL120" t="s" s="2">
         <v>108</v>
@@ -16579,7 +16582,7 @@
         <v>82</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>82</v>
@@ -16587,13 +16590,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>576</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>82</v>
@@ -16618,7 +16621,7 @@
         <v>270</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="M121" t="s" s="2">
         <v>578</v>
@@ -16654,7 +16657,7 @@
       </c>
       <c r="Y121" s="2"/>
       <c r="Z121" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>82</v>
@@ -16687,7 +16690,7 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>108</v>
@@ -16696,7 +16699,7 @@
         <v>82</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>82</v>
@@ -16704,13 +16707,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>576</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>82</v>
@@ -16735,7 +16738,7 @@
         <v>270</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="M122" t="s" s="2">
         <v>578</v>
@@ -16771,7 +16774,7 @@
       </c>
       <c r="Y122" s="2"/>
       <c r="Z122" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>82</v>
@@ -16804,7 +16807,7 @@
         <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>108</v>
@@ -16813,7 +16816,7 @@
         <v>82</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>82</v>
@@ -16821,10 +16824,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16850,14 +16853,14 @@
         <v>386</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>82</v>
@@ -16906,7 +16909,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -16930,7 +16933,7 @@
         <v>82</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>82</v>
@@ -16938,10 +16941,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16967,13 +16970,13 @@
         <v>483</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="M124" t="s" s="2">
+      <c r="N124" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="O124" t="s" s="2">
         <v>487</v>
@@ -17025,7 +17028,7 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17049,7 +17052,7 @@
         <v>82</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>82</v>
@@ -17057,10 +17060,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17083,17 +17086,17 @@
         <v>82</v>
       </c>
       <c r="K125" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="L125" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="L125" t="s" s="2">
+      <c r="M125" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>82</v>
@@ -17142,7 +17145,7 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17166,7 +17169,7 @@
         <v>82</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>82</v>
@@ -17174,10 +17177,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17206,11 +17209,11 @@
         <v>492</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>82</v>
@@ -17259,7 +17262,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17283,7 +17286,7 @@
         <v>82</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>82</v>
@@ -17291,10 +17294,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17320,14 +17323,14 @@
         <v>303</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>82</v>
@@ -17376,7 +17379,7 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17385,13 +17388,13 @@
         <v>90</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>108</v>
@@ -17400,7 +17403,7 @@
         <v>82</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>82</v>
@@ -17408,10 +17411,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17437,10 +17440,10 @@
         <v>296</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>622</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -17491,7 +17494,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -17506,7 +17509,7 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>108</v>
@@ -17523,10 +17526,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17552,16 +17555,16 @@
         <v>552</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="M129" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="M129" t="s" s="2">
+      <c r="N129" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="N129" t="s" s="2">
+      <c r="O129" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>628</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>82</v>
@@ -17610,7 +17613,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -17625,10 +17628,10 @@
         <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AL129" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="AL129" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>82</v>
@@ -17642,10 +17645,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17757,10 +17760,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17874,10 +17877,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17993,10 +17996,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18022,16 +18025,16 @@
         <v>270</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="M133" t="s" s="2">
+      <c r="N133" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="N133" t="s" s="2">
+      <c r="O133" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>82</v>
@@ -18080,7 +18083,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>90</v>
@@ -18095,16 +18098,16 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AL133" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="AL133" t="s" s="2">
+      <c r="AM133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN133" t="s" s="2">
         <v>640</v>
-      </c>
-      <c r="AM133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN133" t="s" s="2">
-        <v>641</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>82</v>
@@ -18112,10 +18115,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18141,16 +18144,16 @@
         <v>377</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="N134" t="s" s="2">
+      <c r="O134" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>82</v>
@@ -18199,7 +18202,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18214,16 +18217,16 @@
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AL134" t="s" s="2">
         <v>647</v>
       </c>
-      <c r="AL134" t="s" s="2">
+      <c r="AM134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN134" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="AM134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN134" t="s" s="2">
-        <v>649</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>82</v>
@@ -18231,14 +18234,14 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
@@ -18257,16 +18260,16 @@
         <v>82</v>
       </c>
       <c r="K135" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="L135" t="s" s="2">
         <v>652</v>
       </c>
-      <c r="L135" t="s" s="2">
+      <c r="M135" t="s" s="2">
         <v>653</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="N135" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>655</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -18316,7 +18319,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18331,7 +18334,7 @@
         <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>108</v>
@@ -18340,7 +18343,7 @@
         <v>82</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>82</v>
@@ -18348,10 +18351,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18374,19 +18377,19 @@
         <v>91</v>
       </c>
       <c r="K136" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="L136" t="s" s="2">
         <v>659</v>
       </c>
-      <c r="L136" t="s" s="2">
+      <c r="M136" t="s" s="2">
         <v>660</v>
       </c>
-      <c r="M136" t="s" s="2">
+      <c r="N136" t="s" s="2">
         <v>661</v>
       </c>
-      <c r="N136" t="s" s="2">
+      <c r="O136" t="s" s="2">
         <v>662</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>663</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>82</v>
@@ -18435,7 +18438,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -18450,10 +18453,10 @@
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>82</v>
@@ -18467,10 +18470,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18496,16 +18499,16 @@
         <v>552</v>
       </c>
       <c r="L137" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="M137" t="s" s="2">
         <v>666</v>
       </c>
-      <c r="M137" t="s" s="2">
+      <c r="N137" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="N137" t="s" s="2">
+      <c r="O137" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>82</v>
@@ -18554,7 +18557,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -18569,7 +18572,7 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>108</v>
@@ -18586,10 +18589,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18701,10 +18704,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18818,10 +18821,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18937,10 +18940,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18963,16 +18966,16 @@
         <v>91</v>
       </c>
       <c r="K141" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="L141" t="s" s="2">
         <v>675</v>
       </c>
-      <c r="L141" t="s" s="2">
+      <c r="M141" t="s" s="2">
         <v>676</v>
       </c>
-      <c r="M141" t="s" s="2">
+      <c r="N141" t="s" s="2">
         <v>677</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>678</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -19022,7 +19025,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>90</v>
@@ -19046,7 +19049,7 @@
         <v>82</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>82</v>
@@ -19054,10 +19057,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19083,10 +19086,10 @@
         <v>170</v>
       </c>
       <c r="L142" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="M142" t="s" s="2">
         <v>681</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>682</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -19116,11 +19119,11 @@
         <v>264</v>
       </c>
       <c r="Y142" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="Z142" t="s" s="2">
         <v>682</v>
       </c>
-      <c r="Z142" t="s" s="2">
-        <v>683</v>
-      </c>
       <c r="AA142" t="s" s="2">
         <v>82</v>
       </c>
@@ -19137,7 +19140,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>90</v>
@@ -19152,7 +19155,7 @@
         <v>102</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>108</v>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:58:46+00:00</t>
+    <t>2025-02-19T14:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T14:07:54+00:00</t>
+    <t>2025-02-19T14:26:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:11:18+00:00</t>
+    <t>2025-05-20T13:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:29:42+00:00</t>
+    <t>2025-05-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5345" uniqueCount="689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5345" uniqueCount="690">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:48:39+00:00</t>
+    <t>2025-06-04T13:32:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -701,13 +701,16 @@
     <t>FR Core Patient Birthdate Update Indicator Extension</t>
   </si>
   <si>
+    <t>Indicateur booléen de mise à jour de la date de naissance</t>
+  </si>
+  <si>
     <t>Patient.extension:birthPlace</t>
   </si>
   <si>
     <t>birthPlace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {patient-birthPlace}
+    <t xml:space="preserve">Extension {patient-birthPlace|5.2.0}
 </t>
   </si>
   <si>
@@ -1832,7 +1835,7 @@
 </t>
   </si>
   <si>
-    <t>Comment on a dataElement | Commentaire sur un dataElement</t>
+    <t>Comment on element Patient.contact | Commentaire sur l'élément Patient.contact</t>
   </si>
   <si>
     <t>Ajout d'un commentaire sur un dataElement d'une ressource.
@@ -5035,7 +5038,7 @@
         <v>217</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5118,13 +5121,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>194</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>82</v>
@@ -5146,13 +5149,13 @@
         <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5235,10 +5238,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5350,10 +5353,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5465,10 +5468,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5494,13 +5497,13 @@
         <v>132</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5508,7 +5511,7 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>82</v>
@@ -5550,7 +5553,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>90</v>
@@ -5582,10 +5585,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5608,13 +5611,13 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5665,7 +5668,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5674,7 +5677,7 @@
         <v>90</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>102</v>
@@ -5697,13 +5700,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>194</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>82</v>
@@ -5725,13 +5728,13 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5814,10 +5817,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5843,16 +5846,16 @@
         <v>111</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5901,7 +5904,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5933,10 +5936,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5959,17 +5962,17 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -6006,10 +6009,10 @@
         <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>82</v>
@@ -6018,7 +6021,7 @@
         <v>117</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6033,16 +6036,16 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -6050,10 +6053,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6165,10 +6168,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6282,10 +6285,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6311,16 +6314,16 @@
         <v>170</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6345,13 +6348,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -6369,7 +6372,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6384,7 +6387,7 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>82</v>
@@ -6401,10 +6404,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6427,19 +6430,19 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6468,7 +6471,7 @@
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6486,7 +6489,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6501,7 +6504,7 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>82</v>
@@ -6510,7 +6513,7 @@
         <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6518,10 +6521,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6547,16 +6550,16 @@
         <v>132</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6569,7 +6572,7 @@
         <v>82</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>82</v>
@@ -6605,7 +6608,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6620,7 +6623,7 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>82</v>
@@ -6629,7 +6632,7 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6637,10 +6640,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6666,13 +6669,13 @@
         <v>104</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6686,7 +6689,7 @@
         <v>82</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>82</v>
@@ -6722,7 +6725,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6737,7 +6740,7 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>82</v>
@@ -6746,7 +6749,7 @@
         <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6754,10 +6757,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6780,13 +6783,13 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6837,7 +6840,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6852,7 +6855,7 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>82</v>
@@ -6861,7 +6864,7 @@
         <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6869,10 +6872,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6895,16 +6898,16 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6954,7 +6957,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6969,7 +6972,7 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>82</v>
@@ -6978,7 +6981,7 @@
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6986,13 +6989,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>82</v>
@@ -7014,17 +7017,17 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -7073,7 +7076,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7088,16 +7091,16 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7105,10 +7108,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7220,10 +7223,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7337,10 +7340,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7366,16 +7369,16 @@
         <v>170</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7385,7 +7388,7 @@
         <v>82</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>82</v>
@@ -7400,13 +7403,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7424,7 +7427,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7439,7 +7442,7 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>82</v>
@@ -7456,10 +7459,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7482,19 +7485,19 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7504,7 +7507,7 @@
         <v>82</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>82</v>
@@ -7523,7 +7526,7 @@
       </c>
       <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7541,7 +7544,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7556,7 +7559,7 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>82</v>
@@ -7565,7 +7568,7 @@
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7573,10 +7576,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7602,16 +7605,16 @@
         <v>132</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7621,10 +7624,10 @@
         <v>82</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>82</v>
@@ -7660,7 +7663,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7675,7 +7678,7 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>82</v>
@@ -7684,7 +7687,7 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7692,10 +7695,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7721,13 +7724,13 @@
         <v>104</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7741,7 +7744,7 @@
         <v>82</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>82</v>
@@ -7777,7 +7780,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7792,7 +7795,7 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>82</v>
@@ -7801,7 +7804,7 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7809,10 +7812,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7835,13 +7838,13 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7892,7 +7895,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7907,7 +7910,7 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>82</v>
@@ -7916,7 +7919,7 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7924,10 +7927,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7950,16 +7953,16 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8009,7 +8012,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8024,7 +8027,7 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>82</v>
@@ -8033,7 +8036,7 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8041,13 +8044,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>82</v>
@@ -8069,17 +8072,17 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -8128,7 +8131,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8143,16 +8146,16 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8160,10 +8163,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8275,10 +8278,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8392,10 +8395,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8421,16 +8424,16 @@
         <v>170</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8440,7 +8443,7 @@
         <v>82</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>82</v>
@@ -8455,13 +8458,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8479,7 +8482,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8494,7 +8497,7 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>82</v>
@@ -8511,10 +8514,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8537,19 +8540,19 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8559,7 +8562,7 @@
         <v>82</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>82</v>
@@ -8578,7 +8581,7 @@
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8596,7 +8599,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8611,7 +8614,7 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
@@ -8620,7 +8623,7 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8628,10 +8631,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8657,16 +8660,16 @@
         <v>132</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8676,10 +8679,10 @@
         <v>82</v>
       </c>
       <c r="S53" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>82</v>
@@ -8715,7 +8718,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8730,7 +8733,7 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
@@ -8739,7 +8742,7 @@
         <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8747,10 +8750,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8776,13 +8779,13 @@
         <v>104</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8796,7 +8799,7 @@
         <v>82</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>82</v>
@@ -8832,7 +8835,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8847,7 +8850,7 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>82</v>
@@ -8856,7 +8859,7 @@
         <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8864,10 +8867,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8890,13 +8893,13 @@
         <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8947,7 +8950,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8962,7 +8965,7 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>82</v>
@@ -8971,7 +8974,7 @@
         <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8979,10 +8982,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9005,16 +9008,16 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9064,7 +9067,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9079,7 +9082,7 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>82</v>
@@ -9088,7 +9091,7 @@
         <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -9096,13 +9099,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>82</v>
@@ -9124,17 +9127,17 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9183,7 +9186,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9198,16 +9201,16 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9215,10 +9218,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9330,10 +9333,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9447,10 +9450,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9476,16 +9479,16 @@
         <v>170</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9495,7 +9498,7 @@
         <v>82</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>82</v>
@@ -9510,13 +9513,13 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9534,7 +9537,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9549,7 +9552,7 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
@@ -9566,10 +9569,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9592,19 +9595,19 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9614,7 +9617,7 @@
         <v>82</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>82</v>
@@ -9633,7 +9636,7 @@
       </c>
       <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9651,7 +9654,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9666,7 +9669,7 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
@@ -9675,7 +9678,7 @@
         <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9683,10 +9686,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9712,16 +9715,16 @@
         <v>132</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9731,10 +9734,10 @@
         <v>82</v>
       </c>
       <c r="S62" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="T62" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="U62" t="s" s="2">
         <v>82</v>
@@ -9770,7 +9773,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9785,7 +9788,7 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
@@ -9794,7 +9797,7 @@
         <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9802,10 +9805,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9831,13 +9834,13 @@
         <v>104</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9851,7 +9854,7 @@
         <v>82</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>82</v>
@@ -9887,7 +9890,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9902,7 +9905,7 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>82</v>
@@ -9911,7 +9914,7 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9919,10 +9922,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9945,13 +9948,13 @@
         <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10002,7 +10005,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10017,7 +10020,7 @@
         <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>82</v>
@@ -10026,7 +10029,7 @@
         <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10034,10 +10037,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10060,16 +10063,16 @@
         <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10119,7 +10122,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10134,7 +10137,7 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>82</v>
@@ -10143,7 +10146,7 @@
         <v>82</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10151,13 +10154,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>82</v>
@@ -10179,17 +10182,17 @@
         <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10238,7 +10241,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10253,16 +10256,16 @@
         <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10270,10 +10273,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10385,10 +10388,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10502,10 +10505,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10531,16 +10534,16 @@
         <v>170</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10550,7 +10553,7 @@
         <v>82</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>82</v>
@@ -10565,13 +10568,13 @@
         <v>82</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10589,7 +10592,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10604,7 +10607,7 @@
         <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>82</v>
@@ -10621,10 +10624,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10647,19 +10650,19 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10669,7 +10672,7 @@
         <v>82</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>82</v>
@@ -10688,7 +10691,7 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10706,7 +10709,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10721,7 +10724,7 @@
         <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>82</v>
@@ -10730,7 +10733,7 @@
         <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10738,10 +10741,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10767,16 +10770,16 @@
         <v>132</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -10789,7 +10792,7 @@
         <v>82</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>82</v>
@@ -10825,7 +10828,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10840,7 +10843,7 @@
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>82</v>
@@ -10849,7 +10852,7 @@
         <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -10857,10 +10860,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10886,13 +10889,13 @@
         <v>104</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10906,7 +10909,7 @@
         <v>82</v>
       </c>
       <c r="T72" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="U72" t="s" s="2">
         <v>82</v>
@@ -10942,7 +10945,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10957,7 +10960,7 @@
         <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>82</v>
@@ -10966,7 +10969,7 @@
         <v>82</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -10974,10 +10977,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11000,13 +11003,13 @@
         <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11057,7 +11060,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11072,7 +11075,7 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>82</v>
@@ -11081,7 +11084,7 @@
         <v>82</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11089,10 +11092,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11115,16 +11118,16 @@
         <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11174,7 +11177,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11189,7 +11192,7 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>82</v>
@@ -11198,7 +11201,7 @@
         <v>82</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11206,13 +11209,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>82</v>
@@ -11234,17 +11237,17 @@
         <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11293,7 +11296,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11308,16 +11311,16 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11325,10 +11328,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11440,10 +11443,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11557,10 +11560,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11586,16 +11589,16 @@
         <v>170</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11605,7 +11608,7 @@
         <v>82</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>82</v>
@@ -11620,13 +11623,13 @@
         <v>82</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>82</v>
@@ -11644,7 +11647,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11659,7 +11662,7 @@
         <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>82</v>
@@ -11676,10 +11679,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11702,19 +11705,19 @@
         <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11724,7 +11727,7 @@
         <v>82</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>82</v>
@@ -11743,7 +11746,7 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
@@ -11761,7 +11764,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11776,7 +11779,7 @@
         <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>82</v>
@@ -11785,7 +11788,7 @@
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -11793,10 +11796,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11822,16 +11825,16 @@
         <v>132</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -11844,7 +11847,7 @@
         <v>82</v>
       </c>
       <c r="T80" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="U80" t="s" s="2">
         <v>82</v>
@@ -11880,7 +11883,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11895,7 +11898,7 @@
         <v>102</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>82</v>
@@ -11904,7 +11907,7 @@
         <v>82</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -11912,10 +11915,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11941,13 +11944,13 @@
         <v>104</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11961,7 +11964,7 @@
         <v>82</v>
       </c>
       <c r="T81" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="U81" t="s" s="2">
         <v>82</v>
@@ -11997,7 +12000,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12012,7 +12015,7 @@
         <v>102</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>82</v>
@@ -12021,7 +12024,7 @@
         <v>82</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12029,10 +12032,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12055,13 +12058,13 @@
         <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12112,7 +12115,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12127,7 +12130,7 @@
         <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>82</v>
@@ -12136,7 +12139,7 @@
         <v>82</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12144,10 +12147,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12170,16 +12173,16 @@
         <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12229,7 +12232,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12244,7 +12247,7 @@
         <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>82</v>
@@ -12253,7 +12256,7 @@
         <v>82</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12261,10 +12264,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12287,70 +12290,70 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="P84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q84" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="R84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF84" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="P84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q84" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="R84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12365,13 +12368,13 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
@@ -12382,10 +12385,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12408,19 +12411,19 @@
         <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12457,7 +12460,7 @@
         <v>82</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AC85" s="2"/>
       <c r="AD85" t="s" s="2">
@@ -12467,7 +12470,7 @@
         <v>117</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12482,16 +12485,16 @@
         <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12499,13 +12502,13 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>82</v>
@@ -12527,19 +12530,19 @@
         <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12588,7 +12591,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12603,16 +12606,16 @@
         <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12620,10 +12623,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12735,10 +12738,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12852,10 +12855,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12881,16 +12884,16 @@
         <v>170</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -12900,7 +12903,7 @@
         <v>82</v>
       </c>
       <c r="S89" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="T89" t="s" s="2">
         <v>82</v>
@@ -12915,13 +12918,13 @@
         <v>82</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -12939,7 +12942,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12954,7 +12957,7 @@
         <v>102</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>82</v>
@@ -12963,7 +12966,7 @@
         <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -12971,10 +12974,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13000,16 +13003,16 @@
         <v>104</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
@@ -13058,7 +13061,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13073,7 +13076,7 @@
         <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>82</v>
@@ -13082,7 +13085,7 @@
         <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13090,14 +13093,14 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13119,13 +13122,13 @@
         <v>104</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13175,7 +13178,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13190,7 +13193,7 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>82</v>
@@ -13199,7 +13202,7 @@
         <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13207,14 +13210,14 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13236,13 +13239,13 @@
         <v>104</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13292,7 +13295,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13307,7 +13310,7 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>82</v>
@@ -13316,7 +13319,7 @@
         <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13324,10 +13327,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13353,10 +13356,10 @@
         <v>104</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13407,7 +13410,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13422,7 +13425,7 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>82</v>
@@ -13431,7 +13434,7 @@
         <v>82</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13439,10 +13442,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13468,10 +13471,10 @@
         <v>104</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13522,7 +13525,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13537,7 +13540,7 @@
         <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>82</v>
@@ -13546,7 +13549,7 @@
         <v>82</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13554,10 +13557,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13580,17 +13583,17 @@
         <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13639,7 +13642,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13654,7 +13657,7 @@
         <v>102</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>82</v>
@@ -13663,7 +13666,7 @@
         <v>82</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13671,13 +13674,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>82</v>
@@ -13699,19 +13702,19 @@
         <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -13760,7 +13763,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13775,16 +13778,16 @@
         <v>102</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -13792,10 +13795,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13907,10 +13910,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14024,13 +14027,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>82</v>
@@ -14052,13 +14055,13 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14141,10 +14144,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14170,16 +14173,16 @@
         <v>170</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14189,7 +14192,7 @@
         <v>82</v>
       </c>
       <c r="S100" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="T100" t="s" s="2">
         <v>82</v>
@@ -14204,13 +14207,13 @@
         <v>82</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>82</v>
@@ -14228,7 +14231,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14243,7 +14246,7 @@
         <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>82</v>
@@ -14252,7 +14255,7 @@
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14260,10 +14263,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14289,16 +14292,16 @@
         <v>104</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14347,7 +14350,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14362,7 +14365,7 @@
         <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>82</v>
@@ -14371,7 +14374,7 @@
         <v>82</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14379,14 +14382,14 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -14408,13 +14411,13 @@
         <v>104</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14464,7 +14467,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14479,7 +14482,7 @@
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>82</v>
@@ -14488,7 +14491,7 @@
         <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14496,14 +14499,14 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -14525,13 +14528,13 @@
         <v>104</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14581,7 +14584,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14596,7 +14599,7 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>82</v>
@@ -14605,7 +14608,7 @@
         <v>82</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14613,10 +14616,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14642,10 +14645,10 @@
         <v>104</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14696,7 +14699,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14711,7 +14714,7 @@
         <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>82</v>
@@ -14720,7 +14723,7 @@
         <v>82</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -14728,10 +14731,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14757,10 +14760,10 @@
         <v>104</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14811,7 +14814,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14826,7 +14829,7 @@
         <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>82</v>
@@ -14835,7 +14838,7 @@
         <v>82</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -14843,10 +14846,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14869,17 +14872,17 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -14928,7 +14931,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14943,7 +14946,7 @@
         <v>102</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>82</v>
@@ -14952,7 +14955,7 @@
         <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -14960,10 +14963,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14986,19 +14989,19 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>82</v>
@@ -15047,7 +15050,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15062,16 +15065,16 @@
         <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15079,10 +15082,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15108,16 +15111,16 @@
         <v>170</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -15142,13 +15145,13 @@
         <v>82</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15166,7 +15169,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15181,16 +15184,16 @@
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15198,10 +15201,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15224,19 +15227,19 @@
         <v>91</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15285,7 +15288,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15300,27 +15303,27 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15343,19 +15346,19 @@
         <v>91</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15404,7 +15407,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15419,7 +15422,7 @@
         <v>102</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>108</v>
@@ -15428,7 +15431,7 @@
         <v>82</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -15436,10 +15439,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15462,19 +15465,19 @@
         <v>91</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15523,7 +15526,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15538,16 +15541,16 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -15555,10 +15558,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15581,17 +15584,17 @@
         <v>82</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -15620,7 +15623,7 @@
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>82</v>
@@ -15638,7 +15641,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -15653,16 +15656,16 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -15670,10 +15673,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15696,19 +15699,19 @@
         <v>82</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>82</v>
@@ -15757,7 +15760,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -15772,7 +15775,7 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>108</v>
@@ -15781,7 +15784,7 @@
         <v>82</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -15789,10 +15792,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15815,19 +15818,19 @@
         <v>82</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>82</v>
@@ -15876,7 +15879,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -15891,7 +15894,7 @@
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>108</v>
@@ -15900,7 +15903,7 @@
         <v>82</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -15908,10 +15911,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15934,19 +15937,19 @@
         <v>82</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -15995,7 +15998,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16007,10 +16010,10 @@
         <v>82</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>108</v>
@@ -16027,10 +16030,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16142,10 +16145,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16255,13 +16258,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="B118" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="B118" t="s" s="2">
-        <v>565</v>
-      </c>
       <c r="C118" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>82</v>
@@ -16283,13 +16286,13 @@
         <v>82</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16372,13 +16375,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>82</v>
@@ -16400,13 +16403,13 @@
         <v>82</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -16489,14 +16492,14 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -16518,16 +16521,16 @@
         <v>111</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
@@ -16576,7 +16579,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -16608,10 +16611,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16634,17 +16637,17 @@
         <v>82</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>82</v>
@@ -16672,10 +16675,10 @@
         <v>152</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>82</v>
@@ -16691,7 +16694,7 @@
         <v>117</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -16706,7 +16709,7 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>108</v>
@@ -16715,7 +16718,7 @@
         <v>82</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>82</v>
@@ -16723,13 +16726,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>82</v>
@@ -16751,17 +16754,17 @@
         <v>82</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>82</v>
@@ -16790,7 +16793,7 @@
       </c>
       <c r="Y122" s="2"/>
       <c r="Z122" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>82</v>
@@ -16808,7 +16811,7 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -16823,7 +16826,7 @@
         <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>108</v>
@@ -16832,7 +16835,7 @@
         <v>82</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>82</v>
@@ -16840,13 +16843,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>82</v>
@@ -16868,17 +16871,17 @@
         <v>82</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>82</v>
@@ -16907,7 +16910,7 @@
       </c>
       <c r="Y123" s="2"/>
       <c r="Z123" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>82</v>
@@ -16925,7 +16928,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -16940,7 +16943,7 @@
         <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>108</v>
@@ -16949,7 +16952,7 @@
         <v>82</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>82</v>
@@ -16957,10 +16960,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16983,17 +16986,17 @@
         <v>82</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>82</v>
@@ -17042,7 +17045,7 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17057,7 +17060,7 @@
         <v>102</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AL124" t="s" s="2">
         <v>108</v>
@@ -17066,7 +17069,7 @@
         <v>82</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>82</v>
@@ -17074,10 +17077,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17100,19 +17103,19 @@
         <v>82</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>82</v>
@@ -17161,7 +17164,7 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17176,7 +17179,7 @@
         <v>102</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AL125" t="s" s="2">
         <v>108</v>
@@ -17185,7 +17188,7 @@
         <v>82</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>82</v>
@@ -17193,10 +17196,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17219,17 +17222,17 @@
         <v>82</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>82</v>
@@ -17278,7 +17281,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17293,7 +17296,7 @@
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>108</v>
@@ -17302,7 +17305,7 @@
         <v>82</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>82</v>
@@ -17310,10 +17313,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17339,14 +17342,14 @@
         <v>170</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>82</v>
@@ -17371,13 +17374,13 @@
         <v>82</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>82</v>
@@ -17395,7 +17398,7 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17410,7 +17413,7 @@
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>108</v>
@@ -17419,7 +17422,7 @@
         <v>82</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>82</v>
@@ -17427,10 +17430,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17453,17 +17456,17 @@
         <v>82</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>82</v>
@@ -17512,7 +17515,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -17521,13 +17524,13 @@
         <v>90</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>108</v>
@@ -17536,7 +17539,7 @@
         <v>82</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>82</v>
@@ -17544,10 +17547,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17570,13 +17573,13 @@
         <v>82</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17627,7 +17630,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -17642,7 +17645,7 @@
         <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>108</v>
@@ -17659,10 +17662,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17685,19 +17688,19 @@
         <v>82</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>82</v>
@@ -17746,7 +17749,7 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -17761,10 +17764,10 @@
         <v>102</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>82</v>
@@ -17778,10 +17781,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17893,10 +17896,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18010,14 +18013,14 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -18039,16 +18042,16 @@
         <v>111</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N133" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>82</v>
@@ -18097,7 +18100,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18129,10 +18132,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18155,19 +18158,19 @@
         <v>82</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>82</v>
@@ -18216,7 +18219,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>90</v>
@@ -18231,16 +18234,16 @@
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>82</v>
@@ -18248,10 +18251,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18274,19 +18277,19 @@
         <v>82</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>82</v>
@@ -18335,7 +18338,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18350,16 +18353,16 @@
         <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>82</v>
@@ -18367,14 +18370,14 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
@@ -18393,16 +18396,16 @@
         <v>82</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -18452,7 +18455,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -18467,7 +18470,7 @@
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>108</v>
@@ -18476,7 +18479,7 @@
         <v>82</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>82</v>
@@ -18484,10 +18487,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18510,19 +18513,19 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>82</v>
@@ -18571,7 +18574,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -18586,10 +18589,10 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>82</v>
@@ -18603,10 +18606,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18629,19 +18632,19 @@
         <v>91</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>82</v>
@@ -18690,7 +18693,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -18705,7 +18708,7 @@
         <v>102</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>108</v>
@@ -18722,10 +18725,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18837,10 +18840,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18954,14 +18957,14 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
@@ -18983,16 +18986,16 @@
         <v>111</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N141" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>82</v>
@@ -19041,7 +19044,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19073,10 +19076,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19099,16 +19102,16 @@
         <v>91</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -19158,7 +19161,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>90</v>
@@ -19173,7 +19176,7 @@
         <v>102</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>108</v>
@@ -19182,7 +19185,7 @@
         <v>82</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>82</v>
@@ -19190,10 +19193,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19219,10 +19222,10 @@
         <v>170</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -19249,13 +19252,13 @@
         <v>82</v>
       </c>
       <c r="X143" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Y143" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="Z143" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>82</v>
@@ -19273,7 +19276,7 @@
         <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>90</v>
@@ -19288,7 +19291,7 @@
         <v>102</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AL143" t="s" s="2">
         <v>108</v>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T13:32:30+00:00</t>
+    <t>2025-06-24T17:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T17:01:22+00:00</t>
+    <t>2025-07-04T12:19:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T12:19:33+00:00</t>
+    <t>2025-07-08T13:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5345" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5344" uniqueCount="692">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-08T13:28:39+00:00</t>
+    <t>2025-07-16T09:34:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -789,7 +789,7 @@
     <t>Rang Gémellaire</t>
   </si>
   <si>
-    <t>Extension crée pour exprimer le rang gémellaire, notamment utle dans le cadre des attestations de droits à l'assurance maladie. Cette extension implemente l'élément PatientMultipleBirth de R5 https://www.hl7.org/fhir/patient-definitions.html#Patient.multipleBirth_x.</t>
+    <t>Extension créée pour exprimer le rang gémellaire, notamment utile dans le cadre des attestations de droits à l'assurance maladie. Cette extension implemente l'élément PatientMultipleBirth de R5 https://www.hl7.org/fhir/patient-definitions.html#Patient.multipleBirth_x.</t>
   </si>
   <si>
     <t>Patient.modifierExtension</t>
@@ -815,7 +815,7 @@
 </t>
   </si>
   <si>
-    <t>An identifier for this patient | Identifiant patient. Pour modéliser un patient avec une INS validée, il est nécessaire de respecter la conformité au profil FrCorePatientINS. Les identifiants NIR et NIA ne sont définis uniquement dans le cas du FRCorePatientINS.</t>
+    <t>An identifier for this patient | Identifiant patient. Pour modéliser un patient avec une INS au statut qualifié, il est nécessaire de respecter la conformité au profil FRCorePatientINS. Les identifiants NIR et NIA ne sont définis que dans le cas du FRCorePatientINS.</t>
   </si>
   <si>
     <t>An identifier for this patient.</t>
@@ -828,7 +828,7 @@
 </t>
   </si>
   <si>
-    <t>slicing de l'identifiant Patient sur le type d'identifiant (IPP, INS-NIR, INS-NIA, etc.)</t>
+    <t>Slicing de l'identifiant Patient sur le type d'identifiant (IPP, INS-NIR, INS-NIA, etc.)</t>
   </si>
   <si>
     <t>id</t>
@@ -1151,7 +1151,7 @@
     <t>PI</t>
   </si>
   <si>
-    <t>Hospital assigned patient identifier | IPP</t>
+    <t>Hospital assigned patient identifier | Identifiant Patient Permanent (IPP).</t>
   </si>
   <si>
     <t>Patient.identifier:PI.id</t>
@@ -1163,7 +1163,10 @@
     <t>Patient.identifier:PI.use</t>
   </si>
   <si>
-    <t>usual</t>
+    <t>La valeur old permet d'identifier des IPP désactivés (en cas de fusion d'identité pour résoudre des problèmes de doublonnage par exemple)</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-identifier-use</t>
   </si>
   <si>
     <t>Patient.identifier:PI.type</t>
@@ -1339,6 +1342,9 @@
   </si>
   <si>
     <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
+  </si>
+  <si>
+    <t>usual</t>
   </si>
   <si>
     <t>The use of a human name.</t>
@@ -2531,7 +2537,7 @@
     <col min="26" max="26" width="53.21484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="64.48046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="64.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -10540,7 +10546,7 @@
         <v>267</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>268</v>
+        <v>363</v>
       </c>
       <c r="O69" t="s" s="2">
         <v>269</v>
@@ -10553,7 +10559,7 @@
         <v>82</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>363</v>
+        <v>82</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>82</v>
@@ -10570,11 +10576,9 @@
       <c r="X69" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="Y69" t="s" s="2">
-        <v>271</v>
-      </c>
+      <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>272</v>
+        <v>364</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10624,7 +10628,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>275</v>
@@ -10672,7 +10676,7 @@
         <v>82</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>82</v>
@@ -10741,7 +10745,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>284</v>
@@ -10860,7 +10864,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>293</v>
@@ -10977,7 +10981,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>301</v>
@@ -11092,7 +11096,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>308</v>
@@ -11209,13 +11213,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>252</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>82</v>
@@ -11240,7 +11244,7 @@
         <v>253</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M75" t="s" s="2">
         <v>255</v>
@@ -11328,7 +11332,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>263</v>
@@ -11443,7 +11447,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>264</v>
@@ -11560,7 +11564,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>265</v>
@@ -11679,7 +11683,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>275</v>
@@ -11727,7 +11731,7 @@
         <v>82</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>82</v>
@@ -11796,7 +11800,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>284</v>
@@ -11915,7 +11919,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>293</v>
@@ -12032,7 +12036,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>301</v>
@@ -12147,7 +12151,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>308</v>
@@ -12264,10 +12268,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12290,70 +12294,70 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="P84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q84" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="R84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF84" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="P84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q84" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="R84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12368,13 +12372,13 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
@@ -12385,10 +12389,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12411,19 +12415,19 @@
         <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12460,7 +12464,7 @@
         <v>82</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AC85" s="2"/>
       <c r="AD85" t="s" s="2">
@@ -12470,7 +12474,7 @@
         <v>117</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12485,16 +12489,16 @@
         <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12502,13 +12506,13 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>82</v>
@@ -12530,19 +12534,19 @@
         <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12591,7 +12595,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12606,16 +12610,16 @@
         <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12623,10 +12627,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12738,10 +12742,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12855,10 +12859,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12884,16 +12888,16 @@
         <v>170</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -12903,7 +12907,7 @@
         <v>82</v>
       </c>
       <c r="S89" t="s" s="2">
-        <v>363</v>
+        <v>417</v>
       </c>
       <c r="T89" t="s" s="2">
         <v>82</v>
@@ -12921,10 +12925,10 @@
         <v>270</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -12942,7 +12946,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12957,7 +12961,7 @@
         <v>102</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>82</v>
@@ -12966,7 +12970,7 @@
         <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -12974,10 +12978,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13003,16 +13007,16 @@
         <v>104</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
@@ -13061,7 +13065,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13076,7 +13080,7 @@
         <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>82</v>
@@ -13085,7 +13089,7 @@
         <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13093,14 +13097,14 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13122,13 +13126,13 @@
         <v>104</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13178,7 +13182,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13193,7 +13197,7 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>82</v>
@@ -13202,7 +13206,7 @@
         <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13210,14 +13214,14 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13239,13 +13243,13 @@
         <v>104</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13295,7 +13299,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13310,7 +13314,7 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>82</v>
@@ -13319,7 +13323,7 @@
         <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13327,10 +13331,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13356,10 +13360,10 @@
         <v>104</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13410,7 +13414,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13425,7 +13429,7 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>82</v>
@@ -13434,7 +13438,7 @@
         <v>82</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13442,10 +13446,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13471,10 +13475,10 @@
         <v>104</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13525,7 +13529,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13540,7 +13544,7 @@
         <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>82</v>
@@ -13549,7 +13553,7 @@
         <v>82</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13557,10 +13561,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13586,14 +13590,14 @@
         <v>302</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13642,7 +13646,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13657,7 +13661,7 @@
         <v>102</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>82</v>
@@ -13666,7 +13670,7 @@
         <v>82</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13674,13 +13678,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>82</v>
@@ -13702,19 +13706,19 @@
         <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -13763,7 +13767,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13778,16 +13782,16 @@
         <v>102</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -13795,10 +13799,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13910,10 +13914,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14027,13 +14031,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>82</v>
@@ -14055,13 +14059,13 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14144,10 +14148,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14173,16 +14177,16 @@
         <v>170</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14210,10 +14214,10 @@
         <v>270</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>82</v>
@@ -14231,7 +14235,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14246,7 +14250,7 @@
         <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>82</v>
@@ -14255,7 +14259,7 @@
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14263,10 +14267,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14292,16 +14296,16 @@
         <v>104</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14350,7 +14354,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14365,7 +14369,7 @@
         <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>82</v>
@@ -14374,7 +14378,7 @@
         <v>82</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14382,14 +14386,14 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -14411,13 +14415,13 @@
         <v>104</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14467,7 +14471,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14482,7 +14486,7 @@
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>82</v>
@@ -14491,7 +14495,7 @@
         <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14499,14 +14503,14 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -14528,13 +14532,13 @@
         <v>104</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14584,7 +14588,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14599,7 +14603,7 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>82</v>
@@ -14608,7 +14612,7 @@
         <v>82</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14616,10 +14620,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14645,10 +14649,10 @@
         <v>104</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14699,7 +14703,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14714,7 +14718,7 @@
         <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>82</v>
@@ -14723,7 +14727,7 @@
         <v>82</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -14731,10 +14735,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14760,10 +14764,10 @@
         <v>104</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14814,7 +14818,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14829,7 +14833,7 @@
         <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>82</v>
@@ -14838,7 +14842,7 @@
         <v>82</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -14846,10 +14850,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14875,14 +14879,14 @@
         <v>302</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -14931,7 +14935,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14946,7 +14950,7 @@
         <v>102</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>82</v>
@@ -14955,7 +14959,7 @@
         <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -14963,10 +14967,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14989,19 +14993,19 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>82</v>
@@ -15050,7 +15054,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15065,16 +15069,16 @@
         <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15082,10 +15086,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15111,16 +15115,16 @@
         <v>170</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -15148,10 +15152,10 @@
         <v>270</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15169,7 +15173,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15184,16 +15188,16 @@
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15201,10 +15205,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15227,19 +15231,19 @@
         <v>91</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15288,7 +15292,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15303,27 +15307,27 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15346,19 +15350,19 @@
         <v>91</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15407,7 +15411,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15422,7 +15426,7 @@
         <v>102</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>108</v>
@@ -15431,7 +15435,7 @@
         <v>82</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -15439,10 +15443,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15468,16 +15472,16 @@
         <v>237</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15526,7 +15530,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15541,16 +15545,16 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -15558,10 +15562,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15587,14 +15591,14 @@
         <v>276</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -15623,7 +15627,7 @@
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>82</v>
@@ -15641,7 +15645,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -15656,16 +15660,16 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -15673,10 +15677,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15699,19 +15703,19 @@
         <v>82</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>82</v>
@@ -15760,7 +15764,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -15775,7 +15779,7 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>108</v>
@@ -15784,7 +15788,7 @@
         <v>82</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -15792,10 +15796,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15818,19 +15822,19 @@
         <v>82</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>82</v>
@@ -15879,7 +15883,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -15894,7 +15898,7 @@
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>108</v>
@@ -15903,7 +15907,7 @@
         <v>82</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -15911,10 +15915,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15937,19 +15941,19 @@
         <v>82</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -15998,7 +16002,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16010,10 +16014,10 @@
         <v>82</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>108</v>
@@ -16030,10 +16034,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16145,10 +16149,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16258,13 +16262,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>82</v>
@@ -16286,13 +16290,13 @@
         <v>82</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16375,13 +16379,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>82</v>
@@ -16403,13 +16407,13 @@
         <v>82</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -16492,14 +16496,14 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -16521,10 +16525,10 @@
         <v>111</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>114</v>
@@ -16579,7 +16583,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -16611,10 +16615,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16640,14 +16644,14 @@
         <v>276</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>82</v>
@@ -16675,10 +16679,10 @@
         <v>152</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>82</v>
@@ -16694,7 +16698,7 @@
         <v>117</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -16709,7 +16713,7 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>108</v>
@@ -16718,7 +16722,7 @@
         <v>82</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>82</v>
@@ -16726,13 +16730,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>82</v>
@@ -16757,14 +16761,14 @@
         <v>276</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>82</v>
@@ -16793,7 +16797,7 @@
       </c>
       <c r="Y122" s="2"/>
       <c r="Z122" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>82</v>
@@ -16811,7 +16815,7 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -16826,7 +16830,7 @@
         <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>108</v>
@@ -16835,7 +16839,7 @@
         <v>82</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>82</v>
@@ -16843,13 +16847,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>82</v>
@@ -16874,14 +16878,14 @@
         <v>276</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>82</v>
@@ -16910,7 +16914,7 @@
       </c>
       <c r="Y123" s="2"/>
       <c r="Z123" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>82</v>
@@ -16928,7 +16932,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -16943,7 +16947,7 @@
         <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>108</v>
@@ -16952,7 +16956,7 @@
         <v>82</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>82</v>
@@ -16960,10 +16964,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16986,17 +16990,17 @@
         <v>82</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>82</v>
@@ -17045,7 +17049,7 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17060,7 +17064,7 @@
         <v>102</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AL124" t="s" s="2">
         <v>108</v>
@@ -17069,7 +17073,7 @@
         <v>82</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>82</v>
@@ -17077,10 +17081,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17103,19 +17107,19 @@
         <v>82</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>82</v>
@@ -17164,7 +17168,7 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17179,7 +17183,7 @@
         <v>102</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AL125" t="s" s="2">
         <v>108</v>
@@ -17188,7 +17192,7 @@
         <v>82</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>82</v>
@@ -17196,10 +17200,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17222,17 +17226,17 @@
         <v>82</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>82</v>
@@ -17281,7 +17285,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17296,7 +17300,7 @@
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>108</v>
@@ -17305,7 +17309,7 @@
         <v>82</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>82</v>
@@ -17313,10 +17317,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17342,14 +17346,14 @@
         <v>170</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>82</v>
@@ -17377,10 +17381,10 @@
         <v>270</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>82</v>
@@ -17398,7 +17402,7 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17413,7 +17417,7 @@
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>108</v>
@@ -17422,7 +17426,7 @@
         <v>82</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>82</v>
@@ -17430,10 +17434,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17459,14 +17463,14 @@
         <v>309</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>82</v>
@@ -17515,7 +17519,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -17524,13 +17528,13 @@
         <v>90</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>108</v>
@@ -17539,7 +17543,7 @@
         <v>82</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>82</v>
@@ -17547,10 +17551,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17576,10 +17580,10 @@
         <v>302</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17630,7 +17634,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -17645,7 +17649,7 @@
         <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>108</v>
@@ -17662,10 +17666,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17688,19 +17692,19 @@
         <v>82</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>82</v>
@@ -17749,7 +17753,7 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -17764,10 +17768,10 @@
         <v>102</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>82</v>
@@ -17781,10 +17785,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17896,10 +17900,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18013,14 +18017,14 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -18042,10 +18046,10 @@
         <v>111</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="N133" t="s" s="2">
         <v>114</v>
@@ -18100,7 +18104,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18132,10 +18136,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18161,16 +18165,16 @@
         <v>276</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>82</v>
@@ -18219,7 +18223,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>90</v>
@@ -18234,16 +18238,16 @@
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>82</v>
@@ -18251,10 +18255,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18277,19 +18281,19 @@
         <v>82</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>82</v>
@@ -18338,7 +18342,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18353,16 +18357,16 @@
         <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>82</v>
@@ -18370,14 +18374,14 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
@@ -18396,16 +18400,16 @@
         <v>82</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -18455,7 +18459,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -18470,7 +18474,7 @@
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>108</v>
@@ -18479,7 +18483,7 @@
         <v>82</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>82</v>
@@ -18487,10 +18491,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18513,19 +18517,19 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>82</v>
@@ -18574,7 +18578,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -18589,10 +18593,10 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>82</v>
@@ -18606,10 +18610,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18632,19 +18636,19 @@
         <v>91</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>82</v>
@@ -18693,7 +18697,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -18708,7 +18712,7 @@
         <v>102</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>108</v>
@@ -18725,10 +18729,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18840,10 +18844,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18957,14 +18961,14 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
@@ -18986,10 +18990,10 @@
         <v>111</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="N141" t="s" s="2">
         <v>114</v>
@@ -19044,7 +19048,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19076,10 +19080,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19102,16 +19106,16 @@
         <v>91</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -19161,7 +19165,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>90</v>
@@ -19185,7 +19189,7 @@
         <v>82</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>82</v>
@@ -19193,10 +19197,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19222,10 +19226,10 @@
         <v>170</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -19255,28 +19259,28 @@
         <v>270</v>
       </c>
       <c r="Y143" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="Z143" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="AA143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF143" t="s" s="2">
         <v>687</v>
-      </c>
-      <c r="Z143" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="AA143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF143" t="s" s="2">
-        <v>685</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>90</v>
@@ -19291,7 +19295,7 @@
         <v>102</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="AL143" t="s" s="2">
         <v>108</v>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T09:34:35+00:00</t>
+    <t>2025-07-30T14:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5344" uniqueCount="692">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5344" uniqueCount="691">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T14:55:53+00:00</t>
+    <t>2025-10-08T07:32:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -710,7 +710,7 @@
     <t>birthPlace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {patient-birthPlace|5.2.0}
+    <t xml:space="preserve">Extension {patient-birthPlace|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -766,14 +766,10 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ext-1
-</t>
   </si>
   <si>
     <t>Patient.extension:multipleBirth</t>
@@ -1166,7 +1162,7 @@
     <t>La valeur old permet d'identifier des IPP désactivés (en cas de fusion d'identité pour résoudre des problèmes de doublonnage par exemple)</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-identifier-use</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-identifier-use-pi</t>
   </si>
   <si>
     <t>Patient.identifier:PI.type</t>
@@ -2534,7 +2530,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="53.21484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.48828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="64.65625" customWidth="true" bestFit="true"/>
@@ -5221,7 +5217,7 @@
         <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>82</v>
+        <v>203</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>119</v>
@@ -5270,7 +5266,7 @@
         <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>105</v>
@@ -5336,7 +5332,7 @@
         <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>203</v>
+        <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>82</v>
@@ -5683,7 +5679,7 @@
         <v>90</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>241</v>
+        <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>102</v>
@@ -5706,13 +5702,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>194</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>82</v>
@@ -5734,13 +5730,13 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5823,10 +5819,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5852,16 +5848,16 @@
         <v>111</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5910,7 +5906,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5942,10 +5938,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5968,17 +5964,17 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -6015,10 +6011,10 @@
         <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AC30" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>82</v>
@@ -6027,7 +6023,7 @@
         <v>117</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6042,16 +6038,16 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -6059,10 +6055,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6174,10 +6170,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6291,10 +6287,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6320,16 +6316,16 @@
         <v>170</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6354,31 +6350,31 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="Y33" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="Y33" t="s" s="2">
+      <c r="Z33" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="Z33" t="s" s="2">
+      <c r="AA33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6393,7 +6389,7 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>82</v>
@@ -6410,10 +6406,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6436,19 +6432,19 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6477,25 +6473,25 @@
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6510,7 +6506,7 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>82</v>
@@ -6519,7 +6515,7 @@
         <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6527,10 +6523,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6556,16 +6552,16 @@
         <v>132</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6578,43 +6574,43 @@
         <v>82</v>
       </c>
       <c r="T35" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6629,16 +6625,16 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6646,10 +6642,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6675,13 +6671,13 @@
         <v>104</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6695,43 +6691,43 @@
         <v>82</v>
       </c>
       <c r="T36" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="U36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6746,16 +6742,16 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6763,10 +6759,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6789,13 +6785,13 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6846,7 +6842,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6861,16 +6857,16 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6878,10 +6874,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6904,16 +6900,16 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6963,7 +6959,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6978,16 +6974,16 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6995,13 +6991,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="C39" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>82</v>
@@ -7023,17 +7019,17 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -7082,7 +7078,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7097,16 +7093,16 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7114,10 +7110,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7229,10 +7225,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7346,10 +7342,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7375,16 +7371,16 @@
         <v>170</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7394,7 +7390,7 @@
         <v>82</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>82</v>
@@ -7409,31 +7405,31 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="Y42" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="Y42" t="s" s="2">
+      <c r="Z42" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="Z42" t="s" s="2">
+      <c r="AA42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7448,7 +7444,7 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>82</v>
@@ -7465,10 +7461,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7491,19 +7487,19 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7513,7 +7509,7 @@
         <v>82</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>82</v>
@@ -7532,25 +7528,25 @@
       </c>
       <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7565,7 +7561,7 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>82</v>
@@ -7574,7 +7570,7 @@
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7582,10 +7578,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7611,16 +7607,16 @@
         <v>132</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7630,46 +7626,46 @@
         <v>82</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="T44" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7684,16 +7680,16 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7701,10 +7697,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7730,13 +7726,13 @@
         <v>104</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7750,43 +7746,43 @@
         <v>82</v>
       </c>
       <c r="T45" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7801,16 +7797,16 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7818,10 +7814,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7844,13 +7840,13 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7901,7 +7897,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7916,16 +7912,16 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7933,10 +7929,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7959,16 +7955,16 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8018,7 +8014,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8033,16 +8029,16 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8050,13 +8046,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="C48" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>82</v>
@@ -8078,17 +8074,17 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -8137,7 +8133,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8152,16 +8148,16 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AL48" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AL48" t="s" s="2">
+      <c r="AM48" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AN48" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8169,10 +8165,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8284,10 +8280,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8401,10 +8397,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8430,16 +8426,16 @@
         <v>170</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8449,7 +8445,7 @@
         <v>82</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>82</v>
@@ -8464,31 +8460,31 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="Y51" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="Y51" t="s" s="2">
+      <c r="Z51" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="Z51" t="s" s="2">
+      <c r="AA51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8503,7 +8499,7 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>82</v>
@@ -8520,10 +8516,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8546,19 +8542,19 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8568,7 +8564,7 @@
         <v>82</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>82</v>
@@ -8587,25 +8583,25 @@
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8620,7 +8616,7 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
@@ -8629,7 +8625,7 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8637,10 +8633,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8666,16 +8662,16 @@
         <v>132</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8685,46 +8681,46 @@
         <v>82</v>
       </c>
       <c r="S53" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="T53" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8739,16 +8735,16 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8756,10 +8752,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8785,13 +8781,13 @@
         <v>104</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8805,43 +8801,43 @@
         <v>82</v>
       </c>
       <c r="T54" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF54" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8856,16 +8852,16 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8873,10 +8869,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8899,13 +8895,13 @@
         <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8956,7 +8952,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8971,16 +8967,16 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8988,10 +8984,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9014,16 +9010,16 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9073,7 +9069,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9088,16 +9084,16 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -9105,13 +9101,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="C57" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>82</v>
@@ -9133,17 +9129,17 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9192,7 +9188,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9207,16 +9203,16 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AL57" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AL57" t="s" s="2">
+      <c r="AM57" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AM57" t="s" s="2">
+      <c r="AN57" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9224,10 +9220,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9339,10 +9335,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9456,10 +9452,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9485,16 +9481,16 @@
         <v>170</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9504,7 +9500,7 @@
         <v>82</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>82</v>
@@ -9519,31 +9515,31 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="Y60" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="Y60" t="s" s="2">
+      <c r="Z60" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="Z60" t="s" s="2">
+      <c r="AA60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF60" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9558,7 +9554,7 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
@@ -9575,10 +9571,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9601,19 +9597,19 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9623,7 +9619,7 @@
         <v>82</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>82</v>
@@ -9642,25 +9638,25 @@
       </c>
       <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF61" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9675,7 +9671,7 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
@@ -9684,7 +9680,7 @@
         <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9692,10 +9688,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9721,16 +9717,16 @@
         <v>132</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9740,46 +9736,46 @@
         <v>82</v>
       </c>
       <c r="S62" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="T62" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF62" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9794,16 +9790,16 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9811,10 +9807,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9840,13 +9836,13 @@
         <v>104</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9860,43 +9856,43 @@
         <v>82</v>
       </c>
       <c r="T63" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF63" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9911,16 +9907,16 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9928,10 +9924,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9954,13 +9950,13 @@
         <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10011,7 +10007,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10026,16 +10022,16 @@
         <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10043,10 +10039,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10069,16 +10065,16 @@
         <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10128,7 +10124,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10143,16 +10139,16 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10160,13 +10156,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="C66" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>82</v>
@@ -10188,17 +10184,17 @@
         <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10247,7 +10243,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10262,16 +10258,16 @@
         <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AL66" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AL66" t="s" s="2">
+      <c r="AM66" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AM66" t="s" s="2">
+      <c r="AN66" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10279,10 +10275,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10394,10 +10390,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10511,10 +10507,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10540,16 +10536,16 @@
         <v>170</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M69" t="s" s="2">
-        <v>267</v>
-      </c>
       <c r="N69" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10574,11 +10570,11 @@
         <v>82</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10596,7 +10592,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10611,7 +10607,7 @@
         <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>82</v>
@@ -10628,10 +10624,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10654,19 +10650,19 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10676,7 +10672,7 @@
         <v>82</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>82</v>
@@ -10695,25 +10691,25 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF70" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10728,7 +10724,7 @@
         <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>82</v>
@@ -10737,7 +10733,7 @@
         <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10745,10 +10741,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10774,16 +10770,16 @@
         <v>132</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -10796,43 +10792,43 @@
         <v>82</v>
       </c>
       <c r="T71" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10847,16 +10843,16 @@
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -10864,10 +10860,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10893,13 +10889,13 @@
         <v>104</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10913,43 +10909,43 @@
         <v>82</v>
       </c>
       <c r="T72" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF72" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10964,16 +10960,16 @@
         <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -10981,10 +10977,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11007,13 +11003,13 @@
         <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11064,7 +11060,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11079,16 +11075,16 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN73" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11096,10 +11092,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11122,16 +11118,16 @@
         <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11181,7 +11177,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11196,16 +11192,16 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11213,13 +11209,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="C75" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C75" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>82</v>
@@ -11241,17 +11237,17 @@
         <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11300,7 +11296,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11315,16 +11311,16 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AL75" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AL75" t="s" s="2">
+      <c r="AM75" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AM75" t="s" s="2">
+      <c r="AN75" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11332,10 +11328,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11447,10 +11443,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11564,10 +11560,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11593,16 +11589,16 @@
         <v>170</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11612,7 +11608,7 @@
         <v>82</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>82</v>
@@ -11627,31 +11623,31 @@
         <v>82</v>
       </c>
       <c r="X78" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="Y78" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="Y78" t="s" s="2">
+      <c r="Z78" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="Z78" t="s" s="2">
+      <c r="AA78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF78" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11666,7 +11662,7 @@
         <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>82</v>
@@ -11683,10 +11679,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11709,19 +11705,19 @@
         <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="N79" t="s" s="2">
+      <c r="O79" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11731,7 +11727,7 @@
         <v>82</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>82</v>
@@ -11750,25 +11746,25 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF79" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11783,7 +11779,7 @@
         <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>82</v>
@@ -11792,7 +11788,7 @@
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -11800,10 +11796,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11829,16 +11825,16 @@
         <v>132</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="N80" t="s" s="2">
+      <c r="O80" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -11851,43 +11847,43 @@
         <v>82</v>
       </c>
       <c r="T80" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF80" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11902,16 +11898,16 @@
         <v>102</v>
       </c>
       <c r="AK80" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -11919,10 +11915,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11948,13 +11944,13 @@
         <v>104</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11968,43 +11964,43 @@
         <v>82</v>
       </c>
       <c r="T81" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF81" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12019,16 +12015,16 @@
         <v>102</v>
       </c>
       <c r="AK81" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN81" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12036,10 +12032,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12062,13 +12058,13 @@
         <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12119,7 +12115,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12134,16 +12130,16 @@
         <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12151,10 +12147,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12177,16 +12173,16 @@
         <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12236,7 +12232,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12251,16 +12247,16 @@
         <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12268,10 +12264,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12294,26 +12290,26 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="N84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="O84" t="s" s="2">
+      <c r="P84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q84" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="P84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q84" t="s" s="2">
-        <v>389</v>
-      </c>
       <c r="R84" t="s" s="2">
         <v>82</v>
       </c>
@@ -12357,7 +12353,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12372,13 +12368,13 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
@@ -12389,10 +12385,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12415,19 +12411,19 @@
         <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="L85" t="s" s="2">
+      <c r="M85" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="N85" t="s" s="2">
+      <c r="O85" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12464,7 +12460,7 @@
         <v>82</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AC85" s="2"/>
       <c r="AD85" t="s" s="2">
@@ -12474,7 +12470,7 @@
         <v>117</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12489,16 +12485,16 @@
         <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AL85" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AL85" t="s" s="2">
+      <c r="AM85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12506,13 +12502,13 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="C86" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>82</v>
@@ -12534,19 +12530,19 @@
         <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="M86" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="M86" t="s" s="2">
-        <v>406</v>
-      </c>
       <c r="N86" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="O86" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12595,7 +12591,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12610,16 +12606,16 @@
         <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AL86" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AL86" t="s" s="2">
+      <c r="AM86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12627,10 +12623,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="B87" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12742,10 +12738,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="B88" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12859,10 +12855,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="B89" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12888,16 +12884,16 @@
         <v>170</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="N89" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="N89" t="s" s="2">
+      <c r="O89" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -12907,46 +12903,46 @@
         <v>82</v>
       </c>
       <c r="S89" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="Y89" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="T89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X89" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="Y89" t="s" s="2">
+      <c r="Z89" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="Z89" t="s" s="2">
+      <c r="AA89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF89" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12961,16 +12957,16 @@
         <v>102</v>
       </c>
       <c r="AK89" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN89" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -12978,10 +12974,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="B90" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13007,16 +13003,16 @@
         <v>104</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
@@ -13065,7 +13061,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13080,16 +13076,16 @@
         <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN90" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13097,14 +13093,14 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="B91" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13126,13 +13122,13 @@
         <v>104</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13182,7 +13178,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13197,16 +13193,16 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13214,14 +13210,14 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="B92" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13243,13 +13239,13 @@
         <v>104</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13299,7 +13295,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13314,16 +13310,16 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN92" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="AL92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13331,10 +13327,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B93" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13360,10 +13356,10 @@
         <v>104</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13414,7 +13410,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13429,16 +13425,16 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN93" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AL93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13446,10 +13442,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="B94" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13475,10 +13471,10 @@
         <v>104</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13529,7 +13525,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13544,16 +13540,16 @@
         <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="AL94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13561,10 +13557,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="B95" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13587,17 +13583,17 @@
         <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13646,7 +13642,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13661,16 +13657,16 @@
         <v>102</v>
       </c>
       <c r="AK95" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13678,13 +13674,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="C96" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="C96" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>82</v>
@@ -13706,19 +13702,19 @@
         <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="M96" t="s" s="2">
-        <v>475</v>
-      </c>
       <c r="N96" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="O96" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -13767,7 +13763,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13782,16 +13778,16 @@
         <v>102</v>
       </c>
       <c r="AK96" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AL96" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AL96" t="s" s="2">
+      <c r="AM96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -13799,10 +13795,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13914,10 +13910,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14031,13 +14027,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="C99" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="C99" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>82</v>
@@ -14059,13 +14055,13 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="L99" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="L99" t="s" s="2">
+      <c r="M99" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14148,10 +14144,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14177,16 +14173,16 @@
         <v>170</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="N100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14196,7 +14192,7 @@
         <v>82</v>
       </c>
       <c r="S100" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="T100" t="s" s="2">
         <v>82</v>
@@ -14211,31 +14207,31 @@
         <v>82</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Y100" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="Z100" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="Z100" t="s" s="2">
+      <c r="AA100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF100" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14250,16 +14246,16 @@
         <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN100" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14267,10 +14263,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14296,16 +14292,16 @@
         <v>104</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14354,7 +14350,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14369,16 +14365,16 @@
         <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN101" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AL101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14386,14 +14382,14 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -14415,13 +14411,13 @@
         <v>104</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14471,7 +14467,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14486,16 +14482,16 @@
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN102" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14503,14 +14499,14 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -14532,13 +14528,13 @@
         <v>104</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14588,7 +14584,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14603,16 +14599,16 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN103" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14620,10 +14616,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14649,10 +14645,10 @@
         <v>104</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14703,7 +14699,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14718,16 +14714,16 @@
         <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN104" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AL104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -14735,10 +14731,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14764,10 +14760,10 @@
         <v>104</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14818,7 +14814,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14833,16 +14829,16 @@
         <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN105" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -14850,10 +14846,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14876,17 +14872,17 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -14935,7 +14931,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14950,16 +14946,16 @@
         <v>102</v>
       </c>
       <c r="AK106" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN106" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -14967,10 +14963,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14993,19 +14989,19 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="L107" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="L107" t="s" s="2">
+      <c r="M107" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="N107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>82</v>
@@ -15054,7 +15050,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15069,16 +15065,16 @@
         <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AL107" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="AL107" t="s" s="2">
+      <c r="AM107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN107" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15086,10 +15082,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15115,16 +15111,16 @@
         <v>170</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="M108" t="s" s="2">
+      <c r="N108" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="N108" t="s" s="2">
+      <c r="O108" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -15149,14 +15145,14 @@
         <v>82</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Y108" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="Z108" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="Z108" t="s" s="2">
-        <v>505</v>
-      </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
       </c>
@@ -15173,7 +15169,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15188,16 +15184,16 @@
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AL108" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="AL108" t="s" s="2">
+      <c r="AM108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN108" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15205,10 +15201,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15231,19 +15227,19 @@
         <v>91</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="L109" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="M109" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="M109" t="s" s="2">
+      <c r="N109" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="N109" t="s" s="2">
+      <c r="O109" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15292,7 +15288,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15307,27 +15303,27 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AL109" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="AL109" t="s" s="2">
+      <c r="AM109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN109" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="AM109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN109" t="s" s="2">
+      <c r="AO109" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="AO109" t="s" s="2">
-        <v>518</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15350,19 +15346,19 @@
         <v>91</v>
       </c>
       <c r="K110" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="L110" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="L110" t="s" s="2">
+      <c r="M110" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="N110" t="s" s="2">
+      <c r="O110" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15411,7 +15407,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15426,7 +15422,7 @@
         <v>102</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>108</v>
@@ -15435,7 +15431,7 @@
         <v>82</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -15443,10 +15439,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15472,16 +15468,16 @@
         <v>237</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="M111" t="s" s="2">
+      <c r="N111" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="N111" t="s" s="2">
+      <c r="O111" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15530,7 +15526,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15545,16 +15541,16 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AL111" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="AL111" t="s" s="2">
+      <c r="AM111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN111" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN111" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -15562,10 +15558,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15588,17 +15584,17 @@
         <v>82</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -15627,7 +15623,7 @@
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>82</v>
@@ -15645,7 +15641,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -15660,16 +15656,16 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AL112" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="AL112" t="s" s="2">
+      <c r="AM112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN112" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -15677,10 +15673,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15703,19 +15699,19 @@
         <v>82</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="L113" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="L113" t="s" s="2">
+      <c r="M113" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="N113" t="s" s="2">
+      <c r="O113" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>82</v>
@@ -15764,7 +15760,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -15779,7 +15775,7 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>108</v>
@@ -15788,7 +15784,7 @@
         <v>82</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -15796,10 +15792,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15822,19 +15818,19 @@
         <v>82</v>
       </c>
       <c r="K114" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="L114" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="L114" t="s" s="2">
+      <c r="M114" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="M114" t="s" s="2">
+      <c r="N114" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="N114" t="s" s="2">
+      <c r="O114" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>82</v>
@@ -15883,7 +15879,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -15898,7 +15894,7 @@
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>108</v>
@@ -15907,7 +15903,7 @@
         <v>82</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -15915,10 +15911,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15941,19 +15937,19 @@
         <v>82</v>
       </c>
       <c r="K115" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="L115" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="L115" t="s" s="2">
+      <c r="M115" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="N115" t="s" s="2">
+      <c r="O115" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16002,7 +15998,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16014,10 +16010,10 @@
         <v>82</v>
       </c>
       <c r="AJ115" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AK115" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="AK115" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>108</v>
@@ -16034,10 +16030,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16149,10 +16145,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16262,13 +16258,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="C118" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="C118" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>82</v>
@@ -16290,13 +16286,13 @@
         <v>82</v>
       </c>
       <c r="K118" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="L118" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="L118" t="s" s="2">
+      <c r="M118" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16379,13 +16375,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="C119" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="C119" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>82</v>
@@ -16407,13 +16403,13 @@
         <v>82</v>
       </c>
       <c r="K119" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="L119" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="L119" t="s" s="2">
+      <c r="M119" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>578</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -16496,14 +16492,14 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -16525,16 +16521,16 @@
         <v>111</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
@@ -16583,7 +16579,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -16615,10 +16611,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16641,17 +16637,17 @@
         <v>82</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="M121" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>82</v>
@@ -16679,10 +16675,10 @@
         <v>152</v>
       </c>
       <c r="Y121" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="Z121" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>82</v>
@@ -16698,7 +16694,7 @@
         <v>117</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -16713,7 +16709,7 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>108</v>
@@ -16722,7 +16718,7 @@
         <v>82</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>82</v>
@@ -16730,13 +16726,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="C122" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="C122" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>82</v>
@@ -16758,17 +16754,17 @@
         <v>82</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>82</v>
@@ -16797,7 +16793,7 @@
       </c>
       <c r="Y122" s="2"/>
       <c r="Z122" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>82</v>
@@ -16815,7 +16811,7 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -16830,7 +16826,7 @@
         <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>108</v>
@@ -16839,7 +16835,7 @@
         <v>82</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>82</v>
@@ -16847,13 +16843,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="C123" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="C123" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>82</v>
@@ -16875,17 +16871,17 @@
         <v>82</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>82</v>
@@ -16914,7 +16910,7 @@
       </c>
       <c r="Y123" s="2"/>
       <c r="Z123" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>82</v>
@@ -16932,7 +16928,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -16947,7 +16943,7 @@
         <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>108</v>
@@ -16956,7 +16952,7 @@
         <v>82</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>82</v>
@@ -16964,10 +16960,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16990,17 +16986,17 @@
         <v>82</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>82</v>
@@ -17049,7 +17045,7 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17064,7 +17060,7 @@
         <v>102</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AL124" t="s" s="2">
         <v>108</v>
@@ -17073,7 +17069,7 @@
         <v>82</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>82</v>
@@ -17081,10 +17077,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17107,19 +17103,19 @@
         <v>82</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="M125" t="s" s="2">
+      <c r="N125" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="N125" t="s" s="2">
-        <v>608</v>
-      </c>
       <c r="O125" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>82</v>
@@ -17168,7 +17164,7 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17183,7 +17179,7 @@
         <v>102</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AL125" t="s" s="2">
         <v>108</v>
@@ -17192,7 +17188,7 @@
         <v>82</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>82</v>
@@ -17200,10 +17196,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17226,17 +17222,17 @@
         <v>82</v>
       </c>
       <c r="K126" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="L126" t="s" s="2">
         <v>611</v>
       </c>
-      <c r="L126" t="s" s="2">
+      <c r="M126" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>82</v>
@@ -17285,7 +17281,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17300,7 +17296,7 @@
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>108</v>
@@ -17309,7 +17305,7 @@
         <v>82</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>82</v>
@@ -17317,10 +17313,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17346,14 +17342,14 @@
         <v>170</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>82</v>
@@ -17378,14 +17374,14 @@
         <v>82</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Y127" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="Z127" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="Z127" t="s" s="2">
-        <v>505</v>
-      </c>
       <c r="AA127" t="s" s="2">
         <v>82</v>
       </c>
@@ -17402,7 +17398,7 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17417,7 +17413,7 @@
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>108</v>
@@ -17426,7 +17422,7 @@
         <v>82</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>82</v>
@@ -17434,10 +17430,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17460,17 +17456,17 @@
         <v>82</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>622</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>82</v>
@@ -17519,7 +17515,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -17528,13 +17524,13 @@
         <v>90</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>108</v>
@@ -17543,7 +17539,7 @@
         <v>82</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>82</v>
@@ -17551,10 +17547,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17577,13 +17573,13 @@
         <v>82</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="M129" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17634,7 +17630,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -17649,7 +17645,7 @@
         <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>108</v>
@@ -17666,10 +17662,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17692,19 +17688,19 @@
         <v>82</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="M130" t="s" s="2">
+      <c r="N130" t="s" s="2">
         <v>633</v>
       </c>
-      <c r="N130" t="s" s="2">
+      <c r="O130" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>635</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>82</v>
@@ -17753,7 +17749,7 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -17768,10 +17764,10 @@
         <v>102</v>
       </c>
       <c r="AK130" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AL130" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="AL130" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>82</v>
@@ -17785,10 +17781,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17900,10 +17896,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18017,14 +18013,14 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -18046,16 +18042,16 @@
         <v>111</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="N133" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>82</v>
@@ -18104,7 +18100,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18136,10 +18132,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18162,19 +18158,19 @@
         <v>82</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="N134" t="s" s="2">
+      <c r="O134" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>645</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>82</v>
@@ -18223,7 +18219,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>90</v>
@@ -18238,16 +18234,16 @@
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AL134" t="s" s="2">
         <v>646</v>
       </c>
-      <c r="AL134" t="s" s="2">
+      <c r="AM134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN134" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="AM134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN134" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>82</v>
@@ -18255,10 +18251,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18281,19 +18277,19 @@
         <v>82</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="N135" t="s" s="2">
         <v>651</v>
       </c>
-      <c r="N135" t="s" s="2">
+      <c r="O135" t="s" s="2">
         <v>652</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>653</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>82</v>
@@ -18342,7 +18338,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18357,16 +18353,16 @@
         <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AL135" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="AL135" t="s" s="2">
+      <c r="AM135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN135" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="AM135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN135" t="s" s="2">
-        <v>656</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>82</v>
@@ -18374,14 +18370,14 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
@@ -18400,16 +18396,16 @@
         <v>82</v>
       </c>
       <c r="K136" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="L136" t="s" s="2">
         <v>659</v>
       </c>
-      <c r="L136" t="s" s="2">
+      <c r="M136" t="s" s="2">
         <v>660</v>
       </c>
-      <c r="M136" t="s" s="2">
+      <c r="N136" t="s" s="2">
         <v>661</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>662</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -18459,7 +18455,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -18474,7 +18470,7 @@
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>108</v>
@@ -18483,7 +18479,7 @@
         <v>82</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>82</v>
@@ -18491,10 +18487,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18517,19 +18513,19 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="L137" t="s" s="2">
         <v>666</v>
       </c>
-      <c r="L137" t="s" s="2">
+      <c r="M137" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="M137" t="s" s="2">
+      <c r="N137" t="s" s="2">
         <v>668</v>
       </c>
-      <c r="N137" t="s" s="2">
+      <c r="O137" t="s" s="2">
         <v>669</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>670</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>82</v>
@@ -18578,7 +18574,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -18593,10 +18589,10 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>82</v>
@@ -18610,10 +18606,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18636,19 +18632,19 @@
         <v>91</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="L138" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="M138" t="s" s="2">
         <v>673</v>
       </c>
-      <c r="M138" t="s" s="2">
+      <c r="N138" t="s" s="2">
         <v>674</v>
       </c>
-      <c r="N138" t="s" s="2">
+      <c r="O138" t="s" s="2">
         <v>675</v>
-      </c>
-      <c r="O138" t="s" s="2">
-        <v>676</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>82</v>
@@ -18697,7 +18693,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -18712,7 +18708,7 @@
         <v>102</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>108</v>
@@ -18729,10 +18725,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18844,10 +18840,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18961,14 +18957,14 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
@@ -18990,16 +18986,16 @@
         <v>111</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="N141" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>82</v>
@@ -19048,7 +19044,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19080,10 +19076,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19106,16 +19102,16 @@
         <v>91</v>
       </c>
       <c r="K142" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="L142" t="s" s="2">
         <v>682</v>
       </c>
-      <c r="L142" t="s" s="2">
+      <c r="M142" t="s" s="2">
         <v>683</v>
       </c>
-      <c r="M142" t="s" s="2">
+      <c r="N142" t="s" s="2">
         <v>684</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>685</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -19165,7 +19161,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>90</v>
@@ -19180,7 +19176,7 @@
         <v>102</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>108</v>
@@ -19189,7 +19185,7 @@
         <v>82</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>82</v>
@@ -19197,10 +19193,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19226,10 +19222,10 @@
         <v>170</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>688</v>
-      </c>
-      <c r="M143" t="s" s="2">
-        <v>689</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -19256,14 +19252,14 @@
         <v>82</v>
       </c>
       <c r="X143" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Y143" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="Z143" t="s" s="2">
         <v>689</v>
       </c>
-      <c r="Z143" t="s" s="2">
-        <v>690</v>
-      </c>
       <c r="AA143" t="s" s="2">
         <v>82</v>
       </c>
@@ -19280,7 +19276,7 @@
         <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>90</v>
@@ -19295,7 +19291,7 @@
         <v>102</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="AL143" t="s" s="2">
         <v>108</v>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5344" uniqueCount="691">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5343" uniqueCount="693">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T07:32:57+00:00</t>
+    <t>2025-10-08T12:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1593,10 +1593,10 @@
     <t>Patient.gender</t>
   </si>
   <si>
-    <t>male | female | other | unknown</t>
-  </si>
-  <si>
-    <t>French patient's gender checked with the INSi teleservice | Genre du patient. Dans le cas d'une identité récupérée par le téléservice INSi, les valeurs sont M ou F</t>
+    <t>male | female | unknown</t>
+  </si>
+  <si>
+    <t>French patient's gender checked with the INSi teleservice | Genre administratif du patient. Dans le cas d'une identité récupérée par le téléservice INSi, les valeurs M ou F issues du téléservice sont à adapter à FHIR (male | female | unknown).</t>
   </si>
   <si>
     <t>The gender might not match the biological sex as determined by genetics or the individual's preferred identification. Note that for both humans and particularly animals, there are other legitimate possibilities than male and female, though the vast majority of systems and contexts only support male and female.  Systems providing decision support or enforcing business rules should ideally do this on the basis of Observations dealing with the specific sex or gender aspect of interest (anatomical, chromosomal, social, etc.)  However, because these observations are infrequently recorded, defaulting to the administrative gender is common practice.  Where such defaulting occurs, rule enforcement should allow for the variation between administrative and biological, chromosomal and other gender aspects.  For example, an alert about a hysterectomy on a male should be handled as a warning or overridable error, not a "hard" error.  See the Patient Gender and Sex section for additional information about communicating patient gender and sex.</t>
@@ -1605,10 +1605,7 @@
     <t>Needed for identification of the individual, in combination with (at least) name and birth date.</t>
   </si>
   <si>
-    <t>The gender of a person used for administrative purposes.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.0.1</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-gender</t>
   </si>
   <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/administrativeGender</t>
@@ -1961,10 +1958,19 @@
     <t>Patient.contact.gender</t>
   </si>
   <si>
+    <t>male | female | other | unknown</t>
+  </si>
+  <si>
     <t>Administrative Gender - the gender that the contact person is considered to have for administration and record keeping purposes.</t>
   </si>
   <si>
     <t>Needed to address the person correctly.</t>
+  </si>
+  <si>
+    <t>The gender of a person used for administrative purposes.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.0.1</t>
   </si>
   <si>
     <t>NK1-15</t>
@@ -15147,11 +15153,9 @@
       <c r="X108" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="Y108" t="s" s="2">
+      <c r="Y108" s="2"/>
+      <c r="Z108" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="Z108" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15184,16 +15188,16 @@
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AL108" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="AL108" t="s" s="2">
+      <c r="AM108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN108" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15201,10 +15205,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15227,19 +15231,19 @@
         <v>91</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="L109" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="M109" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="M109" t="s" s="2">
+      <c r="N109" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="N109" t="s" s="2">
+      <c r="O109" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15288,7 +15292,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15303,27 +15307,27 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AL109" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="AL109" t="s" s="2">
+      <c r="AM109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN109" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="AM109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN109" t="s" s="2">
+      <c r="AO109" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="AO109" t="s" s="2">
-        <v>517</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15346,19 +15350,19 @@
         <v>91</v>
       </c>
       <c r="K110" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="L110" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="L110" t="s" s="2">
+      <c r="M110" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="N110" t="s" s="2">
+      <c r="O110" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15407,7 +15411,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15422,7 +15426,7 @@
         <v>102</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>108</v>
@@ -15431,7 +15435,7 @@
         <v>82</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -15439,10 +15443,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15468,16 +15472,16 @@
         <v>237</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="M111" t="s" s="2">
+      <c r="N111" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="N111" t="s" s="2">
+      <c r="O111" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15526,7 +15530,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15541,16 +15545,16 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AL111" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="AL111" t="s" s="2">
+      <c r="AM111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN111" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN111" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -15558,10 +15562,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15587,14 +15591,14 @@
         <v>275</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -15623,7 +15627,7 @@
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>82</v>
@@ -15641,7 +15645,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -15656,16 +15660,16 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AL112" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="AL112" t="s" s="2">
+      <c r="AM112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN112" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -15673,10 +15677,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15699,19 +15703,19 @@
         <v>82</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="L113" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="L113" t="s" s="2">
+      <c r="M113" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="N113" t="s" s="2">
+      <c r="O113" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>82</v>
@@ -15760,7 +15764,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -15775,7 +15779,7 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>108</v>
@@ -15784,7 +15788,7 @@
         <v>82</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -15792,10 +15796,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15818,19 +15822,19 @@
         <v>82</v>
       </c>
       <c r="K114" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="L114" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="L114" t="s" s="2">
+      <c r="M114" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="M114" t="s" s="2">
+      <c r="N114" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="N114" t="s" s="2">
+      <c r="O114" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>82</v>
@@ -15879,7 +15883,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -15894,7 +15898,7 @@
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>108</v>
@@ -15903,7 +15907,7 @@
         <v>82</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -15911,10 +15915,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15937,19 +15941,19 @@
         <v>82</v>
       </c>
       <c r="K115" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="L115" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="L115" t="s" s="2">
+      <c r="M115" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="N115" t="s" s="2">
+      <c r="O115" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -15998,7 +16002,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16010,10 +16014,10 @@
         <v>82</v>
       </c>
       <c r="AJ115" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AK115" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="AK115" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>108</v>
@@ -16030,10 +16034,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16145,10 +16149,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16258,13 +16262,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="C118" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="C118" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>82</v>
@@ -16286,13 +16290,13 @@
         <v>82</v>
       </c>
       <c r="K118" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="L118" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="L118" t="s" s="2">
+      <c r="M118" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16375,13 +16379,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="C119" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="C119" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>82</v>
@@ -16403,13 +16407,13 @@
         <v>82</v>
       </c>
       <c r="K119" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="L119" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="L119" t="s" s="2">
+      <c r="M119" t="s" s="2">
         <v>576</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>577</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -16492,14 +16496,14 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -16521,10 +16525,10 @@
         <v>111</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>114</v>
@@ -16579,7 +16583,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -16611,10 +16615,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16640,14 +16644,14 @@
         <v>275</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="M121" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>82</v>
@@ -16675,10 +16679,10 @@
         <v>152</v>
       </c>
       <c r="Y121" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="Z121" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>82</v>
@@ -16694,7 +16698,7 @@
         <v>117</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -16709,7 +16713,7 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>108</v>
@@ -16718,7 +16722,7 @@
         <v>82</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>82</v>
@@ -16726,13 +16730,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="C122" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="C122" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>82</v>
@@ -16757,14 +16761,14 @@
         <v>275</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>82</v>
@@ -16793,7 +16797,7 @@
       </c>
       <c r="Y122" s="2"/>
       <c r="Z122" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>82</v>
@@ -16811,7 +16815,7 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -16826,7 +16830,7 @@
         <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>108</v>
@@ -16835,7 +16839,7 @@
         <v>82</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>82</v>
@@ -16843,13 +16847,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="C123" t="s" s="2">
         <v>595</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="C123" t="s" s="2">
-        <v>596</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>82</v>
@@ -16874,14 +16878,14 @@
         <v>275</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>82</v>
@@ -16910,7 +16914,7 @@
       </c>
       <c r="Y123" s="2"/>
       <c r="Z123" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>82</v>
@@ -16928,7 +16932,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -16943,7 +16947,7 @@
         <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>108</v>
@@ -16952,7 +16956,7 @@
         <v>82</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>82</v>
@@ -16960,10 +16964,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16989,14 +16993,14 @@
         <v>392</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>82</v>
@@ -17045,7 +17049,7 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17069,7 +17073,7 @@
         <v>82</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>82</v>
@@ -17077,10 +17081,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17106,13 +17110,13 @@
         <v>490</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="M125" t="s" s="2">
+      <c r="N125" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="O125" t="s" s="2">
         <v>494</v>
@@ -17164,7 +17168,7 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17188,7 +17192,7 @@
         <v>82</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>82</v>
@@ -17196,10 +17200,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17222,17 +17226,17 @@
         <v>82</v>
       </c>
       <c r="K126" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="L126" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="L126" t="s" s="2">
+      <c r="M126" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>82</v>
@@ -17281,7 +17285,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17296,7 +17300,7 @@
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>108</v>
@@ -17305,7 +17309,7 @@
         <v>82</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>82</v>
@@ -17313,10 +17317,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17342,7 +17346,7 @@
         <v>170</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>499</v>
+        <v>615</v>
       </c>
       <c r="M127" t="s" s="2">
         <v>616</v>
@@ -17377,10 +17381,10 @@
         <v>269</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>503</v>
+        <v>618</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>504</v>
+        <v>619</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>82</v>
@@ -17398,7 +17402,7 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17413,7 +17417,7 @@
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>108</v>
@@ -17422,7 +17426,7 @@
         <v>82</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>82</v>
@@ -17430,10 +17434,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17459,14 +17463,14 @@
         <v>308</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>82</v>
@@ -17515,7 +17519,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -17524,13 +17528,13 @@
         <v>90</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>108</v>
@@ -17539,7 +17543,7 @@
         <v>82</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>82</v>
@@ -17547,10 +17551,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17576,10 +17580,10 @@
         <v>301</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17630,7 +17634,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -17645,7 +17649,7 @@
         <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>108</v>
@@ -17662,10 +17666,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17688,19 +17692,19 @@
         <v>82</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>82</v>
@@ -17749,7 +17753,7 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -17764,10 +17768,10 @@
         <v>102</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>82</v>
@@ -17781,10 +17785,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17896,10 +17900,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18013,14 +18017,14 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -18042,10 +18046,10 @@
         <v>111</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="N133" t="s" s="2">
         <v>114</v>
@@ -18100,7 +18104,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18132,10 +18136,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18161,16 +18165,16 @@
         <v>275</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>82</v>
@@ -18219,7 +18223,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>90</v>
@@ -18234,16 +18238,16 @@
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>82</v>
@@ -18251,10 +18255,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18280,16 +18284,16 @@
         <v>383</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>82</v>
@@ -18338,7 +18342,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18353,16 +18357,16 @@
         <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>82</v>
@@ -18370,14 +18374,14 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
@@ -18396,16 +18400,16 @@
         <v>82</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -18455,7 +18459,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -18470,7 +18474,7 @@
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>108</v>
@@ -18479,7 +18483,7 @@
         <v>82</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>82</v>
@@ -18487,10 +18491,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18513,19 +18517,19 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>82</v>
@@ -18574,7 +18578,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -18589,10 +18593,10 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>82</v>
@@ -18606,10 +18610,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18632,19 +18636,19 @@
         <v>91</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>82</v>
@@ -18693,7 +18697,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -18708,7 +18712,7 @@
         <v>102</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>108</v>
@@ -18725,10 +18729,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18840,10 +18844,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18957,14 +18961,14 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
@@ -18986,10 +18990,10 @@
         <v>111</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="N141" t="s" s="2">
         <v>114</v>
@@ -19044,7 +19048,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19076,10 +19080,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19102,16 +19106,16 @@
         <v>91</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -19161,7 +19165,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>90</v>
@@ -19185,7 +19189,7 @@
         <v>82</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>82</v>
@@ -19193,10 +19197,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19222,10 +19226,10 @@
         <v>170</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -19255,28 +19259,28 @@
         <v>269</v>
       </c>
       <c r="Y143" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="Z143" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="AA143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF143" t="s" s="2">
         <v>688</v>
-      </c>
-      <c r="Z143" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="AA143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF143" t="s" s="2">
-        <v>686</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>90</v>
@@ -19291,7 +19295,7 @@
         <v>102</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="AL143" t="s" s="2">
         <v>108</v>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T12:04:30+00:00</t>
+    <t>2025-10-08T16:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -688,10 +688,10 @@
 Carries the death place of the patient</t>
   </si>
   <si>
-    <t>Patient.extension:birthdateUpdateIndicator</t>
-  </si>
-  <si>
-    <t>birthdateUpdateIndicator</t>
+    <t>Patient.extension:birthDateUpdateIndicator</t>
+  </si>
+  <si>
+    <t>birthDateUpdateIndicator</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-birthdate-update-indicator}
@@ -1882,10 +1882,10 @@
     <t>NK1-7, NK1-3</t>
   </si>
   <si>
-    <t>Patient.contact.relationship:Role</t>
-  </si>
-  <si>
-    <t>Role</t>
+    <t>Patient.contact.relationship:role</t>
+  </si>
+  <si>
+    <t>role</t>
   </si>
   <si>
     <t>The nature of the relationship. Rôle de la personne. Ex : personne de confiance, aidant ...</t>
@@ -1894,10 +1894,10 @@
     <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-role</t>
   </si>
   <si>
-    <t>Patient.contact.relationship:RelationType</t>
-  </si>
-  <si>
-    <t>RelationType</t>
+    <t>Patient.contact.relationship:relationType</t>
+  </si>
+  <si>
+    <t>relationType</t>
   </si>
   <si>
     <t>The nature of the relationship. Relation de la personne. Ex : Mère, époux, enfant ...</t>
@@ -2119,7 +2119,7 @@
     <t>Patient.managingOrganization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|Organization)
 </t>
   </si>
   <si>
@@ -2513,7 +2513,7 @@
   <cols>
     <col min="1" max="1" width="46.9765625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="33.83984375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="20.76953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="20.984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:25:45+00:00</t>
+    <t>2026-02-04T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:09:39+00:00</t>
+    <t>2026-02-09T06:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T06:47:58+00:00</t>
+    <t>2026-02-11T16:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T16:15:37+00:00</t>
+    <t>2026-02-17T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:02:14+00:00</t>
+    <t>2026-02-23T09:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T09:26:22+00:00</t>
+    <t>2026-02-23T10:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:39:10+00:00</t>
+    <t>2026-02-23T12:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T07:09:47+00:00</t>
+    <t>2026-03-25T10:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5306" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5964" uniqueCount="738">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:11+00:00</t>
+    <t>2026-03-25T10:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1867,6 +1867,10 @@
     <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship|4.0.1</t>
   </si>
   <si>
+    <t xml:space="preserve">value:extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-contact-relationship-category').value}
+</t>
+  </si>
+  <si>
     <t>code</t>
   </si>
   <si>
@@ -1885,6 +1889,121 @@
     <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-role|2.2.0</t>
   </si>
   <si>
+    <t>Patient.contact.relationship:role.id</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.id</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:role.extension</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.extension</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:role.extension:category</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-contact-relationship-category|2.2.0}
+</t>
+  </si>
+  <si>
+    <t>FR Core Patient Contact Relationship Category Extension</t>
+  </si>
+  <si>
+    <t>Catégorie de la relation du contact patient : indique si le CodeableConcept représente un rôle (ex : personne à prévenir) ou un type de relation (ex : mère)</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:role.extension:category.id</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.extension.id</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:role.extension:category.extension</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.extension.extension</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:role.extension:category.url</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.extension.url</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-contact-relationship-category</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:role.extension:category.value[x]</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-relationship-category|2.2.0</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:role.coding</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.coding</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:role.text</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
     <t>Patient.contact.relationship:relationType</t>
   </si>
   <si>
@@ -1895,6 +2014,33 @@
   </si>
   <si>
     <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-relation-type|2.2.0</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:relationType.id</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:relationType.extension</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:relationType.extension:category</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:relationType.extension:category.id</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:relationType.extension:category.extension</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:relationType.extension:category.url</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:relationType.extension:category.value[x]</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:relationType.coding</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:relationType.text</t>
   </si>
   <si>
     <t>Patient.contact.name</t>
@@ -2499,11 +2645,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO142"/>
+  <dimension ref="A1:AO160"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="46.9765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="33.83984375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="56.85546875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.97265625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="20.984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -2527,9 +2673,9 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.015625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="69.84765625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="91.3359375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="64.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
@@ -16562,7 +16708,7 @@
         <v>82</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>142</v>
+        <v>585</v>
       </c>
       <c r="AC120" s="2"/>
       <c r="AD120" t="s" s="2">
@@ -16587,7 +16733,7 @@
         <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AL120" t="s" s="2">
         <v>108</v>
@@ -16596,7 +16742,7 @@
         <v>82</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>82</v>
@@ -16604,13 +16750,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>579</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>82</v>
@@ -16635,7 +16781,7 @@
         <v>272</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M121" t="s" s="2">
         <v>581</v>
@@ -16671,7 +16817,7 @@
       </c>
       <c r="Y121" s="2"/>
       <c r="Z121" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>82</v>
@@ -16704,7 +16850,7 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>108</v>
@@ -16713,7 +16859,7 @@
         <v>82</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>82</v>
@@ -16721,14 +16867,12 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="C122" t="s" s="2">
-        <v>592</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
         <v>82</v>
       </c>
@@ -16749,18 +16893,16 @@
         <v>82</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>272</v>
+        <v>104</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>593</v>
+        <v>105</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>581</v>
+        <v>106</v>
       </c>
       <c r="N122" s="2"/>
-      <c r="O122" t="s" s="2">
-        <v>582</v>
-      </c>
+      <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>82</v>
       </c>
@@ -16784,11 +16926,13 @@
         <v>82</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y122" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z122" t="s" s="2">
-        <v>594</v>
+        <v>82</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>82</v>
@@ -16806,31 +16950,31 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>579</v>
+        <v>107</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>585</v>
+        <v>108</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>586</v>
+        <v>82</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>82</v>
@@ -16838,7 +16982,7 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>595</v>
@@ -16849,10 +16993,10 @@
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>82</v>
@@ -16864,18 +17008,16 @@
         <v>82</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>389</v>
+        <v>111</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>596</v>
+        <v>196</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>597</v>
+        <v>197</v>
       </c>
       <c r="N123" s="2"/>
-      <c r="O123" t="s" s="2">
-        <v>598</v>
-      </c>
+      <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>82</v>
       </c>
@@ -16911,43 +17053,43 @@
         <v>82</v>
       </c>
       <c r="AB123" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC123" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD123" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE123" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>595</v>
+        <v>118</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>599</v>
+        <v>82</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>82</v>
@@ -16955,21 +17097,23 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="C124" s="2"/>
+        <v>595</v>
+      </c>
+      <c r="C124" t="s" s="2">
+        <v>597</v>
+      </c>
       <c r="D124" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>82</v>
@@ -16981,20 +17125,16 @@
         <v>82</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>487</v>
+        <v>598</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>491</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="N124" s="2"/>
+      <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>82</v>
       </c>
@@ -17042,7 +17182,7 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>600</v>
+        <v>118</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17054,19 +17194,19 @@
         <v>82</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>492</v>
+        <v>82</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>604</v>
+        <v>82</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>82</v>
@@ -17074,10 +17214,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17100,18 +17240,16 @@
         <v>82</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>606</v>
+        <v>104</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>607</v>
+        <v>105</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>608</v>
+        <v>106</v>
       </c>
       <c r="N125" s="2"/>
-      <c r="O125" t="s" s="2">
-        <v>609</v>
-      </c>
+      <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>82</v>
       </c>
@@ -17159,7 +17297,7 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>605</v>
+        <v>107</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17171,19 +17309,19 @@
         <v>82</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>527</v>
+        <v>108</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>610</v>
+        <v>82</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>82</v>
@@ -17191,10 +17329,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17205,7 +17343,7 @@
         <v>80</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>82</v>
@@ -17217,18 +17355,16 @@
         <v>82</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>171</v>
+        <v>111</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>612</v>
+        <v>196</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>613</v>
+        <v>197</v>
       </c>
       <c r="N126" s="2"/>
-      <c r="O126" t="s" s="2">
-        <v>614</v>
-      </c>
+      <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
         <v>82</v>
       </c>
@@ -17252,55 +17388,55 @@
         <v>82</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>266</v>
+        <v>82</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>615</v>
+        <v>82</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>616</v>
+        <v>82</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB126" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC126" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD126" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE126" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>611</v>
+        <v>118</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>501</v>
+        <v>82</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>617</v>
+        <v>82</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>82</v>
@@ -17308,10 +17444,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>618</v>
+        <v>605</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17319,7 +17455,7 @@
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G127" t="s" s="2">
         <v>90</v>
@@ -17334,24 +17470,24 @@
         <v>82</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>305</v>
+        <v>132</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>619</v>
+        <v>231</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="N127" s="2"/>
-      <c r="O127" t="s" s="2">
-        <v>621</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
-        <v>82</v>
+        <v>607</v>
       </c>
       <c r="S127" t="s" s="2">
         <v>82</v>
@@ -17393,31 +17529,31 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>618</v>
+        <v>235</v>
       </c>
       <c r="AG127" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH127" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>622</v>
+        <v>82</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>623</v>
+        <v>194</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>624</v>
+        <v>82</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>82</v>
@@ -17425,10 +17561,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>625</v>
+        <v>608</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>625</v>
+        <v>609</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17451,13 +17587,13 @@
         <v>82</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>298</v>
+        <v>171</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>626</v>
+        <v>239</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>627</v>
+        <v>610</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -17469,7 +17605,7 @@
         <v>82</v>
       </c>
       <c r="S128" t="s" s="2">
-        <v>82</v>
+        <v>589</v>
       </c>
       <c r="T128" t="s" s="2">
         <v>82</v>
@@ -17484,13 +17620,11 @@
         <v>82</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y128" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="Y128" s="2"/>
       <c r="Z128" t="s" s="2">
-        <v>82</v>
+        <v>611</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>82</v>
@@ -17508,7 +17642,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>625</v>
+        <v>241</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -17523,10 +17657,10 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>628</v>
+        <v>194</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>82</v>
@@ -17540,10 +17674,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>629</v>
+        <v>612</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>629</v>
+        <v>613</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17563,22 +17697,22 @@
         <v>82</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>555</v>
+        <v>149</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>630</v>
+        <v>614</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>631</v>
+        <v>615</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>632</v>
+        <v>616</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>633</v>
+        <v>617</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>82</v>
@@ -17627,7 +17761,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>629</v>
+        <v>618</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -17642,16 +17776,16 @@
         <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>634</v>
+        <v>619</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>635</v>
+        <v>82</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>82</v>
+        <v>620</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>82</v>
@@ -17659,10 +17793,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>636</v>
+        <v>621</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>636</v>
+        <v>622</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17682,19 +17816,23 @@
         <v>82</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K130" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>105</v>
+        <v>623</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N130" s="2"/>
-      <c r="O130" s="2"/>
+        <v>624</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="O130" t="s" s="2">
+        <v>626</v>
+      </c>
       <c r="P130" t="s" s="2">
         <v>82</v>
       </c>
@@ -17742,7 +17880,7 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>107</v>
+        <v>627</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -17754,10 +17892,10 @@
         <v>82</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>108</v>
+        <v>628</v>
       </c>
       <c r="AL130" t="s" s="2">
         <v>82</v>
@@ -17766,7 +17904,7 @@
         <v>82</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>82</v>
+        <v>629</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>82</v>
@@ -17774,21 +17912,23 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="C131" s="2"/>
+        <v>579</v>
+      </c>
+      <c r="C131" t="s" s="2">
+        <v>631</v>
+      </c>
       <c r="D131" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>82</v>
@@ -17800,18 +17940,18 @@
         <v>82</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>111</v>
+        <v>272</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>112</v>
+        <v>632</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O131" s="2"/>
+        <v>581</v>
+      </c>
+      <c r="N131" s="2"/>
+      <c r="O131" t="s" s="2">
+        <v>582</v>
+      </c>
       <c r="P131" t="s" s="2">
         <v>82</v>
       </c>
@@ -17835,13 +17975,11 @@
         <v>82</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y131" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y131" s="2"/>
       <c r="Z131" t="s" s="2">
-        <v>82</v>
+        <v>633</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>82</v>
@@ -17859,7 +17997,7 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>118</v>
+        <v>579</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -17871,19 +18009,19 @@
         <v>82</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK131" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AL131" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="AL131" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>82</v>
+        <v>587</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>82</v>
@@ -17891,46 +18029,42 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>638</v>
+        <v>593</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>575</v>
+        <v>82</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I132" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>576</v>
+        <v>105</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N132" s="2"/>
+      <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>82</v>
       </c>
@@ -17978,22 +18112,22 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>578</v>
+        <v>107</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>194</v>
+        <v>108</v>
       </c>
       <c r="AL132" t="s" s="2">
         <v>82</v>
@@ -18010,10 +18144,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>639</v>
+        <v>595</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18024,7 +18158,7 @@
         <v>90</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>82</v>
@@ -18036,20 +18170,16 @@
         <v>82</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>272</v>
+        <v>111</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>640</v>
+        <v>196</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>643</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N133" s="2"/>
+      <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>82</v>
       </c>
@@ -18073,55 +18203,55 @@
         <v>82</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB133" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC133" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE133" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>639</v>
+        <v>118</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>644</v>
+        <v>82</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>645</v>
+        <v>82</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>646</v>
+        <v>82</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>82</v>
@@ -18129,18 +18259,20 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>647</v>
+        <v>636</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="C134" s="2"/>
+        <v>595</v>
+      </c>
+      <c r="C134" t="s" s="2">
+        <v>597</v>
+      </c>
       <c r="D134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G134" t="s" s="2">
         <v>90</v>
@@ -18155,20 +18287,16 @@
         <v>82</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>380</v>
+        <v>598</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>648</v>
+        <v>599</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>651</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="N134" s="2"/>
+      <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>82</v>
       </c>
@@ -18216,31 +18344,31 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>647</v>
+        <v>118</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>652</v>
+        <v>82</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>653</v>
+        <v>82</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>654</v>
+        <v>82</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>82</v>
@@ -18248,21 +18376,21 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>655</v>
+        <v>637</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>655</v>
+        <v>602</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>656</v>
+        <v>82</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>82</v>
@@ -18274,17 +18402,15 @@
         <v>82</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>657</v>
+        <v>104</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>658</v>
+        <v>105</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>660</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N135" s="2"/>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>82</v>
@@ -18333,31 +18459,31 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>655</v>
+        <v>107</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>661</v>
+        <v>108</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>662</v>
+        <v>82</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>82</v>
@@ -18365,10 +18491,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>663</v>
+        <v>638</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>663</v>
+        <v>604</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18379,7 +18505,7 @@
         <v>80</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>82</v>
@@ -18388,23 +18514,19 @@
         <v>82</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>664</v>
+        <v>111</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>665</v>
+        <v>196</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>668</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N136" s="2"/>
+      <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
         <v>82</v>
       </c>
@@ -18440,37 +18562,37 @@
         <v>82</v>
       </c>
       <c r="AB136" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC136" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD136" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE136" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>663</v>
+        <v>118</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>623</v>
+        <v>82</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>669</v>
+        <v>82</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>82</v>
@@ -18484,10 +18606,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>670</v>
+        <v>639</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>670</v>
+        <v>606</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18495,41 +18617,39 @@
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I137" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J137" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>555</v>
+        <v>132</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>671</v>
+        <v>231</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>672</v>
+        <v>232</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>674</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q137" s="2"/>
       <c r="R137" t="s" s="2">
-        <v>82</v>
+        <v>607</v>
       </c>
       <c r="S137" t="s" s="2">
         <v>82</v>
@@ -18571,25 +18691,25 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>670</v>
+        <v>235</v>
       </c>
       <c r="AG137" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>675</v>
+        <v>194</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>82</v>
@@ -18603,10 +18723,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>676</v>
+        <v>640</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>676</v>
+        <v>609</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18629,13 +18749,13 @@
         <v>82</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>104</v>
+        <v>171</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>105</v>
+        <v>239</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>106</v>
+        <v>610</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -18647,7 +18767,7 @@
         <v>82</v>
       </c>
       <c r="S138" t="s" s="2">
-        <v>82</v>
+        <v>631</v>
       </c>
       <c r="T138" t="s" s="2">
         <v>82</v>
@@ -18662,13 +18782,11 @@
         <v>82</v>
       </c>
       <c r="X138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y138" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="Y138" s="2"/>
       <c r="Z138" t="s" s="2">
-        <v>82</v>
+        <v>611</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>82</v>
@@ -18686,7 +18804,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>107</v>
+        <v>241</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -18698,10 +18816,10 @@
         <v>82</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>108</v>
+        <v>194</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>82</v>
@@ -18718,14 +18836,14 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>677</v>
+        <v>641</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>677</v>
+        <v>613</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
@@ -18741,21 +18859,23 @@
         <v>82</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>112</v>
+        <v>614</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>113</v>
+        <v>615</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O139" s="2"/>
+        <v>616</v>
+      </c>
+      <c r="O139" t="s" s="2">
+        <v>617</v>
+      </c>
       <c r="P139" t="s" s="2">
         <v>82</v>
       </c>
@@ -18803,7 +18923,7 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>118</v>
+        <v>618</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -18815,10 +18935,10 @@
         <v>82</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>108</v>
+        <v>619</v>
       </c>
       <c r="AL139" t="s" s="2">
         <v>82</v>
@@ -18827,7 +18947,7 @@
         <v>82</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>82</v>
+        <v>620</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>82</v>
@@ -18835,45 +18955,45 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>678</v>
+        <v>642</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>678</v>
+        <v>622</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>575</v>
+        <v>82</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I140" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J140" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>576</v>
+        <v>623</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>577</v>
+        <v>624</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>114</v>
+        <v>625</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>246</v>
+        <v>626</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>82</v>
@@ -18922,22 +19042,22 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>578</v>
+        <v>627</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>194</v>
+        <v>628</v>
       </c>
       <c r="AL140" t="s" s="2">
         <v>82</v>
@@ -18946,7 +19066,7 @@
         <v>82</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>82</v>
+        <v>629</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>82</v>
@@ -18954,10 +19074,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>679</v>
+        <v>643</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>679</v>
+        <v>643</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18965,7 +19085,7 @@
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G141" t="s" s="2">
         <v>90</v>
@@ -18977,21 +19097,21 @@
         <v>82</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>680</v>
+        <v>389</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>681</v>
+        <v>644</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="O141" s="2"/>
+        <v>645</v>
+      </c>
+      <c r="N141" s="2"/>
+      <c r="O141" t="s" s="2">
+        <v>646</v>
+      </c>
       <c r="P141" t="s" s="2">
         <v>82</v>
       </c>
@@ -19039,10 +19159,10 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>679</v>
+        <v>643</v>
       </c>
       <c r="AG141" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH141" t="s" s="2">
         <v>90</v>
@@ -19054,7 +19174,7 @@
         <v>102</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>255</v>
+        <v>395</v>
       </c>
       <c r="AL141" t="s" s="2">
         <v>108</v>
@@ -19063,7 +19183,7 @@
         <v>82</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>684</v>
+        <v>647</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>82</v>
@@ -19071,10 +19191,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>685</v>
+        <v>648</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>685</v>
+        <v>648</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19082,10 +19202,10 @@
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>82</v>
@@ -19094,19 +19214,23 @@
         <v>82</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>171</v>
+        <v>487</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>686</v>
+        <v>649</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="N142" s="2"/>
-      <c r="O142" s="2"/>
+        <v>650</v>
+      </c>
+      <c r="N142" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="O142" t="s" s="2">
+        <v>491</v>
+      </c>
       <c r="P142" t="s" s="2">
         <v>82</v>
       </c>
@@ -19130,13 +19254,13 @@
         <v>82</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>266</v>
+        <v>82</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>687</v>
+        <v>82</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>688</v>
+        <v>82</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>82</v>
@@ -19154,13 +19278,13 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>685</v>
+        <v>648</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI142" t="s" s="2">
         <v>82</v>
@@ -19169,7 +19293,7 @@
         <v>102</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>689</v>
+        <v>492</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>108</v>
@@ -19178,9 +19302,2121 @@
         <v>82</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>82</v>
+        <v>652</v>
       </c>
       <c r="AO142" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="C143" s="2"/>
+      <c r="D143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E143" s="2"/>
+      <c r="F143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G143" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K143" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="L143" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="M143" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="N143" s="2"/>
+      <c r="O143" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="P143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q143" s="2"/>
+      <c r="R143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF143" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AG143" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH143" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ143" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK143" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AL143" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN143" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="AO143" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="C144" s="2"/>
+      <c r="D144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E144" s="2"/>
+      <c r="F144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G144" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K144" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L144" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="M144" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="N144" s="2"/>
+      <c r="O144" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="P144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q144" s="2"/>
+      <c r="R144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X144" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="Y144" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="Z144" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="AA144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF144" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AG144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH144" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ144" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK144" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AL144" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN144" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="AO144" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="C145" s="2"/>
+      <c r="D145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E145" s="2"/>
+      <c r="F145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G145" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K145" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L145" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="M145" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="N145" s="2"/>
+      <c r="O145" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="P145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q145" s="2"/>
+      <c r="R145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF145" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="AG145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH145" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI145" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="AJ145" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK145" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="AL145" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN145" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="AO145" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="C146" s="2"/>
+      <c r="D146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E146" s="2"/>
+      <c r="F146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G146" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K146" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="L146" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="M146" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="N146" s="2"/>
+      <c r="O146" s="2"/>
+      <c r="P146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q146" s="2"/>
+      <c r="R146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF146" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="AG146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH146" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ146" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK146" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="AL146" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO146" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="C147" s="2"/>
+      <c r="D147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E147" s="2"/>
+      <c r="F147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G147" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K147" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="L147" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="M147" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="N147" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="O147" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="P147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q147" s="2"/>
+      <c r="R147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF147" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="AG147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH147" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ147" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK147" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="AL147" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="AM147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO147" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="C148" s="2"/>
+      <c r="D148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E148" s="2"/>
+      <c r="F148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G148" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K148" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L148" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M148" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N148" s="2"/>
+      <c r="O148" s="2"/>
+      <c r="P148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q148" s="2"/>
+      <c r="R148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF148" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH148" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK148" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AL148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO148" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="B149" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="C149" s="2"/>
+      <c r="D149" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E149" s="2"/>
+      <c r="F149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G149" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K149" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L149" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M149" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N149" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O149" s="2"/>
+      <c r="P149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q149" s="2"/>
+      <c r="R149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF149" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH149" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ149" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK149" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AL149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO149" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="C150" s="2"/>
+      <c r="D150" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="E150" s="2"/>
+      <c r="F150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G150" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I150" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J150" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K150" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L150" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M150" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="N150" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O150" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="P150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q150" s="2"/>
+      <c r="R150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF150" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AG150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH150" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ150" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK150" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AL150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO150" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="C151" s="2"/>
+      <c r="D151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E151" s="2"/>
+      <c r="F151" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G151" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K151" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="L151" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="M151" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="N151" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="O151" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="P151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q151" s="2"/>
+      <c r="R151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X151" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="Y151" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="Z151" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AA151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF151" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="AG151" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH151" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ151" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK151" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="AL151" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="AM151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN151" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="AO151" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="C152" s="2"/>
+      <c r="D152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E152" s="2"/>
+      <c r="F152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G152" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K152" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="L152" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="M152" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="O152" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="P152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q152" s="2"/>
+      <c r="R152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF152" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="AG152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH152" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ152" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK152" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="AL152" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="AM152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN152" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="AO152" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="C153" s="2"/>
+      <c r="D153" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="E153" s="2"/>
+      <c r="F153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G153" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K153" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="L153" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="M153" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="N153" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="O153" s="2"/>
+      <c r="P153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q153" s="2"/>
+      <c r="R153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF153" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="AG153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH153" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ153" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK153" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="AL153" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN153" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AO153" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="C154" s="2"/>
+      <c r="D154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E154" s="2"/>
+      <c r="F154" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G154" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J154" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K154" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="L154" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="M154" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="N154" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="O154" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="P154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q154" s="2"/>
+      <c r="R154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF154" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AG154" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH154" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ154" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK154" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="AL154" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="AM154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO154" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="B155" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="C155" s="2"/>
+      <c r="D155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E155" s="2"/>
+      <c r="F155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G155" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I155" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J155" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K155" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="L155" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="M155" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="N155" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="O155" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="P155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q155" s="2"/>
+      <c r="R155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF155" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="AG155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH155" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ155" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK155" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="AL155" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO155" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="B156" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="C156" s="2"/>
+      <c r="D156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E156" s="2"/>
+      <c r="F156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G156" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K156" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L156" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M156" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N156" s="2"/>
+      <c r="O156" s="2"/>
+      <c r="P156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q156" s="2"/>
+      <c r="R156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF156" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH156" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK156" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AL156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO156" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="B157" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="C157" s="2"/>
+      <c r="D157" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E157" s="2"/>
+      <c r="F157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G157" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K157" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L157" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M157" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N157" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O157" s="2"/>
+      <c r="P157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q157" s="2"/>
+      <c r="R157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF157" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH157" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ157" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK157" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AL157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO157" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="C158" s="2"/>
+      <c r="D158" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="E158" s="2"/>
+      <c r="F158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G158" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I158" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J158" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K158" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L158" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M158" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="N158" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O158" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="P158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q158" s="2"/>
+      <c r="R158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF158" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AG158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH158" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ158" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK158" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AL158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO158" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="C159" s="2"/>
+      <c r="D159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E159" s="2"/>
+      <c r="F159" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G159" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J159" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K159" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="L159" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="M159" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="N159" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="O159" s="2"/>
+      <c r="P159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q159" s="2"/>
+      <c r="R159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF159" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="AG159" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH159" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ159" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK159" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AL159" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN159" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="AO159" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="C160" s="2"/>
+      <c r="D160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E160" s="2"/>
+      <c r="F160" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G160" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J160" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K160" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L160" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="M160" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="N160" s="2"/>
+      <c r="O160" s="2"/>
+      <c r="P160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q160" s="2"/>
+      <c r="R160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X160" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="Y160" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="Z160" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="AA160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF160" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="AG160" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH160" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ160" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK160" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="AL160" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO160" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:40+00:00</t>
+    <t>2026-03-25T10:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5964" uniqueCount="738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6298" uniqueCount="752">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:25:13+00:00</t>
+    <t>2026-03-25T15:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -992,28 +992,28 @@
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
   </si>
   <si>
-    <t>Patient.identifier:NSS</t>
-  </si>
-  <si>
-    <t>NSS</t>
+    <t>Patient.identifier:NSS-NIR</t>
+  </si>
+  <si>
+    <t>NSS-NIR</t>
   </si>
   <si>
     <t>National Health Plan Identifier | Le Numéro d'Inscription au Répertoire (NIR) de facturation permet de faire transiter le numéro de sécurité social de l’ayant droit ou du bénéfiaire (patient) / le numéro de sécurité sociale de l’ouvrant droit (assuré).</t>
   </si>
   <si>
-    <t>Patient.identifier:NSS.id</t>
-  </si>
-  <si>
-    <t>Patient.identifier:NSS.extension</t>
-  </si>
-  <si>
-    <t>Patient.identifier:NSS.use</t>
+    <t>Patient.identifier:NSS-NIR.id</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIR.extension</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIR.use</t>
   </si>
   <si>
     <t>official</t>
   </si>
   <si>
-    <t>Patient.identifier:NSS.type</t>
+    <t>Patient.identifier:NSS-NIR.type</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -1024,19 +1024,61 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Patient.identifier:NSS.system</t>
-  </si>
-  <si>
-    <t>urn:oid:1.2.250.1.213.1.4.8</t>
-  </si>
-  <si>
-    <t>Patient.identifier:NSS.value</t>
-  </si>
-  <si>
-    <t>Patient.identifier:NSS.period</t>
-  </si>
-  <si>
-    <t>Patient.identifier:NSS.assigner</t>
+    <t>Patient.identifier:NSS-NIR.system</t>
+  </si>
+  <si>
+    <t>Autorité d’affectation du NIR utilisé en tant que numéro de sécurité sociale</t>
+  </si>
+  <si>
+    <t>urn:oid:1.2.250.1.213.1.4.13</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIR.value</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIR.period</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIR.assigner</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA</t>
+  </si>
+  <si>
+    <t>NSS-NIA</t>
+  </si>
+  <si>
+    <t>National Health Plan Identifier | Le Numéro d'Inscription au Répertoire (NIA) de facturation d'attente permet de faire transiter le numéro de sécurité social de l’ayant droit ou du bénéfiaire (patient) / le numéro de sécurité sociale d'attente de l’ouvrant droit (assuré).</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.id</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.extension</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.use</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.type</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.system</t>
+  </si>
+  <si>
+    <t>Autorité d’affectation du NIA utilisé en tant que numéro de sécurité sociale</t>
+  </si>
+  <si>
+    <t>urn:oid:1.2.250.1.213.1.4.14</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.value</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.period</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.assigner</t>
   </si>
   <si>
     <t>Patient.identifier:INS-C</t>
@@ -2645,7 +2687,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO160"/>
+  <dimension ref="A1:AO169"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="56.85546875" customWidth="true" bestFit="true"/>
@@ -7633,7 +7675,7 @@
         <v>132</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>281</v>
+        <v>322</v>
       </c>
       <c r="M43" t="s" s="2">
         <v>282</v>
@@ -7652,7 +7694,7 @@
         <v>82</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>285</v>
@@ -7723,7 +7765,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>289</v>
@@ -7840,7 +7882,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>297</v>
@@ -7955,7 +7997,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>304</v>
@@ -8072,13 +8114,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>248</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>82</v>
@@ -8088,7 +8130,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>82</v>
@@ -8103,7 +8145,7 @@
         <v>249</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M47" t="s" s="2">
         <v>251</v>
@@ -8191,7 +8233,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>259</v>
@@ -8306,7 +8348,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>260</v>
@@ -8423,7 +8465,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>261</v>
@@ -8471,7 +8513,7 @@
         <v>82</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>82</v>
@@ -8590,7 +8632,7 @@
         <v>82</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>82</v>
@@ -8659,7 +8701,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>280</v>
@@ -8688,7 +8730,7 @@
         <v>132</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>281</v>
+        <v>335</v>
       </c>
       <c r="M52" t="s" s="2">
         <v>282</v>
@@ -9143,7 +9185,7 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>82</v>
@@ -9526,7 +9568,7 @@
         <v>82</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>82</v>
@@ -9597,7 +9639,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>271</v>
@@ -9645,7 +9687,7 @@
         <v>82</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>82</v>
@@ -9714,7 +9756,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>280</v>
@@ -9762,7 +9804,7 @@
         <v>82</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>285</v>
@@ -9833,7 +9875,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>289</v>
@@ -9950,7 +9992,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>297</v>
@@ -10065,7 +10107,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>304</v>
@@ -10182,13 +10224,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>248</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>82</v>
@@ -10198,7 +10240,7 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -10213,7 +10255,7 @@
         <v>249</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M65" t="s" s="2">
         <v>251</v>
@@ -10301,7 +10343,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>259</v>
@@ -10416,7 +10458,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>260</v>
@@ -10533,7 +10575,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>261</v>
@@ -10568,7 +10610,7 @@
         <v>263</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>359</v>
+        <v>264</v>
       </c>
       <c r="O68" t="s" s="2">
         <v>265</v>
@@ -10581,7 +10623,7 @@
         <v>82</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>82</v>
@@ -10598,9 +10640,11 @@
       <c r="X68" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="Y68" s="2"/>
+      <c r="Y68" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="Z68" t="s" s="2">
-        <v>360</v>
+        <v>268</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10650,7 +10694,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>271</v>
@@ -10698,7 +10742,7 @@
         <v>82</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>82</v>
@@ -10767,7 +10811,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>280</v>
@@ -10815,7 +10859,7 @@
         <v>82</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>82</v>
+        <v>363</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>285</v>
@@ -11621,7 +11665,7 @@
         <v>263</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>264</v>
+        <v>373</v>
       </c>
       <c r="O77" t="s" s="2">
         <v>265</v>
@@ -11634,7 +11678,7 @@
         <v>82</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>332</v>
+        <v>82</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>82</v>
@@ -11651,11 +11695,9 @@
       <c r="X77" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="Y77" t="s" s="2">
-        <v>267</v>
-      </c>
+      <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
-        <v>268</v>
+        <v>374</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>82</v>
@@ -11705,7 +11747,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>271</v>
@@ -11753,7 +11795,7 @@
         <v>82</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>82</v>
@@ -11822,7 +11864,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>280</v>
@@ -11941,7 +11983,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>289</v>
@@ -12058,7 +12100,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>297</v>
@@ -12173,7 +12215,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>304</v>
@@ -12290,12 +12332,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="C83" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="C83" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="D83" t="s" s="2">
         <v>82</v>
       </c>
@@ -12304,38 +12348,34 @@
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J83" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>380</v>
+        <v>249</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>384</v>
+        <v>252</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q83" t="s" s="2">
-        <v>385</v>
-      </c>
+      <c r="Q83" s="2"/>
       <c r="R83" t="s" s="2">
         <v>82</v>
       </c>
@@ -12379,13 +12419,13 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>379</v>
+        <v>248</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>82</v>
@@ -12394,16 +12434,16 @@
         <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>386</v>
+        <v>255</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>108</v>
+        <v>256</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>387</v>
+        <v>257</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>82</v>
+        <v>258</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12411,10 +12451,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>388</v>
+        <v>259</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12425,7 +12465,7 @@
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>82</v>
@@ -12434,23 +12474,19 @@
         <v>82</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>389</v>
+        <v>104</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>390</v>
+        <v>105</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
       </c>
@@ -12486,41 +12522,43 @@
         <v>82</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AC84" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>388</v>
+        <v>107</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>395</v>
+        <v>108</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>396</v>
+        <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12528,16 +12566,14 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="C85" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12553,23 +12589,21 @@
         <v>82</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>400</v>
+        <v>111</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>401</v>
+        <v>112</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>402</v>
+        <v>113</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12605,19 +12639,19 @@
         <v>82</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>388</v>
+        <v>118</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12629,19 +12663,19 @@
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>395</v>
+        <v>108</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>396</v>
+        <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12649,10 +12683,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>404</v>
+        <v>261</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12660,7 +12694,7 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>90</v>
@@ -12669,22 +12703,26 @@
         <v>82</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>104</v>
+        <v>171</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>105</v>
+        <v>262</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12693,7 +12731,7 @@
         <v>82</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>82</v>
@@ -12708,13 +12746,13 @@
         <v>82</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>82</v>
@@ -12732,7 +12770,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>107</v>
+        <v>269</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12744,10 +12782,10 @@
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>108</v>
+        <v>270</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>82</v>
@@ -12756,7 +12794,7 @@
         <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>82</v>
+        <v>194</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12764,21 +12802,21 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>405</v>
+        <v>387</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>406</v>
+        <v>271</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>82</v>
@@ -12787,21 +12825,23 @@
         <v>82</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>111</v>
+        <v>272</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>112</v>
+        <v>273</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>113</v>
+        <v>274</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O87" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -12810,7 +12850,7 @@
         <v>82</v>
       </c>
       <c r="S87" t="s" s="2">
-        <v>82</v>
+        <v>388</v>
       </c>
       <c r="T87" t="s" s="2">
         <v>82</v>
@@ -12825,46 +12865,44 @@
         <v>82</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y87" s="2"/>
       <c r="Z87" t="s" s="2">
-        <v>82</v>
+        <v>277</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>118</v>
+        <v>278</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>108</v>
+        <v>270</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>82</v>
@@ -12873,7 +12911,7 @@
         <v>82</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -12881,10 +12919,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>407</v>
+        <v>389</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>408</v>
+        <v>280</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12901,25 +12939,25 @@
         <v>82</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J88" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>171</v>
+        <v>132</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>409</v>
+        <v>281</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>410</v>
+        <v>282</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>411</v>
+        <v>283</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>412</v>
+        <v>284</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -12929,10 +12967,10 @@
         <v>82</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>413</v>
+        <v>82</v>
       </c>
       <c r="T88" t="s" s="2">
-        <v>82</v>
+        <v>285</v>
       </c>
       <c r="U88" t="s" s="2">
         <v>82</v>
@@ -12944,13 +12982,13 @@
         <v>82</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>266</v>
+        <v>82</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>414</v>
+        <v>82</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>415</v>
+        <v>82</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
@@ -12968,7 +13006,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>416</v>
+        <v>286</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12983,7 +13021,7 @@
         <v>102</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>417</v>
+        <v>287</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>82</v>
@@ -12992,7 +13030,7 @@
         <v>82</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>418</v>
+        <v>288</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -13000,10 +13038,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>419</v>
+        <v>390</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>420</v>
+        <v>289</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13011,7 +13049,7 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>90</v>
@@ -13029,17 +13067,15 @@
         <v>104</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>421</v>
+        <v>290</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>422</v>
+        <v>291</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
@@ -13051,7 +13087,7 @@
         <v>82</v>
       </c>
       <c r="T89" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="U89" t="s" s="2">
         <v>82</v>
@@ -13087,7 +13123,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>425</v>
+        <v>294</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13102,7 +13138,7 @@
         <v>102</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>426</v>
+        <v>295</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>82</v>
@@ -13111,7 +13147,7 @@
         <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>427</v>
+        <v>296</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13119,14 +13155,14 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>428</v>
+        <v>391</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>429</v>
+        <v>297</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>430</v>
+        <v>82</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13145,17 +13181,15 @@
         <v>91</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>104</v>
+        <v>298</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>431</v>
+        <v>299</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>433</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>82</v>
@@ -13204,7 +13238,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>434</v>
+        <v>301</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13219,7 +13253,7 @@
         <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>435</v>
+        <v>302</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>82</v>
@@ -13228,7 +13262,7 @@
         <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>436</v>
+        <v>303</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13236,21 +13270,21 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>437</v>
+        <v>392</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>438</v>
+        <v>304</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>439</v>
+        <v>82</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>82</v>
@@ -13262,16 +13296,16 @@
         <v>91</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>104</v>
+        <v>305</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>440</v>
+        <v>306</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>441</v>
+        <v>307</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>442</v>
+        <v>308</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13321,13 +13355,13 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>443</v>
+        <v>309</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>82</v>
@@ -13336,7 +13370,7 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>444</v>
+        <v>310</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>82</v>
@@ -13345,7 +13379,7 @@
         <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>445</v>
+        <v>311</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13353,10 +13387,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>446</v>
+        <v>393</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>447</v>
+        <v>393</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13367,32 +13401,38 @@
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J92" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>104</v>
+        <v>394</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>448</v>
+        <v>395</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q92" s="2"/>
+      <c r="Q92" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="R92" t="s" s="2">
         <v>82</v>
       </c>
@@ -13436,13 +13476,13 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>450</v>
+        <v>393</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>82</v>
@@ -13451,16 +13491,16 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>451</v>
+        <v>400</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>82</v>
+        <v>401</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>452</v>
+        <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13468,10 +13508,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>453</v>
+        <v>402</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>454</v>
+        <v>402</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13494,16 +13534,20 @@
         <v>91</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>104</v>
+        <v>403</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>455</v>
+        <v>404</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" s="2"/>
+        <v>405</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
       </c>
@@ -13539,19 +13583,17 @@
         <v>82</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="AC93" s="2"/>
       <c r="AD93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>457</v>
+        <v>402</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13566,16 +13608,16 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>458</v>
+        <v>409</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>82</v>
+        <v>410</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>459</v>
+        <v>411</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13583,12 +13625,14 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>460</v>
+        <v>412</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="C94" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="C94" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="D94" t="s" s="2">
         <v>82</v>
       </c>
@@ -13597,7 +13641,7 @@
         <v>80</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>82</v>
@@ -13609,17 +13653,19 @@
         <v>91</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>298</v>
+        <v>414</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>462</v>
+        <v>415</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N94" s="2"/>
+        <v>416</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="O94" t="s" s="2">
-        <v>464</v>
+        <v>407</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13668,13 +13714,13 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>465</v>
+        <v>402</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>82</v>
@@ -13683,16 +13729,16 @@
         <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>466</v>
+        <v>409</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>82</v>
+        <v>410</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>467</v>
+        <v>411</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13700,14 +13746,12 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>468</v>
+        <v>417</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="C95" t="s" s="2">
-        <v>469</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
         <v>82</v>
       </c>
@@ -13716,7 +13760,7 @@
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>82</v>
@@ -13725,23 +13769,19 @@
         <v>82</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>400</v>
+        <v>104</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>470</v>
+        <v>105</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>82</v>
       </c>
@@ -13789,31 +13829,31 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>388</v>
+        <v>107</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>395</v>
+        <v>108</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>396</v>
+        <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13821,21 +13861,21 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>472</v>
+        <v>419</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>404</v>
+        <v>420</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>82</v>
@@ -13847,15 +13887,17 @@
         <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N96" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -13892,31 +13934,31 @@
         <v>82</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>108</v>
@@ -13936,44 +13978,46 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>406</v>
+        <v>422</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>112</v>
+        <v>423</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>113</v>
+        <v>424</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O97" s="2"/>
+        <v>425</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>426</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
       </c>
@@ -13982,7 +14026,7 @@
         <v>82</v>
       </c>
       <c r="S97" t="s" s="2">
-        <v>82</v>
+        <v>427</v>
       </c>
       <c r="T97" t="s" s="2">
         <v>82</v>
@@ -13997,46 +14041,46 @@
         <v>82</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>82</v>
+        <v>428</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>118</v>
+        <v>430</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>108</v>
+        <v>431</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>82</v>
@@ -14045,7 +14089,7 @@
         <v>82</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>82</v>
+        <v>432</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -14053,14 +14097,12 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>474</v>
+        <v>433</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="C98" t="s" s="2">
-        <v>475</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
         <v>82</v>
       </c>
@@ -14078,19 +14120,23 @@
         <v>82</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>476</v>
+        <v>104</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>477</v>
+        <v>435</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>438</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
@@ -14138,22 +14184,22 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>118</v>
+        <v>439</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>82</v>
@@ -14162,7 +14208,7 @@
         <v>82</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>82</v>
+        <v>441</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -14170,18 +14216,18 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>479</v>
+        <v>442</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>408</v>
+        <v>443</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>82</v>
+        <v>444</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>90</v>
@@ -14190,26 +14236,24 @@
         <v>82</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J99" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>171</v>
+        <v>104</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>409</v>
+        <v>445</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>410</v>
+        <v>446</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>412</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
@@ -14218,7 +14262,7 @@
         <v>82</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>318</v>
+        <v>82</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>82</v>
@@ -14233,13 +14277,13 @@
         <v>82</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>266</v>
+        <v>82</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>414</v>
+        <v>82</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>415</v>
+        <v>82</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>82</v>
@@ -14257,7 +14301,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>416</v>
+        <v>448</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14272,7 +14316,7 @@
         <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>417</v>
+        <v>449</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>82</v>
@@ -14281,7 +14325,7 @@
         <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>418</v>
+        <v>450</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14289,21 +14333,21 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>480</v>
+        <v>451</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>420</v>
+        <v>452</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>82</v>
+        <v>453</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>82</v>
@@ -14318,17 +14362,15 @@
         <v>104</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>421</v>
+        <v>454</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>422</v>
+        <v>455</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
@@ -14376,13 +14418,13 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>425</v>
+        <v>457</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>82</v>
@@ -14391,7 +14433,7 @@
         <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>426</v>
+        <v>458</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>82</v>
@@ -14400,7 +14442,7 @@
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>427</v>
+        <v>459</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14408,21 +14450,21 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>481</v>
+        <v>460</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>429</v>
+        <v>461</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>430</v>
+        <v>82</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>82</v>
@@ -14437,14 +14479,12 @@
         <v>104</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>431</v>
+        <v>462</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>433</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14493,13 +14533,13 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>434</v>
+        <v>464</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>82</v>
@@ -14508,7 +14548,7 @@
         <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>435</v>
+        <v>465</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>82</v>
@@ -14517,7 +14557,7 @@
         <v>82</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>436</v>
+        <v>466</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14525,18 +14565,18 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>482</v>
+        <v>467</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>438</v>
+        <v>468</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>439</v>
+        <v>82</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>81</v>
@@ -14554,14 +14594,12 @@
         <v>104</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>440</v>
+        <v>469</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>442</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>82</v>
@@ -14610,7 +14648,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>443</v>
+        <v>471</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14625,7 +14663,7 @@
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>444</v>
+        <v>472</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>82</v>
@@ -14634,7 +14672,7 @@
         <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>445</v>
+        <v>473</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14642,10 +14680,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>447</v>
+        <v>475</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14656,7 +14694,7 @@
         <v>80</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>82</v>
@@ -14668,16 +14706,18 @@
         <v>91</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>104</v>
+        <v>298</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>448</v>
+        <v>476</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>449</v>
+        <v>477</v>
       </c>
       <c r="N103" s="2"/>
-      <c r="O103" s="2"/>
+      <c r="O103" t="s" s="2">
+        <v>478</v>
+      </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
       </c>
@@ -14725,13 +14765,13 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>450</v>
+        <v>479</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>82</v>
@@ -14740,7 +14780,7 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>451</v>
+        <v>480</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>82</v>
@@ -14749,7 +14789,7 @@
         <v>82</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>452</v>
+        <v>481</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14757,12 +14797,14 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="C104" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="C104" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="D104" t="s" s="2">
         <v>82</v>
       </c>
@@ -14783,16 +14825,20 @@
         <v>91</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>104</v>
+        <v>414</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>455</v>
+        <v>484</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
+        <v>485</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
       </c>
@@ -14840,7 +14886,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>457</v>
+        <v>402</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14855,16 +14901,16 @@
         <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>458</v>
+        <v>409</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>82</v>
+        <v>410</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>459</v>
+        <v>411</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -14872,10 +14918,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>461</v>
+        <v>418</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14895,21 +14941,19 @@
         <v>82</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>298</v>
+        <v>104</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>462</v>
+        <v>105</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>463</v>
+        <v>106</v>
       </c>
       <c r="N105" s="2"/>
-      <c r="O105" t="s" s="2">
-        <v>464</v>
-      </c>
+      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>82</v>
       </c>
@@ -14957,7 +15001,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>465</v>
+        <v>107</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14969,10 +15013,10 @@
         <v>82</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>466</v>
+        <v>108</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>82</v>
@@ -14981,7 +15025,7 @@
         <v>82</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>467</v>
+        <v>82</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -14989,14 +15033,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>486</v>
+        <v>420</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -15012,23 +15056,21 @@
         <v>82</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>487</v>
+        <v>111</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>488</v>
+        <v>112</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>489</v>
+        <v>113</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>491</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>82</v>
       </c>
@@ -15064,19 +15106,19 @@
         <v>82</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>486</v>
+        <v>118</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15088,19 +15130,19 @@
         <v>82</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>492</v>
+        <v>108</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>493</v>
+        <v>82</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>494</v>
+        <v>82</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -15108,12 +15150,14 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="C107" s="2"/>
+        <v>420</v>
+      </c>
+      <c r="C107" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="D107" t="s" s="2">
         <v>82</v>
       </c>
@@ -15131,23 +15175,19 @@
         <v>82</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>171</v>
+        <v>490</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>499</v>
-      </c>
+        <v>492</v>
+      </c>
+      <c r="N107" s="2"/>
+      <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>82</v>
       </c>
@@ -15171,11 +15211,13 @@
         <v>82</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="Y107" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z107" t="s" s="2">
-        <v>500</v>
+        <v>82</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -15193,31 +15235,31 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>495</v>
+        <v>118</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>501</v>
+        <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>502</v>
+        <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>503</v>
+        <v>82</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15225,10 +15267,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>504</v>
+        <v>422</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15236,7 +15278,7 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G108" t="s" s="2">
         <v>90</v>
@@ -15245,25 +15287,25 @@
         <v>82</v>
       </c>
       <c r="I108" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J108" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>505</v>
+        <v>171</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>506</v>
+        <v>423</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>507</v>
+        <v>424</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>508</v>
+        <v>425</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>509</v>
+        <v>426</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -15273,7 +15315,7 @@
         <v>82</v>
       </c>
       <c r="S108" t="s" s="2">
-        <v>82</v>
+        <v>318</v>
       </c>
       <c r="T108" t="s" s="2">
         <v>82</v>
@@ -15288,13 +15330,13 @@
         <v>82</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>82</v>
+        <v>428</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15312,7 +15354,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>504</v>
+        <v>430</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15327,27 +15369,27 @@
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>510</v>
+        <v>431</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>511</v>
+        <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>512</v>
+        <v>432</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>513</v>
+        <v>82</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>514</v>
+        <v>494</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>514</v>
+        <v>434</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15364,25 +15406,25 @@
         <v>82</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J109" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>515</v>
+        <v>104</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>516</v>
+        <v>435</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>517</v>
+        <v>436</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>518</v>
+        <v>437</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>519</v>
+        <v>438</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15431,7 +15473,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>514</v>
+        <v>439</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15446,16 +15488,16 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>520</v>
+        <v>440</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>521</v>
+        <v>441</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>
@@ -15463,21 +15505,21 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>522</v>
+        <v>495</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>522</v>
+        <v>443</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>82</v>
+        <v>444</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>82</v>
@@ -15489,20 +15531,18 @@
         <v>91</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>238</v>
+        <v>104</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>523</v>
+        <v>445</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>524</v>
+        <v>446</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>526</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>82</v>
       </c>
@@ -15550,13 +15590,13 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>522</v>
+        <v>448</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>82</v>
@@ -15565,16 +15605,16 @@
         <v>102</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>527</v>
+        <v>449</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>529</v>
+        <v>450</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -15582,21 +15622,21 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>530</v>
+        <v>496</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>530</v>
+        <v>452</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>82</v>
+        <v>453</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>82</v>
@@ -15605,21 +15645,21 @@
         <v>82</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>272</v>
+        <v>104</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>531</v>
+        <v>454</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N111" s="2"/>
-      <c r="O111" t="s" s="2">
-        <v>533</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>82</v>
       </c>
@@ -15643,11 +15683,13 @@
         <v>82</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y111" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z111" t="s" s="2">
-        <v>534</v>
+        <v>82</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>82</v>
@@ -15665,13 +15707,13 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>530</v>
+        <v>457</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>82</v>
@@ -15680,16 +15722,16 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>535</v>
+        <v>458</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>536</v>
+        <v>82</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>537</v>
+        <v>459</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -15697,10 +15739,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>538</v>
+        <v>497</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>538</v>
+        <v>461</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15711,7 +15753,7 @@
         <v>80</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>82</v>
@@ -15720,23 +15762,19 @@
         <v>82</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>539</v>
+        <v>104</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>540</v>
+        <v>462</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>543</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>82</v>
       </c>
@@ -15784,13 +15822,13 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>538</v>
+        <v>464</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>82</v>
@@ -15799,16 +15837,16 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>544</v>
+        <v>465</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>545</v>
+        <v>466</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -15816,10 +15854,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>546</v>
+        <v>498</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>546</v>
+        <v>468</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15839,23 +15877,19 @@
         <v>82</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>547</v>
+        <v>104</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>548</v>
+        <v>469</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>551</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>82</v>
       </c>
@@ -15903,7 +15937,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>546</v>
+        <v>471</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -15918,16 +15952,16 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>552</v>
+        <v>472</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>553</v>
+        <v>473</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -15935,10 +15969,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>554</v>
+        <v>499</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>554</v>
+        <v>475</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15949,7 +15983,7 @@
         <v>80</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>82</v>
@@ -15958,22 +15992,20 @@
         <v>82</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>555</v>
+        <v>298</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>556</v>
+        <v>476</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>558</v>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>559</v>
+        <v>478</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>82</v>
@@ -16022,31 +16054,31 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>554</v>
+        <v>479</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>560</v>
+        <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>561</v>
+        <v>480</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>82</v>
+        <v>481</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -16054,10 +16086,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>562</v>
+        <v>500</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>562</v>
+        <v>500</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16068,7 +16100,7 @@
         <v>80</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>82</v>
@@ -16077,19 +16109,23 @@
         <v>82</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>104</v>
+        <v>501</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>105</v>
+        <v>502</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N115" s="2"/>
-      <c r="O115" s="2"/>
+        <v>503</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="O115" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
       </c>
@@ -16137,31 +16173,31 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>107</v>
+        <v>500</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>108</v>
+        <v>506</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>82</v>
+        <v>507</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>82</v>
+        <v>508</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
@@ -16169,10 +16205,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>563</v>
+        <v>509</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>563</v>
+        <v>509</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16183,7 +16219,7 @@
         <v>80</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>82</v>
@@ -16192,19 +16228,23 @@
         <v>82</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>196</v>
+        <v>510</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
+        <v>511</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>513</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>82</v>
       </c>
@@ -16228,53 +16268,53 @@
         <v>82</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="Y116" s="2"/>
       <c r="Z116" t="s" s="2">
-        <v>82</v>
+        <v>514</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AC116" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE116" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>118</v>
+        <v>509</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>82</v>
+        <v>515</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>82</v>
+        <v>516</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>82</v>
+        <v>517</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>82</v>
@@ -16282,14 +16322,12 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>564</v>
+        <v>518</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="C117" t="s" s="2">
-        <v>565</v>
-      </c>
+        <v>518</v>
+      </c>
+      <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
         <v>82</v>
       </c>
@@ -16307,19 +16345,23 @@
         <v>82</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>566</v>
+        <v>519</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>567</v>
+        <v>520</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
+        <v>521</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>82</v>
       </c>
@@ -16367,46 +16409,44 @@
         <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>118</v>
+        <v>518</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>204</v>
+        <v>82</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>82</v>
+        <v>524</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>82</v>
+        <v>525</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>82</v>
+        <v>526</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>82</v>
+        <v>527</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>569</v>
+        <v>528</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="C118" t="s" s="2">
-        <v>570</v>
-      </c>
+        <v>528</v>
+      </c>
+      <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
         <v>82</v>
       </c>
@@ -16421,22 +16461,26 @@
         <v>82</v>
       </c>
       <c r="I118" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>571</v>
+        <v>529</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>572</v>
+        <v>530</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N118" s="2"/>
-      <c r="O118" s="2"/>
+        <v>531</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>533</v>
+      </c>
       <c r="P118" t="s" s="2">
         <v>82</v>
       </c>
@@ -16484,31 +16528,31 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>118</v>
+        <v>528</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>204</v>
+        <v>82</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>82</v>
+        <v>534</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>82</v>
+        <v>535</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>82</v>
@@ -16516,14 +16560,14 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>574</v>
+        <v>536</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>574</v>
+        <v>536</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>575</v>
+        <v>82</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -16536,25 +16580,25 @@
         <v>82</v>
       </c>
       <c r="I119" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J119" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>111</v>
+        <v>238</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>576</v>
+        <v>537</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>577</v>
+        <v>538</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>114</v>
+        <v>539</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>246</v>
+        <v>540</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>82</v>
@@ -16603,7 +16647,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>578</v>
+        <v>536</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -16615,19 +16659,19 @@
         <v>82</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>194</v>
+        <v>541</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>82</v>
+        <v>542</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>82</v>
+        <v>543</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>82</v>
@@ -16635,10 +16679,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>579</v>
+        <v>544</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>579</v>
+        <v>544</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16649,7 +16693,7 @@
         <v>80</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>82</v>
@@ -16664,14 +16708,14 @@
         <v>272</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>580</v>
+        <v>545</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>581</v>
+        <v>546</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" t="s" s="2">
-        <v>582</v>
+        <v>547</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
@@ -16698,33 +16742,33 @@
       <c r="X120" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="Y120" t="s" s="2">
-        <v>583</v>
-      </c>
+      <c r="Y120" s="2"/>
       <c r="Z120" t="s" s="2">
-        <v>584</v>
+        <v>548</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="AC120" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD120" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE120" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>579</v>
+        <v>544</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>82</v>
@@ -16733,16 +16777,16 @@
         <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>586</v>
+        <v>549</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>108</v>
+        <v>550</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>587</v>
+        <v>551</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>82</v>
@@ -16750,14 +16794,12 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>588</v>
+        <v>552</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="C121" t="s" s="2">
-        <v>589</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
         <v>82</v>
       </c>
@@ -16778,17 +16820,19 @@
         <v>82</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>272</v>
+        <v>553</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>590</v>
+        <v>554</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="N121" s="2"/>
+        <v>555</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>556</v>
+      </c>
       <c r="O121" t="s" s="2">
-        <v>582</v>
+        <v>557</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>82</v>
@@ -16813,11 +16857,13 @@
         <v>82</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y121" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z121" t="s" s="2">
-        <v>591</v>
+        <v>82</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>82</v>
@@ -16835,13 +16881,13 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>579</v>
+        <v>552</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>82</v>
@@ -16850,7 +16896,7 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>586</v>
+        <v>558</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>108</v>
@@ -16859,7 +16905,7 @@
         <v>82</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>587</v>
+        <v>559</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>82</v>
@@ -16867,10 +16913,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>592</v>
+        <v>560</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>593</v>
+        <v>560</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16881,7 +16927,7 @@
         <v>80</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>82</v>
@@ -16893,16 +16939,20 @@
         <v>82</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>104</v>
+        <v>561</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>105</v>
+        <v>562</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N122" s="2"/>
-      <c r="O122" s="2"/>
+        <v>563</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="O122" t="s" s="2">
+        <v>565</v>
+      </c>
       <c r="P122" t="s" s="2">
         <v>82</v>
       </c>
@@ -16950,31 +17000,31 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>107</v>
+        <v>560</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AL122" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="AL122" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM122" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>82</v>
+        <v>567</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>82</v>
@@ -16982,10 +17032,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>594</v>
+        <v>568</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>595</v>
+        <v>568</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16993,7 +17043,7 @@
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G123" t="s" s="2">
         <v>81</v>
@@ -17008,16 +17058,20 @@
         <v>82</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>111</v>
+        <v>569</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>196</v>
+        <v>570</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N123" s="2"/>
-      <c r="O123" s="2"/>
+        <v>571</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="O123" t="s" s="2">
+        <v>573</v>
+      </c>
       <c r="P123" t="s" s="2">
         <v>82</v>
       </c>
@@ -17053,19 +17107,19 @@
         <v>82</v>
       </c>
       <c r="AB123" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="AC123" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AD123" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE123" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>118</v>
+        <v>568</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17077,13 +17131,13 @@
         <v>82</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>119</v>
+        <v>574</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>82</v>
+        <v>575</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>82</v>
@@ -17097,20 +17151,18 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>596</v>
+        <v>576</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="C124" t="s" s="2">
-        <v>597</v>
-      </c>
+        <v>576</v>
+      </c>
+      <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G124" t="s" s="2">
         <v>90</v>
@@ -17125,13 +17177,13 @@
         <v>82</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>598</v>
+        <v>104</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>599</v>
+        <v>105</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>600</v>
+        <v>106</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -17182,22 +17234,22 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AL124" t="s" s="2">
         <v>82</v>
@@ -17214,10 +17266,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>601</v>
+        <v>577</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>602</v>
+        <v>577</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17228,7 +17280,7 @@
         <v>80</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>82</v>
@@ -17240,13 +17292,13 @@
         <v>82</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>105</v>
+        <v>196</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>106</v>
+        <v>197</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -17285,34 +17337,32 @@
         <v>82</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="AC125" s="2"/>
       <c r="AD125" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE125" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AL125" t="s" s="2">
         <v>82</v>
@@ -17329,12 +17379,14 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="C126" s="2"/>
+        <v>577</v>
+      </c>
+      <c r="C126" t="s" s="2">
+        <v>579</v>
+      </c>
       <c r="D126" t="s" s="2">
         <v>82</v>
       </c>
@@ -17343,7 +17395,7 @@
         <v>80</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>82</v>
@@ -17355,13 +17407,13 @@
         <v>82</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>111</v>
+        <v>580</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>196</v>
+        <v>581</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>197</v>
+        <v>582</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -17400,16 +17452,16 @@
         <v>82</v>
       </c>
       <c r="AB126" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="AC126" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AD126" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE126" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
         <v>118</v>
@@ -17421,7 +17473,7 @@
         <v>81</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>82</v>
+        <v>204</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>119</v>
@@ -17444,18 +17496,20 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>605</v>
+        <v>583</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="C127" s="2"/>
+        <v>577</v>
+      </c>
+      <c r="C127" t="s" s="2">
+        <v>584</v>
+      </c>
       <c r="D127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G127" t="s" s="2">
         <v>90</v>
@@ -17470,24 +17524,22 @@
         <v>82</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>132</v>
+        <v>585</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>231</v>
+        <v>586</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>587</v>
+      </c>
+      <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
-        <v>607</v>
+        <v>82</v>
       </c>
       <c r="S127" t="s" s="2">
         <v>82</v>
@@ -17529,22 +17581,22 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>235</v>
+        <v>118</v>
       </c>
       <c r="AG127" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>82</v>
+        <v>204</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>194</v>
+        <v>82</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>82</v>
@@ -17561,42 +17613,46 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>608</v>
+        <v>588</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>609</v>
+        <v>588</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>82</v>
+        <v>589</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I128" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>171</v>
+        <v>111</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>239</v>
+        <v>590</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="N128" s="2"/>
-      <c r="O128" s="2"/>
+        <v>591</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O128" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P128" t="s" s="2">
         <v>82</v>
       </c>
@@ -17605,7 +17661,7 @@
         <v>82</v>
       </c>
       <c r="S128" t="s" s="2">
-        <v>589</v>
+        <v>82</v>
       </c>
       <c r="T128" t="s" s="2">
         <v>82</v>
@@ -17620,11 +17676,13 @@
         <v>82</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="Y128" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z128" t="s" s="2">
-        <v>611</v>
+        <v>82</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>82</v>
@@ -17642,19 +17700,19 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>241</v>
+        <v>592</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>194</v>
@@ -17674,10 +17732,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>612</v>
+        <v>593</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>613</v>
+        <v>593</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17697,22 +17755,20 @@
         <v>82</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>149</v>
+        <v>272</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>614</v>
+        <v>594</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>616</v>
-      </c>
+        <v>595</v>
+      </c>
+      <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>82</v>
@@ -17737,31 +17793,29 @@
         <v>82</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>82</v>
+        <v>597</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>82</v>
+        <v>598</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="AC129" s="2"/>
       <c r="AD129" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE129" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>618</v>
+        <v>593</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -17776,16 +17830,16 @@
         <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>619</v>
+        <v>600</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>620</v>
+        <v>601</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>82</v>
@@ -17793,12 +17847,14 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>621</v>
+        <v>602</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="C130" s="2"/>
+        <v>593</v>
+      </c>
+      <c r="C130" t="s" s="2">
+        <v>603</v>
+      </c>
       <c r="D130" t="s" s="2">
         <v>82</v>
       </c>
@@ -17816,22 +17872,20 @@
         <v>82</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>104</v>
+        <v>272</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>623</v>
+        <v>604</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>625</v>
-      </c>
+        <v>595</v>
+      </c>
+      <c r="N130" s="2"/>
       <c r="O130" t="s" s="2">
-        <v>626</v>
+        <v>596</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>82</v>
@@ -17856,13 +17910,11 @@
         <v>82</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y130" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y130" s="2"/>
       <c r="Z130" t="s" s="2">
-        <v>82</v>
+        <v>605</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>82</v>
@@ -17880,13 +17932,13 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>627</v>
+        <v>593</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>82</v>
@@ -17895,16 +17947,16 @@
         <v>102</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>628</v>
+        <v>600</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>629</v>
+        <v>601</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>82</v>
@@ -17912,14 +17964,12 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>630</v>
+        <v>606</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="C131" t="s" s="2">
-        <v>631</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
         <v>82</v>
       </c>
@@ -17940,18 +17990,16 @@
         <v>82</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>272</v>
+        <v>104</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>632</v>
+        <v>105</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>581</v>
+        <v>106</v>
       </c>
       <c r="N131" s="2"/>
-      <c r="O131" t="s" s="2">
-        <v>582</v>
-      </c>
+      <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>82</v>
       </c>
@@ -17975,11 +18023,13 @@
         <v>82</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y131" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z131" t="s" s="2">
-        <v>633</v>
+        <v>82</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>82</v>
@@ -17997,31 +18047,31 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>579</v>
+        <v>107</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>586</v>
+        <v>108</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>587</v>
+        <v>82</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>82</v>
@@ -18029,10 +18079,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>634</v>
+        <v>608</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>593</v>
+        <v>609</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18040,10 +18090,10 @@
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>82</v>
@@ -18055,13 +18105,13 @@
         <v>82</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>105</v>
+        <v>196</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>106</v>
+        <v>197</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -18100,34 +18150,34 @@
         <v>82</v>
       </c>
       <c r="AB132" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC132" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD132" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE132" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AL132" t="s" s="2">
         <v>82</v>
@@ -18144,12 +18194,14 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>635</v>
+        <v>610</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="C133" s="2"/>
+        <v>609</v>
+      </c>
+      <c r="C133" t="s" s="2">
+        <v>611</v>
+      </c>
       <c r="D133" t="s" s="2">
         <v>82</v>
       </c>
@@ -18158,7 +18210,7 @@
         <v>90</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>82</v>
@@ -18170,13 +18222,13 @@
         <v>82</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>111</v>
+        <v>612</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>196</v>
+        <v>613</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>197</v>
+        <v>614</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -18215,16 +18267,16 @@
         <v>82</v>
       </c>
       <c r="AB133" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="AC133" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AD133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE133" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
         <v>118</v>
@@ -18259,20 +18311,18 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>636</v>
+        <v>615</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="C134" t="s" s="2">
-        <v>597</v>
-      </c>
+        <v>616</v>
+      </c>
+      <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G134" t="s" s="2">
         <v>90</v>
@@ -18287,13 +18337,13 @@
         <v>82</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>598</v>
+        <v>104</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>599</v>
+        <v>105</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>600</v>
+        <v>106</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -18344,22 +18394,22 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AL134" t="s" s="2">
         <v>82</v>
@@ -18376,10 +18426,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>637</v>
+        <v>617</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>602</v>
+        <v>618</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18390,7 +18440,7 @@
         <v>80</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>82</v>
@@ -18402,13 +18452,13 @@
         <v>82</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>105</v>
+        <v>196</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>106</v>
+        <v>197</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -18447,34 +18497,34 @@
         <v>82</v>
       </c>
       <c r="AB135" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC135" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD135" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE135" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>82</v>
@@ -18491,10 +18541,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>638</v>
+        <v>619</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>604</v>
+        <v>620</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18502,10 +18552,10 @@
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>82</v>
@@ -18517,22 +18567,24 @@
         <v>82</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>196</v>
+        <v>231</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N136" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q136" s="2"/>
       <c r="R136" t="s" s="2">
-        <v>82</v>
+        <v>621</v>
       </c>
       <c r="S136" t="s" s="2">
         <v>82</v>
@@ -18562,34 +18614,34 @@
         <v>82</v>
       </c>
       <c r="AB136" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="AC136" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AD136" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE136" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>118</v>
+        <v>235</v>
       </c>
       <c r="AG136" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>82</v>
+        <v>194</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>82</v>
@@ -18606,10 +18658,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>639</v>
+        <v>622</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>606</v>
+        <v>623</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18617,7 +18669,7 @@
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G137" t="s" s="2">
         <v>90</v>
@@ -18632,27 +18684,25 @@
         <v>82</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>624</v>
+      </c>
+      <c r="N137" s="2"/>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q137" s="2"/>
       <c r="R137" t="s" s="2">
-        <v>607</v>
+        <v>82</v>
       </c>
       <c r="S137" t="s" s="2">
-        <v>82</v>
+        <v>603</v>
       </c>
       <c r="T137" t="s" s="2">
         <v>82</v>
@@ -18667,13 +18717,11 @@
         <v>82</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y137" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="Y137" s="2"/>
       <c r="Z137" t="s" s="2">
-        <v>82</v>
+        <v>625</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>82</v>
@@ -18691,10 +18739,10 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="AG137" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH137" t="s" s="2">
         <v>90</v>
@@ -18703,7 +18751,7 @@
         <v>82</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
         <v>194</v>
@@ -18723,10 +18771,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>640</v>
+        <v>626</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>609</v>
+        <v>627</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18737,7 +18785,7 @@
         <v>80</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>82</v>
@@ -18746,19 +18794,23 @@
         <v>82</v>
       </c>
       <c r="J138" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>239</v>
+        <v>628</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="N138" s="2"/>
-      <c r="O138" s="2"/>
+        <v>629</v>
+      </c>
+      <c r="N138" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="O138" t="s" s="2">
+        <v>631</v>
+      </c>
       <c r="P138" t="s" s="2">
         <v>82</v>
       </c>
@@ -18767,7 +18819,7 @@
         <v>82</v>
       </c>
       <c r="S138" t="s" s="2">
-        <v>631</v>
+        <v>82</v>
       </c>
       <c r="T138" t="s" s="2">
         <v>82</v>
@@ -18782,11 +18834,13 @@
         <v>82</v>
       </c>
       <c r="X138" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="Y138" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y138" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z138" t="s" s="2">
-        <v>611</v>
+        <v>82</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>82</v>
@@ -18804,13 +18858,13 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>241</v>
+        <v>632</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>82</v>
@@ -18819,7 +18873,7 @@
         <v>102</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>194</v>
+        <v>633</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>82</v>
@@ -18828,7 +18882,7 @@
         <v>82</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>82</v>
+        <v>634</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>82</v>
@@ -18836,10 +18890,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>613</v>
+        <v>636</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18850,7 +18904,7 @@
         <v>80</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>82</v>
@@ -18862,19 +18916,19 @@
         <v>91</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>149</v>
+        <v>104</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>614</v>
+        <v>637</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>615</v>
+        <v>638</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>616</v>
+        <v>639</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>617</v>
+        <v>640</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>82</v>
@@ -18923,13 +18977,13 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>618</v>
+        <v>641</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>82</v>
@@ -18938,7 +18992,7 @@
         <v>102</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>619</v>
+        <v>642</v>
       </c>
       <c r="AL139" t="s" s="2">
         <v>82</v>
@@ -18947,7 +19001,7 @@
         <v>82</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>620</v>
+        <v>643</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>82</v>
@@ -18955,12 +19009,14 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="C140" s="2"/>
+        <v>593</v>
+      </c>
+      <c r="C140" t="s" s="2">
+        <v>645</v>
+      </c>
       <c r="D140" t="s" s="2">
         <v>82</v>
       </c>
@@ -18978,22 +19034,20 @@
         <v>82</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>104</v>
+        <v>272</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>623</v>
+        <v>646</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>625</v>
-      </c>
+        <v>595</v>
+      </c>
+      <c r="N140" s="2"/>
       <c r="O140" t="s" s="2">
-        <v>626</v>
+        <v>596</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>82</v>
@@ -19018,13 +19072,11 @@
         <v>82</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y140" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y140" s="2"/>
       <c r="Z140" t="s" s="2">
-        <v>82</v>
+        <v>647</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>82</v>
@@ -19042,13 +19094,13 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>627</v>
+        <v>593</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>82</v>
@@ -19057,16 +19109,16 @@
         <v>102</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>628</v>
+        <v>600</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM140" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>629</v>
+        <v>601</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>82</v>
@@ -19074,10 +19126,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>643</v>
+        <v>607</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19100,18 +19152,16 @@
         <v>82</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>389</v>
+        <v>104</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>644</v>
+        <v>105</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>645</v>
+        <v>106</v>
       </c>
       <c r="N141" s="2"/>
-      <c r="O141" t="s" s="2">
-        <v>646</v>
-      </c>
+      <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>82</v>
       </c>
@@ -19159,7 +19209,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>643</v>
+        <v>107</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19171,19 +19221,19 @@
         <v>82</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>395</v>
+        <v>108</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>647</v>
+        <v>82</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>82</v>
@@ -19191,10 +19241,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>648</v>
+        <v>609</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19202,7 +19252,7 @@
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G142" t="s" s="2">
         <v>81</v>
@@ -19217,20 +19267,16 @@
         <v>82</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>487</v>
+        <v>111</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>649</v>
+        <v>196</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="O142" t="s" s="2">
-        <v>491</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N142" s="2"/>
+      <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
         <v>82</v>
       </c>
@@ -19266,19 +19312,19 @@
         <v>82</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC142" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD142" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE142" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>648</v>
+        <v>118</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19290,19 +19336,19 @@
         <v>82</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>492</v>
+        <v>82</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM142" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>652</v>
+        <v>82</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>82</v>
@@ -19310,18 +19356,20 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="C143" s="2"/>
+        <v>609</v>
+      </c>
+      <c r="C143" t="s" s="2">
+        <v>611</v>
+      </c>
       <c r="D143" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G143" t="s" s="2">
         <v>90</v>
@@ -19336,18 +19384,16 @@
         <v>82</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>654</v>
+        <v>612</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>655</v>
+        <v>613</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>656</v>
+        <v>614</v>
       </c>
       <c r="N143" s="2"/>
-      <c r="O143" t="s" s="2">
-        <v>657</v>
-      </c>
+      <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>82</v>
       </c>
@@ -19395,31 +19441,31 @@
         <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>653</v>
+        <v>118</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>527</v>
+        <v>82</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM143" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>658</v>
+        <v>82</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>82</v>
@@ -19427,10 +19473,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>659</v>
+        <v>616</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19453,18 +19499,16 @@
         <v>82</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>171</v>
+        <v>104</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>660</v>
+        <v>105</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>661</v>
+        <v>106</v>
       </c>
       <c r="N144" s="2"/>
-      <c r="O144" t="s" s="2">
-        <v>662</v>
-      </c>
+      <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
         <v>82</v>
       </c>
@@ -19488,13 +19532,13 @@
         <v>82</v>
       </c>
       <c r="X144" t="s" s="2">
-        <v>266</v>
+        <v>82</v>
       </c>
       <c r="Y144" t="s" s="2">
-        <v>663</v>
+        <v>82</v>
       </c>
       <c r="Z144" t="s" s="2">
-        <v>664</v>
+        <v>82</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>82</v>
@@ -19512,7 +19556,7 @@
         <v>82</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>659</v>
+        <v>107</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -19524,19 +19568,19 @@
         <v>82</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>501</v>
+        <v>108</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM144" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>665</v>
+        <v>82</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>82</v>
@@ -19544,10 +19588,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>666</v>
+        <v>652</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>666</v>
+        <v>618</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19558,7 +19602,7 @@
         <v>80</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>82</v>
@@ -19570,18 +19614,16 @@
         <v>82</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>305</v>
+        <v>111</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>667</v>
+        <v>196</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>668</v>
+        <v>197</v>
       </c>
       <c r="N145" s="2"/>
-      <c r="O145" t="s" s="2">
-        <v>669</v>
-      </c>
+      <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
         <v>82</v>
       </c>
@@ -19617,43 +19659,43 @@
         <v>82</v>
       </c>
       <c r="AB145" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC145" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD145" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE145" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>666</v>
+        <v>118</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>670</v>
+        <v>82</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>671</v>
+        <v>82</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM145" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>672</v>
+        <v>82</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>82</v>
@@ -19661,10 +19703,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>673</v>
+        <v>653</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>673</v>
+        <v>620</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19672,7 +19714,7 @@
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G146" t="s" s="2">
         <v>90</v>
@@ -19687,22 +19729,24 @@
         <v>82</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>298</v>
+        <v>132</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>674</v>
+        <v>231</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="N146" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="N146" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q146" s="2"/>
       <c r="R146" t="s" s="2">
-        <v>82</v>
+        <v>621</v>
       </c>
       <c r="S146" t="s" s="2">
         <v>82</v>
@@ -19744,10 +19788,10 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>673</v>
+        <v>235</v>
       </c>
       <c r="AG146" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH146" t="s" s="2">
         <v>90</v>
@@ -19756,13 +19800,13 @@
         <v>82</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>676</v>
+        <v>194</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM146" t="s" s="2">
         <v>82</v>
@@ -19776,10 +19820,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>677</v>
+        <v>654</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>677</v>
+        <v>623</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19790,7 +19834,7 @@
         <v>80</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H147" t="s" s="2">
         <v>82</v>
@@ -19802,20 +19846,16 @@
         <v>82</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>555</v>
+        <v>171</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>678</v>
+        <v>239</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="O147" t="s" s="2">
-        <v>681</v>
-      </c>
+        <v>624</v>
+      </c>
+      <c r="N147" s="2"/>
+      <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
         <v>82</v>
       </c>
@@ -19824,7 +19864,7 @@
         <v>82</v>
       </c>
       <c r="S147" t="s" s="2">
-        <v>82</v>
+        <v>645</v>
       </c>
       <c r="T147" t="s" s="2">
         <v>82</v>
@@ -19839,13 +19879,11 @@
         <v>82</v>
       </c>
       <c r="X147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y147" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="Y147" s="2"/>
       <c r="Z147" t="s" s="2">
-        <v>82</v>
+        <v>625</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>82</v>
@@ -19863,13 +19901,13 @@
         <v>82</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>677</v>
+        <v>241</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH147" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI147" t="s" s="2">
         <v>82</v>
@@ -19878,10 +19916,10 @@
         <v>102</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>682</v>
+        <v>194</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>683</v>
+        <v>82</v>
       </c>
       <c r="AM147" t="s" s="2">
         <v>82</v>
@@ -19895,10 +19933,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>684</v>
+        <v>655</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>684</v>
+        <v>627</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19909,7 +19947,7 @@
         <v>80</v>
       </c>
       <c r="G148" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H148" t="s" s="2">
         <v>82</v>
@@ -19918,19 +19956,23 @@
         <v>82</v>
       </c>
       <c r="J148" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>104</v>
+        <v>149</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>105</v>
+        <v>628</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N148" s="2"/>
-      <c r="O148" s="2"/>
+        <v>629</v>
+      </c>
+      <c r="N148" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="O148" t="s" s="2">
+        <v>631</v>
+      </c>
       <c r="P148" t="s" s="2">
         <v>82</v>
       </c>
@@ -19978,22 +20020,22 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>107</v>
+        <v>632</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH148" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI148" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ148" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>108</v>
+        <v>633</v>
       </c>
       <c r="AL148" t="s" s="2">
         <v>82</v>
@@ -20002,7 +20044,7 @@
         <v>82</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>82</v>
+        <v>634</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>82</v>
@@ -20010,21 +20052,21 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>685</v>
+        <v>656</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>685</v>
+        <v>636</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G149" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H149" t="s" s="2">
         <v>82</v>
@@ -20033,21 +20075,23 @@
         <v>82</v>
       </c>
       <c r="J149" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>112</v>
+        <v>637</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>113</v>
+        <v>638</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O149" s="2"/>
+        <v>639</v>
+      </c>
+      <c r="O149" t="s" s="2">
+        <v>640</v>
+      </c>
       <c r="P149" t="s" s="2">
         <v>82</v>
       </c>
@@ -20095,22 +20139,22 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>118</v>
+        <v>641</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH149" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI149" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>108</v>
+        <v>642</v>
       </c>
       <c r="AL149" t="s" s="2">
         <v>82</v>
@@ -20119,7 +20163,7 @@
         <v>82</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>82</v>
+        <v>643</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>82</v>
@@ -20127,45 +20171,43 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>686</v>
+        <v>657</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>686</v>
+        <v>657</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>575</v>
+        <v>82</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G150" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H150" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I150" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J150" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>111</v>
+        <v>403</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>576</v>
+        <v>658</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="N150" s="2"/>
       <c r="O150" t="s" s="2">
-        <v>246</v>
+        <v>660</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>82</v>
@@ -20214,31 +20256,31 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>578</v>
+        <v>657</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH150" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI150" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>194</v>
+        <v>409</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>82</v>
+        <v>661</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>82</v>
@@ -20246,10 +20288,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>687</v>
+        <v>662</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>687</v>
+        <v>662</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20257,10 +20299,10 @@
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H151" t="s" s="2">
         <v>82</v>
@@ -20272,19 +20314,19 @@
         <v>82</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>272</v>
+        <v>501</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>688</v>
+        <v>663</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>689</v>
+        <v>664</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>690</v>
+        <v>665</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>691</v>
+        <v>505</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>82</v>
@@ -20309,13 +20351,13 @@
         <v>82</v>
       </c>
       <c r="X151" t="s" s="2">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="Y151" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="Z151" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>82</v>
@@ -20333,13 +20375,13 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>687</v>
+        <v>662</v>
       </c>
       <c r="AG151" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI151" t="s" s="2">
         <v>82</v>
@@ -20348,16 +20390,16 @@
         <v>102</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>692</v>
+        <v>506</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>693</v>
+        <v>108</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>694</v>
+        <v>666</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>82</v>
@@ -20365,10 +20407,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>695</v>
+        <v>667</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>695</v>
+        <v>667</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20391,19 +20433,17 @@
         <v>82</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>380</v>
+        <v>668</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>696</v>
+        <v>669</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>698</v>
-      </c>
+        <v>670</v>
+      </c>
+      <c r="N152" s="2"/>
       <c r="O152" t="s" s="2">
-        <v>699</v>
+        <v>671</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>82</v>
@@ -20452,7 +20492,7 @@
         <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>695</v>
+        <v>667</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -20467,16 +20507,16 @@
         <v>102</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>700</v>
+        <v>541</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>701</v>
+        <v>108</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>702</v>
+        <v>672</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>82</v>
@@ -20484,21 +20524,21 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>703</v>
+        <v>673</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>703</v>
+        <v>673</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>704</v>
+        <v>82</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>82</v>
@@ -20510,18 +20550,18 @@
         <v>82</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>705</v>
+        <v>171</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>706</v>
+        <v>674</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="O153" s="2"/>
+        <v>675</v>
+      </c>
+      <c r="N153" s="2"/>
+      <c r="O153" t="s" s="2">
+        <v>676</v>
+      </c>
       <c r="P153" t="s" s="2">
         <v>82</v>
       </c>
@@ -20545,13 +20585,13 @@
         <v>82</v>
       </c>
       <c r="X153" t="s" s="2">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="Y153" t="s" s="2">
-        <v>82</v>
+        <v>677</v>
       </c>
       <c r="Z153" t="s" s="2">
-        <v>82</v>
+        <v>678</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>82</v>
@@ -20569,13 +20609,13 @@
         <v>82</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>703</v>
+        <v>673</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI153" t="s" s="2">
         <v>82</v>
@@ -20584,7 +20624,7 @@
         <v>102</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>709</v>
+        <v>515</v>
       </c>
       <c r="AL153" t="s" s="2">
         <v>108</v>
@@ -20593,7 +20633,7 @@
         <v>82</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>710</v>
+        <v>679</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>82</v>
@@ -20601,10 +20641,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>711</v>
+        <v>680</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>711</v>
+        <v>680</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20624,22 +20664,20 @@
         <v>82</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>712</v>
+        <v>305</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>713</v>
+        <v>681</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>715</v>
-      </c>
+        <v>682</v>
+      </c>
+      <c r="N154" s="2"/>
       <c r="O154" t="s" s="2">
-        <v>716</v>
+        <v>683</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>82</v>
@@ -20688,7 +20726,7 @@
         <v>82</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>711</v>
+        <v>680</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -20697,22 +20735,22 @@
         <v>90</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>82</v>
+        <v>684</v>
       </c>
       <c r="AJ154" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>671</v>
+        <v>685</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>717</v>
+        <v>108</v>
       </c>
       <c r="AM154" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>82</v>
+        <v>686</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>82</v>
@@ -20720,10 +20758,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>718</v>
+        <v>687</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>718</v>
+        <v>687</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20734,32 +20772,28 @@
         <v>80</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H155" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I155" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J155" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>555</v>
+        <v>298</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>719</v>
+        <v>688</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="O155" t="s" s="2">
-        <v>722</v>
-      </c>
+        <v>689</v>
+      </c>
+      <c r="N155" s="2"/>
+      <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
         <v>82</v>
       </c>
@@ -20807,13 +20841,13 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>718</v>
+        <v>687</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH155" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI155" t="s" s="2">
         <v>82</v>
@@ -20822,7 +20856,7 @@
         <v>102</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>723</v>
+        <v>690</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>108</v>
@@ -20839,10 +20873,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>724</v>
+        <v>691</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>724</v>
+        <v>691</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20853,7 +20887,7 @@
         <v>80</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>82</v>
@@ -20865,16 +20899,20 @@
         <v>82</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>104</v>
+        <v>569</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>105</v>
+        <v>692</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N156" s="2"/>
-      <c r="O156" s="2"/>
+        <v>693</v>
+      </c>
+      <c r="N156" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="O156" t="s" s="2">
+        <v>695</v>
+      </c>
       <c r="P156" t="s" s="2">
         <v>82</v>
       </c>
@@ -20922,25 +20960,25 @@
         <v>82</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>107</v>
+        <v>691</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI156" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>108</v>
+        <v>696</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>82</v>
+        <v>697</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>82</v>
@@ -20954,21 +20992,21 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>725</v>
+        <v>698</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>725</v>
+        <v>698</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H157" t="s" s="2">
         <v>82</v>
@@ -20980,17 +21018,15 @@
         <v>82</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N157" s="2"/>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
         <v>82</v>
@@ -21039,19 +21075,19 @@
         <v>82</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH157" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI157" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AK157" t="s" s="2">
         <v>108</v>
@@ -21071,14 +21107,14 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>726</v>
+        <v>699</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>726</v>
+        <v>699</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>575</v>
+        <v>110</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
@@ -21091,26 +21127,24 @@
         <v>82</v>
       </c>
       <c r="I158" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J158" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K158" t="s" s="2">
         <v>111</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>576</v>
+        <v>112</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>577</v>
+        <v>113</v>
       </c>
       <c r="N158" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="O158" t="s" s="2">
-        <v>246</v>
-      </c>
+      <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
         <v>82</v>
       </c>
@@ -21158,7 +21192,7 @@
         <v>82</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>578</v>
+        <v>118</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -21173,7 +21207,7 @@
         <v>119</v>
       </c>
       <c r="AK158" t="s" s="2">
-        <v>194</v>
+        <v>108</v>
       </c>
       <c r="AL158" t="s" s="2">
         <v>82</v>
@@ -21190,44 +21224,46 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>727</v>
+        <v>700</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>727</v>
+        <v>700</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
-        <v>82</v>
+        <v>589</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G159" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H159" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I159" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J159" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>728</v>
+        <v>111</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>729</v>
+        <v>590</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>730</v>
+        <v>591</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="O159" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="O159" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P159" t="s" s="2">
         <v>82</v>
       </c>
@@ -21275,31 +21311,31 @@
         <v>82</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>727</v>
+        <v>592</v>
       </c>
       <c r="AG159" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH159" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI159" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>255</v>
+        <v>194</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM159" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>732</v>
+        <v>82</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>82</v>
@@ -21307,10 +21343,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>733</v>
+        <v>701</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>733</v>
+        <v>701</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21330,19 +21366,23 @@
         <v>82</v>
       </c>
       <c r="J160" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>171</v>
+        <v>272</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>734</v>
+        <v>702</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="N160" s="2"/>
-      <c r="O160" s="2"/>
+        <v>703</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="O160" t="s" s="2">
+        <v>705</v>
+      </c>
       <c r="P160" t="s" s="2">
         <v>82</v>
       </c>
@@ -21366,13 +21406,13 @@
         <v>82</v>
       </c>
       <c r="X160" t="s" s="2">
-        <v>266</v>
+        <v>175</v>
       </c>
       <c r="Y160" t="s" s="2">
-        <v>735</v>
+        <v>176</v>
       </c>
       <c r="Z160" t="s" s="2">
-        <v>736</v>
+        <v>177</v>
       </c>
       <c r="AA160" t="s" s="2">
         <v>82</v>
@@ -21390,7 +21430,7 @@
         <v>82</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>733</v>
+        <v>701</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>90</v>
@@ -21405,18 +21445,1075 @@
         <v>102</v>
       </c>
       <c r="AK160" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="AL160" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="AM160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN160" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="AO160" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="C161" s="2"/>
+      <c r="D161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E161" s="2"/>
+      <c r="F161" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G161" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K161" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="L161" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="M161" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="N161" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="O161" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="P161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q161" s="2"/>
+      <c r="R161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF161" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="AG161" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH161" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ161" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK161" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="AL161" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="AM161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN161" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="AO161" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="B162" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="C162" s="2"/>
+      <c r="D162" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="E162" s="2"/>
+      <c r="F162" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K162" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="L162" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="M162" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="N162" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="O162" s="2"/>
+      <c r="P162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q162" s="2"/>
+      <c r="R162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF162" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="AG162" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ162" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK162" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="AL162" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN162" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="AO162" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="B163" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="C163" s="2"/>
+      <c r="D163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E163" s="2"/>
+      <c r="F163" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G163" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J163" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K163" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="L163" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="M163" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="N163" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="O163" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="P163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q163" s="2"/>
+      <c r="R163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF163" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="AG163" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH163" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ163" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK163" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="AL163" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="AM163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO163" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="B164" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="C164" s="2"/>
+      <c r="D164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E164" s="2"/>
+      <c r="F164" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I164" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J164" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K164" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="L164" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="M164" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="N164" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="O164" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="P164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q164" s="2"/>
+      <c r="R164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF164" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="AG164" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ164" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK164" t="s" s="2">
         <v>737</v>
       </c>
-      <c r="AL160" t="s" s="2">
+      <c r="AL164" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="AM160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO160" t="s" s="2">
+      <c r="AM164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO164" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="B165" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="C165" s="2"/>
+      <c r="D165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E165" s="2"/>
+      <c r="F165" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G165" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K165" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L165" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M165" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N165" s="2"/>
+      <c r="O165" s="2"/>
+      <c r="P165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q165" s="2"/>
+      <c r="R165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF165" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG165" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH165" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK165" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AL165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO165" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="B166" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="C166" s="2"/>
+      <c r="D166" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E166" s="2"/>
+      <c r="F166" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G166" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K166" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L166" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M166" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N166" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O166" s="2"/>
+      <c r="P166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q166" s="2"/>
+      <c r="R166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF166" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG166" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH166" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ166" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK166" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AL166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO166" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="B167" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="C167" s="2"/>
+      <c r="D167" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="E167" s="2"/>
+      <c r="F167" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G167" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I167" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J167" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K167" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L167" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M167" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="N167" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O167" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="P167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q167" s="2"/>
+      <c r="R167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF167" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AG167" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH167" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ167" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK167" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AL167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO167" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="B168" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="C168" s="2"/>
+      <c r="D168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E168" s="2"/>
+      <c r="F168" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G168" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J168" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K168" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="L168" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="M168" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="N168" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="O168" s="2"/>
+      <c r="P168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q168" s="2"/>
+      <c r="R168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF168" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="AG168" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH168" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ168" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK168" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AL168" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN168" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="AO168" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="B169" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="C169" s="2"/>
+      <c r="D169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E169" s="2"/>
+      <c r="F169" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G169" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J169" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K169" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L169" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="M169" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="N169" s="2"/>
+      <c r="O169" s="2"/>
+      <c r="P169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q169" s="2"/>
+      <c r="R169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X169" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="Y169" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="Z169" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="AA169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF169" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="AG169" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH169" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ169" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK169" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="AL169" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO169" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T15:00:47+00:00</t>
+    <t>2026-03-31T09:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:16:18+00:00</t>
+    <t>2026-05-07T06:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:50:40+00:00</t>
+    <t>2026-05-27T14:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:53:55+00:00</t>
+    <t>2026-05-28T14:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:22:24+00:00</t>
+    <t>2026-06-12T14:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:05:00+00:00</t>
+    <t>2026-06-12T14:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:35:23+00:00</t>
+    <t>2026-06-26T12:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T12:32:04+00:00</t>
+    <t>2026-06-29T09:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:30:52+00:00</t>
+    <t>2026-07-22T12:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:21:07+00:00</t>
+    <t>2026-07-27T15:02:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:02:31+00:00</t>
+    <t>2026-08-03T12:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T12:52:25+00:00</t>
+    <t>2026-08-04T12:22:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:22:31+00:00</t>
+    <t>2026-08-04T12:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:29:23+00:00</t>
+    <t>2026-08-10T16:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
